--- a/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_heart.xlsx
+++ b/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_heart.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="34">
   <si>
     <t>configuracion</t>
   </si>
@@ -570,10 +570,16 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H2">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I2" t="s">
         <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L2" t="s">
         <v>32</v>
@@ -635,10 +641,16 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H3">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I3" t="s">
         <v>15</v>
+      </c>
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L3" t="s">
         <v>32</v>
@@ -700,10 +712,16 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H4">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I4" t="s">
         <v>15</v>
+      </c>
+      <c r="J4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L4" t="s">
         <v>32</v>
@@ -765,10 +783,16 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H5">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I5" t="s">
         <v>15</v>
+      </c>
+      <c r="J5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L5" t="s">
         <v>30</v>
@@ -830,11 +854,17 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H6">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I6" t="s">
         <v>15</v>
       </c>
+      <c r="J6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L6" t="s">
         <v>26</v>
       </c>
@@ -851,7 +881,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
@@ -895,10 +925,16 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H7">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I7" t="s">
         <v>15</v>
+      </c>
+      <c r="J7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L7" t="s">
         <v>32</v>
@@ -948,7 +984,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -960,11 +996,17 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H8">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I8" t="s">
         <v>15</v>
       </c>
+      <c r="J8" t="s">
+        <v>28</v>
+      </c>
+      <c r="K8">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L8" t="s">
         <v>32</v>
       </c>
@@ -981,7 +1023,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -993,7 +1035,7 @@
         <v>7</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="V8">
         <v>7</v>
@@ -1025,11 +1067,17 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H9">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I9" t="s">
         <v>15</v>
       </c>
+      <c r="J9" t="s">
+        <v>28</v>
+      </c>
+      <c r="K9">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L9" t="s">
         <v>32</v>
       </c>
@@ -1046,7 +1094,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -1090,10 +1138,16 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H10">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I10" t="s">
         <v>15</v>
+      </c>
+      <c r="J10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L10" t="s">
         <v>26</v>
@@ -1155,11 +1209,17 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H11">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I11" t="s">
         <v>15</v>
       </c>
+      <c r="J11" t="s">
+        <v>28</v>
+      </c>
+      <c r="K11">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L11" t="s">
         <v>32</v>
       </c>
@@ -1176,7 +1236,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>
@@ -1220,11 +1280,17 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H12">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I12" t="s">
         <v>15</v>
       </c>
+      <c r="J12" t="s">
+        <v>30</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
       <c r="L12" t="s">
         <v>32</v>
       </c>
@@ -1241,7 +1307,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="b">
         <v>1</v>
@@ -1285,11 +1351,17 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H13">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I13" t="s">
         <v>15</v>
       </c>
+      <c r="J13" t="s">
+        <v>28</v>
+      </c>
+      <c r="K13">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L13" t="s">
         <v>32</v>
       </c>
@@ -1306,7 +1378,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="b">
         <v>1</v>
@@ -1350,10 +1422,16 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H14">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I14" t="s">
         <v>15</v>
+      </c>
+      <c r="J14" t="s">
+        <v>27</v>
+      </c>
+      <c r="K14">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L14" t="s">
         <v>29</v>
@@ -1415,11 +1493,17 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H15">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I15" t="s">
         <v>15</v>
       </c>
+      <c r="J15" t="s">
+        <v>28</v>
+      </c>
+      <c r="K15">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L15" t="s">
         <v>30</v>
       </c>
@@ -1436,7 +1520,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
@@ -1468,7 +1552,7 @@
         <v>1</v>
       </c>
       <c r="D16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>7</v>
@@ -1480,11 +1564,17 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H16">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I16" t="s">
         <v>15</v>
       </c>
+      <c r="J16" t="s">
+        <v>30</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
       <c r="L16" t="s">
         <v>32</v>
       </c>
@@ -1501,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="b">
         <v>1</v>
@@ -1545,11 +1635,17 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H17">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I17" t="s">
         <v>15</v>
       </c>
+      <c r="J17" t="s">
+        <v>28</v>
+      </c>
+      <c r="K17">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L17" t="s">
         <v>32</v>
       </c>
@@ -1566,7 +1662,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="b">
         <v>1</v>
@@ -1610,11 +1706,17 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H18">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I18" t="s">
         <v>15</v>
       </c>
+      <c r="J18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K18">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L18" t="s">
         <v>32</v>
       </c>
@@ -1631,7 +1733,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="b">
         <v>1</v>
@@ -1675,10 +1777,16 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H19">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I19" t="s">
         <v>15</v>
+      </c>
+      <c r="J19" t="s">
+        <v>26</v>
+      </c>
+      <c r="K19">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L19" t="s">
         <v>30</v>
@@ -1740,11 +1848,17 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H20">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I20" t="s">
         <v>15</v>
       </c>
+      <c r="J20" t="s">
+        <v>28</v>
+      </c>
+      <c r="K20">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L20" t="s">
         <v>31</v>
       </c>
@@ -1761,7 +1875,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
@@ -1805,10 +1919,16 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H21">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I21" t="s">
         <v>15</v>
+      </c>
+      <c r="J21" t="s">
+        <v>27</v>
+      </c>
+      <c r="K21">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L21" t="s">
         <v>30</v>
@@ -1870,11 +1990,17 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H22">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I22" t="s">
         <v>15</v>
       </c>
+      <c r="J22" t="s">
+        <v>30</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
       <c r="L22" t="s">
         <v>32</v>
       </c>
@@ -1891,7 +2017,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="b">
         <v>1</v>
@@ -1935,10 +2061,16 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H23">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I23" t="s">
         <v>15</v>
+      </c>
+      <c r="J23" t="s">
+        <v>26</v>
+      </c>
+      <c r="K23">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L23" t="s">
         <v>32</v>
@@ -2000,10 +2132,16 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H24">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I24" t="s">
         <v>15</v>
+      </c>
+      <c r="J24" t="s">
+        <v>29</v>
+      </c>
+      <c r="K24">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L24" t="s">
         <v>32</v>
@@ -2065,11 +2203,17 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H25">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I25" t="s">
         <v>15</v>
       </c>
+      <c r="J25" t="s">
+        <v>28</v>
+      </c>
+      <c r="K25">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L25" t="s">
         <v>32</v>
       </c>
@@ -2086,7 +2230,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="b">
         <v>1</v>
@@ -2130,10 +2274,16 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H26">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I26" t="s">
         <v>15</v>
+      </c>
+      <c r="J26" t="s">
+        <v>26</v>
+      </c>
+      <c r="K26">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L26" t="s">
         <v>33</v>
@@ -2195,11 +2345,17 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H27">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I27" t="s">
         <v>15</v>
       </c>
+      <c r="J27" t="s">
+        <v>30</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
       <c r="L27" t="s">
         <v>32</v>
       </c>
@@ -2216,7 +2372,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="b">
         <v>1</v>
@@ -2260,11 +2416,17 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H28">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I28" t="s">
         <v>15</v>
       </c>
+      <c r="J28" t="s">
+        <v>30</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
       <c r="L28" t="s">
         <v>31</v>
       </c>
@@ -2281,7 +2443,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="b">
         <v>0</v>
@@ -2325,10 +2487,16 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H29">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I29" t="s">
         <v>15</v>
+      </c>
+      <c r="J29" t="s">
+        <v>27</v>
+      </c>
+      <c r="K29">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L29" t="s">
         <v>33</v>
@@ -2390,10 +2558,16 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H30">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I30" t="s">
         <v>15</v>
+      </c>
+      <c r="J30" t="s">
+        <v>26</v>
+      </c>
+      <c r="K30">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L30" t="s">
         <v>32</v>
@@ -2455,11 +2629,17 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H31">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I31" t="s">
         <v>15</v>
       </c>
+      <c r="J31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
       <c r="L31" t="s">
         <v>31</v>
       </c>
@@ -2476,7 +2656,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="b">
         <v>0</v>
@@ -2520,10 +2700,16 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H32">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I32" t="s">
         <v>15</v>
+      </c>
+      <c r="J32" t="s">
+        <v>26</v>
+      </c>
+      <c r="K32">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L32" t="s">
         <v>32</v>
@@ -2585,10 +2771,16 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H33">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I33" t="s">
         <v>15</v>
+      </c>
+      <c r="J33" t="s">
+        <v>26</v>
+      </c>
+      <c r="K33">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L33" t="s">
         <v>32</v>
@@ -2650,11 +2842,17 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H34">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I34" t="s">
         <v>15</v>
       </c>
+      <c r="J34" t="s">
+        <v>28</v>
+      </c>
+      <c r="K34">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L34" t="s">
         <v>32</v>
       </c>
@@ -2671,7 +2869,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="b">
         <v>1</v>
@@ -2715,11 +2913,17 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H35">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I35" t="s">
         <v>15</v>
       </c>
+      <c r="J35" t="s">
+        <v>30</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
       <c r="L35" t="s">
         <v>32</v>
       </c>
@@ -2736,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="b">
         <v>1</v>
@@ -2780,10 +2984,16 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H36">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I36" t="s">
         <v>15</v>
+      </c>
+      <c r="J36" t="s">
+        <v>27</v>
+      </c>
+      <c r="K36">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L36" t="s">
         <v>32</v>
@@ -2845,11 +3055,17 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H37">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I37" t="s">
         <v>15</v>
       </c>
+      <c r="J37" t="s">
+        <v>28</v>
+      </c>
+      <c r="K37">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L37" t="s">
         <v>26</v>
       </c>
@@ -2866,7 +3082,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
@@ -2910,10 +3126,16 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H38">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I38" t="s">
         <v>15</v>
+      </c>
+      <c r="J38" t="s">
+        <v>26</v>
+      </c>
+      <c r="K38">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L38" t="s">
         <v>33</v>
@@ -2975,10 +3197,16 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H39">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I39" t="s">
         <v>15</v>
+      </c>
+      <c r="J39" t="s">
+        <v>29</v>
+      </c>
+      <c r="K39">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L39" t="s">
         <v>32</v>
@@ -3040,10 +3268,16 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H40">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I40" t="s">
         <v>15</v>
+      </c>
+      <c r="J40" t="s">
+        <v>26</v>
+      </c>
+      <c r="K40">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L40" t="s">
         <v>28</v>
@@ -3105,10 +3339,16 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H41">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I41" t="s">
         <v>15</v>
+      </c>
+      <c r="J41" t="s">
+        <v>26</v>
+      </c>
+      <c r="K41">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L41" t="s">
         <v>32</v>
@@ -3170,11 +3410,17 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H42">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I42" t="s">
         <v>15</v>
       </c>
+      <c r="J42" t="s">
+        <v>30</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
       <c r="L42" t="s">
         <v>32</v>
       </c>
@@ -3191,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="b">
         <v>1</v>
@@ -3235,10 +3481,16 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H43">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I43" t="s">
         <v>15</v>
+      </c>
+      <c r="J43" t="s">
+        <v>27</v>
+      </c>
+      <c r="K43">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L43" t="s">
         <v>33</v>
@@ -3300,11 +3552,17 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H44">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I44" t="s">
         <v>15</v>
       </c>
+      <c r="J44" t="s">
+        <v>28</v>
+      </c>
+      <c r="K44">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L44" t="s">
         <v>32</v>
       </c>
@@ -3321,7 +3579,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="b">
         <v>1</v>
@@ -3365,11 +3623,17 @@
         <v>1.661631768332852</v>
       </c>
       <c r="H45">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I45" t="s">
         <v>15</v>
       </c>
+      <c r="J45" t="s">
+        <v>28</v>
+      </c>
+      <c r="K45">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L45" t="s">
         <v>32</v>
       </c>
@@ -3386,7 +3650,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" t="b">
         <v>1</v>
@@ -3430,11 +3694,17 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H46">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I46" t="s">
         <v>15</v>
       </c>
+      <c r="J46" t="s">
+        <v>26</v>
+      </c>
+      <c r="K46">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L46" t="s">
         <v>27</v>
       </c>
@@ -3451,7 +3721,7 @@
         <v>0.863120568566631</v>
       </c>
       <c r="Q46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" t="b">
         <v>0</v>
@@ -3495,10 +3765,16 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H47">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I47" t="s">
         <v>15</v>
+      </c>
+      <c r="J47" t="s">
+        <v>27</v>
+      </c>
+      <c r="K47">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L47" t="s">
         <v>32</v>
@@ -3560,11 +3836,17 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H48">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I48" t="s">
         <v>15</v>
       </c>
+      <c r="J48" t="s">
+        <v>26</v>
+      </c>
+      <c r="K48">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L48" t="s">
         <v>32</v>
       </c>
@@ -3581,7 +3863,7 @@
         <v>0.863120568566631</v>
       </c>
       <c r="Q48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" t="b">
         <v>1</v>
@@ -3625,11 +3907,17 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H49">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I49" t="s">
         <v>15</v>
       </c>
+      <c r="J49" t="s">
+        <v>28</v>
+      </c>
+      <c r="K49">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L49" t="s">
         <v>32</v>
       </c>
@@ -3646,7 +3934,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" t="b">
         <v>1</v>
@@ -3690,11 +3978,17 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H50">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I50" t="s">
         <v>15</v>
       </c>
+      <c r="J50" t="s">
+        <v>26</v>
+      </c>
+      <c r="K50">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L50" t="s">
         <v>32</v>
       </c>
@@ -3711,7 +4005,7 @@
         <v>0.863120568566631</v>
       </c>
       <c r="Q50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R50" t="b">
         <v>1</v>
@@ -3755,11 +4049,17 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H51">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I51" t="s">
         <v>15</v>
       </c>
+      <c r="J51" t="s">
+        <v>28</v>
+      </c>
+      <c r="K51">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L51" t="s">
         <v>32</v>
       </c>
@@ -3776,7 +4076,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R51" t="b">
         <v>1</v>
@@ -3820,10 +4120,16 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H52">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I52" t="s">
         <v>15</v>
+      </c>
+      <c r="J52" t="s">
+        <v>29</v>
+      </c>
+      <c r="K52">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L52" t="s">
         <v>26</v>
@@ -3885,11 +4191,17 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H53">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I53" t="s">
         <v>15</v>
       </c>
+      <c r="J53" t="s">
+        <v>26</v>
+      </c>
+      <c r="K53">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L53" t="s">
         <v>26</v>
       </c>
@@ -3906,7 +4218,7 @@
         <v>0.863120568566631</v>
       </c>
       <c r="Q53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R53" t="b">
         <v>0</v>
@@ -3950,10 +4262,16 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H54">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I54" t="s">
         <v>15</v>
+      </c>
+      <c r="J54" t="s">
+        <v>29</v>
+      </c>
+      <c r="K54">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L54" t="s">
         <v>29</v>
@@ -4015,11 +4333,17 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H55">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I55" t="s">
         <v>15</v>
       </c>
+      <c r="J55" t="s">
+        <v>28</v>
+      </c>
+      <c r="K55">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L55" t="s">
         <v>32</v>
       </c>
@@ -4036,7 +4360,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R55" t="b">
         <v>1</v>
@@ -4080,11 +4404,17 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H56">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I56" t="s">
         <v>15</v>
       </c>
+      <c r="J56" t="s">
+        <v>30</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
       <c r="L56" t="s">
         <v>32</v>
       </c>
@@ -4101,7 +4431,7 @@
         <v>0</v>
       </c>
       <c r="Q56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R56" t="b">
         <v>1</v>
@@ -4145,10 +4475,16 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H57">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I57" t="s">
         <v>15</v>
+      </c>
+      <c r="J57" t="s">
+        <v>27</v>
+      </c>
+      <c r="K57">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L57" t="s">
         <v>32</v>
@@ -4198,7 +4534,7 @@
         <v>2</v>
       </c>
       <c r="D58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58">
         <v>7</v>
@@ -4210,11 +4546,17 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H58">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I58" t="s">
         <v>15</v>
       </c>
+      <c r="J58" t="s">
+        <v>28</v>
+      </c>
+      <c r="K58">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L58" t="s">
         <v>32</v>
       </c>
@@ -4231,7 +4573,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R58" t="b">
         <v>1</v>
@@ -4243,7 +4585,7 @@
         <v>7</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="V58">
         <v>7</v>
@@ -4275,11 +4617,17 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H59">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I59" t="s">
         <v>15</v>
       </c>
+      <c r="J59" t="s">
+        <v>30</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
       <c r="L59" t="s">
         <v>32</v>
       </c>
@@ -4296,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="Q59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R59" t="b">
         <v>1</v>
@@ -4340,11 +4688,17 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H60">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I60" t="s">
         <v>15</v>
       </c>
+      <c r="J60" t="s">
+        <v>26</v>
+      </c>
+      <c r="K60">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L60" t="s">
         <v>28</v>
       </c>
@@ -4361,7 +4715,7 @@
         <v>0.863120568566631</v>
       </c>
       <c r="Q60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R60" t="b">
         <v>0</v>
@@ -4405,11 +4759,17 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H61">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I61" t="s">
         <v>15</v>
       </c>
+      <c r="J61" t="s">
+        <v>30</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
       <c r="L61" t="s">
         <v>32</v>
       </c>
@@ -4426,7 +4786,7 @@
         <v>0</v>
       </c>
       <c r="Q61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R61" t="b">
         <v>1</v>
@@ -4470,11 +4830,17 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H62">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I62" t="s">
         <v>15</v>
       </c>
+      <c r="J62" t="s">
+        <v>26</v>
+      </c>
+      <c r="K62">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L62" t="s">
         <v>31</v>
       </c>
@@ -4491,7 +4857,7 @@
         <v>0.863120568566631</v>
       </c>
       <c r="Q62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
@@ -4535,11 +4901,17 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H63">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I63" t="s">
         <v>15</v>
       </c>
+      <c r="J63" t="s">
+        <v>26</v>
+      </c>
+      <c r="K63">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L63" t="s">
         <v>32</v>
       </c>
@@ -4556,7 +4928,7 @@
         <v>0.863120568566631</v>
       </c>
       <c r="Q63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R63" t="b">
         <v>1</v>
@@ -4600,11 +4972,17 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H64">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I64" t="s">
         <v>15</v>
       </c>
+      <c r="J64" t="s">
+        <v>26</v>
+      </c>
+      <c r="K64">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L64" t="s">
         <v>32</v>
       </c>
@@ -4621,7 +4999,7 @@
         <v>0.863120568566631</v>
       </c>
       <c r="Q64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R64" t="b">
         <v>1</v>
@@ -4665,11 +5043,17 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H65">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I65" t="s">
         <v>15</v>
       </c>
+      <c r="J65" t="s">
+        <v>26</v>
+      </c>
+      <c r="K65">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L65" t="s">
         <v>32</v>
       </c>
@@ -4686,7 +5070,7 @@
         <v>0.863120568566631</v>
       </c>
       <c r="Q65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R65" t="b">
         <v>1</v>
@@ -4730,11 +5114,17 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H66">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I66" t="s">
         <v>15</v>
       </c>
+      <c r="J66" t="s">
+        <v>26</v>
+      </c>
+      <c r="K66">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L66" t="s">
         <v>28</v>
       </c>
@@ -4751,7 +5141,7 @@
         <v>0.863120568566631</v>
       </c>
       <c r="Q66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
@@ -4783,7 +5173,7 @@
         <v>2</v>
       </c>
       <c r="D67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67">
         <v>7</v>
@@ -4795,11 +5185,17 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H67">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I67" t="s">
         <v>15</v>
       </c>
+      <c r="J67" t="s">
+        <v>26</v>
+      </c>
+      <c r="K67">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L67" t="s">
         <v>32</v>
       </c>
@@ -4816,7 +5212,7 @@
         <v>0.863120568566631</v>
       </c>
       <c r="Q67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R67" t="b">
         <v>1</v>
@@ -4828,7 +5224,7 @@
         <v>7</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="V67">
         <v>7</v>
@@ -4848,7 +5244,7 @@
         <v>2</v>
       </c>
       <c r="D68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68">
         <v>7</v>
@@ -4860,11 +5256,17 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H68">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I68" t="s">
         <v>15</v>
       </c>
+      <c r="J68" t="s">
+        <v>28</v>
+      </c>
+      <c r="K68">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L68" t="s">
         <v>32</v>
       </c>
@@ -4881,7 +5283,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R68" t="b">
         <v>1</v>
@@ -4893,7 +5295,7 @@
         <v>7</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="V68">
         <v>7</v>
@@ -4925,11 +5327,17 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H69">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I69" t="s">
         <v>15</v>
       </c>
+      <c r="J69" t="s">
+        <v>28</v>
+      </c>
+      <c r="K69">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L69" t="s">
         <v>28</v>
       </c>
@@ -4946,7 +5354,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R69" t="b">
         <v>0</v>
@@ -4990,11 +5398,17 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H70">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I70" t="s">
         <v>15</v>
       </c>
+      <c r="J70" t="s">
+        <v>30</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
       <c r="L70" t="s">
         <v>32</v>
       </c>
@@ -5011,7 +5425,7 @@
         <v>0</v>
       </c>
       <c r="Q70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R70" t="b">
         <v>1</v>
@@ -5055,10 +5469,16 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H71">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I71" t="s">
         <v>15</v>
+      </c>
+      <c r="J71" t="s">
+        <v>27</v>
+      </c>
+      <c r="K71">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L71" t="s">
         <v>32</v>
@@ -5120,11 +5540,17 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H72">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I72" t="s">
         <v>15</v>
       </c>
+      <c r="J72" t="s">
+        <v>26</v>
+      </c>
+      <c r="K72">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L72" t="s">
         <v>27</v>
       </c>
@@ -5141,7 +5567,7 @@
         <v>0.863120568566631</v>
       </c>
       <c r="Q72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" t="b">
         <v>0</v>
@@ -5185,11 +5611,17 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H73">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I73" t="s">
         <v>15</v>
       </c>
+      <c r="J73" t="s">
+        <v>26</v>
+      </c>
+      <c r="K73">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L73" t="s">
         <v>32</v>
       </c>
@@ -5206,7 +5638,7 @@
         <v>0.863120568566631</v>
       </c>
       <c r="Q73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R73" t="b">
         <v>1</v>
@@ -5238,7 +5670,7 @@
         <v>2</v>
       </c>
       <c r="D74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74">
         <v>7</v>
@@ -5250,11 +5682,17 @@
         <v>1.778362799058254</v>
       </c>
       <c r="H74">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I74" t="s">
         <v>15</v>
       </c>
+      <c r="J74" t="s">
+        <v>31</v>
+      </c>
+      <c r="K74">
+        <v>0.7142857142857143</v>
+      </c>
       <c r="L74" t="s">
         <v>32</v>
       </c>
@@ -5271,7 +5709,7 @@
         <v>0.863120568566631</v>
       </c>
       <c r="Q74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74" t="b">
         <v>1</v>
@@ -5283,7 +5721,7 @@
         <v>7</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="V74">
         <v>7</v>
@@ -5315,11 +5753,17 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H75">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I75" t="s">
         <v>15</v>
       </c>
+      <c r="J75" t="s">
+        <v>28</v>
+      </c>
+      <c r="K75">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L75" t="s">
         <v>32</v>
       </c>
@@ -5336,7 +5780,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R75" t="b">
         <v>1</v>
@@ -5368,7 +5812,7 @@
         <v>3</v>
       </c>
       <c r="D76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76">
         <v>7</v>
@@ -5380,11 +5824,17 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H76">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I76" t="s">
         <v>15</v>
       </c>
+      <c r="J76" t="s">
+        <v>28</v>
+      </c>
+      <c r="K76">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L76" t="s">
         <v>32</v>
       </c>
@@ -5401,7 +5851,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R76" t="b">
         <v>1</v>
@@ -5413,7 +5863,7 @@
         <v>7</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="V76">
         <v>7</v>
@@ -5445,10 +5895,16 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H77">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I77" t="s">
         <v>15</v>
+      </c>
+      <c r="J77" t="s">
+        <v>26</v>
+      </c>
+      <c r="K77">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L77" t="s">
         <v>32</v>
@@ -5510,11 +5966,17 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H78">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I78" t="s">
         <v>15</v>
       </c>
+      <c r="J78" t="s">
+        <v>28</v>
+      </c>
+      <c r="K78">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L78" t="s">
         <v>32</v>
       </c>
@@ -5531,7 +5993,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R78" t="b">
         <v>1</v>
@@ -5575,10 +6037,16 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H79">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I79" t="s">
         <v>15</v>
+      </c>
+      <c r="J79" t="s">
+        <v>26</v>
+      </c>
+      <c r="K79">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L79" t="s">
         <v>32</v>
@@ -5640,11 +6108,17 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H80">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I80" t="s">
         <v>15</v>
       </c>
+      <c r="J80" t="s">
+        <v>30</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
       <c r="L80" t="s">
         <v>32</v>
       </c>
@@ -5661,7 +6135,7 @@
         <v>0</v>
       </c>
       <c r="Q80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R80" t="b">
         <v>1</v>
@@ -5705,11 +6179,17 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H81">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I81" t="s">
         <v>15</v>
       </c>
+      <c r="J81" t="s">
+        <v>30</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
       <c r="L81" t="s">
         <v>32</v>
       </c>
@@ -5726,7 +6206,7 @@
         <v>0</v>
       </c>
       <c r="Q81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R81" t="b">
         <v>1</v>
@@ -5770,10 +6250,16 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H82">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I82" t="s">
         <v>15</v>
+      </c>
+      <c r="J82" t="s">
+        <v>26</v>
+      </c>
+      <c r="K82">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L82" t="s">
         <v>30</v>
@@ -5835,10 +6321,16 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H83">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I83" t="s">
         <v>15</v>
+      </c>
+      <c r="J83" t="s">
+        <v>26</v>
+      </c>
+      <c r="K83">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L83" t="s">
         <v>33</v>
@@ -5900,10 +6392,16 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H84">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I84" t="s">
         <v>15</v>
+      </c>
+      <c r="J84" t="s">
+        <v>26</v>
+      </c>
+      <c r="K84">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L84" t="s">
         <v>32</v>
@@ -5965,11 +6463,17 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H85">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I85" t="s">
         <v>15</v>
       </c>
+      <c r="J85" t="s">
+        <v>28</v>
+      </c>
+      <c r="K85">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L85" t="s">
         <v>28</v>
       </c>
@@ -5986,7 +6490,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R85" t="b">
         <v>0</v>
@@ -6030,11 +6534,17 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H86">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I86" t="s">
         <v>15</v>
       </c>
+      <c r="J86" t="s">
+        <v>30</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
       <c r="L86" t="s">
         <v>32</v>
       </c>
@@ -6051,7 +6561,7 @@
         <v>0</v>
       </c>
       <c r="Q86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R86" t="b">
         <v>1</v>
@@ -6095,10 +6605,16 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H87">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I87" t="s">
         <v>15</v>
+      </c>
+      <c r="J87" t="s">
+        <v>27</v>
+      </c>
+      <c r="K87">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L87" t="s">
         <v>30</v>
@@ -6148,7 +6664,7 @@
         <v>3</v>
       </c>
       <c r="D88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88">
         <v>7</v>
@@ -6160,11 +6676,17 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H88">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I88" t="s">
         <v>15</v>
       </c>
+      <c r="J88" t="s">
+        <v>28</v>
+      </c>
+      <c r="K88">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L88" t="s">
         <v>32</v>
       </c>
@@ -6181,7 +6703,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R88" t="b">
         <v>1</v>
@@ -6193,7 +6715,7 @@
         <v>7</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="V88">
         <v>7</v>
@@ -6225,11 +6747,17 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H89">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I89" t="s">
         <v>15</v>
       </c>
+      <c r="J89" t="s">
+        <v>30</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
       <c r="L89" t="s">
         <v>32</v>
       </c>
@@ -6246,7 +6774,7 @@
         <v>0</v>
       </c>
       <c r="Q89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R89" t="b">
         <v>1</v>
@@ -6290,11 +6818,17 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H90">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I90" t="s">
         <v>15</v>
       </c>
+      <c r="J90" t="s">
+        <v>30</v>
+      </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
       <c r="L90" t="s">
         <v>32</v>
       </c>
@@ -6311,7 +6845,7 @@
         <v>0</v>
       </c>
       <c r="Q90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R90" t="b">
         <v>1</v>
@@ -6355,11 +6889,17 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H91">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I91" t="s">
         <v>15</v>
       </c>
+      <c r="J91" t="s">
+        <v>28</v>
+      </c>
+      <c r="K91">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L91" t="s">
         <v>29</v>
       </c>
@@ -6376,7 +6916,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R91" t="b">
         <v>0</v>
@@ -6420,11 +6960,17 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H92">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I92" t="s">
         <v>15</v>
       </c>
+      <c r="J92" t="s">
+        <v>28</v>
+      </c>
+      <c r="K92">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L92" t="s">
         <v>32</v>
       </c>
@@ -6441,7 +6987,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R92" t="b">
         <v>1</v>
@@ -6485,11 +7031,17 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H93">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I93" t="s">
         <v>15</v>
       </c>
+      <c r="J93" t="s">
+        <v>30</v>
+      </c>
+      <c r="K93">
+        <v>0</v>
+      </c>
       <c r="L93" t="s">
         <v>32</v>
       </c>
@@ -6506,7 +7058,7 @@
         <v>0</v>
       </c>
       <c r="Q93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R93" t="b">
         <v>1</v>
@@ -6550,10 +7102,16 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H94">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I94" t="s">
         <v>15</v>
+      </c>
+      <c r="J94" t="s">
+        <v>26</v>
+      </c>
+      <c r="K94">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L94" t="s">
         <v>32</v>
@@ -6615,10 +7173,16 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H95">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I95" t="s">
         <v>15</v>
+      </c>
+      <c r="J95" t="s">
+        <v>26</v>
+      </c>
+      <c r="K95">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L95" t="s">
         <v>32</v>
@@ -6680,11 +7244,17 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H96">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I96" t="s">
         <v>15</v>
       </c>
+      <c r="J96" t="s">
+        <v>30</v>
+      </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
       <c r="L96" t="s">
         <v>29</v>
       </c>
@@ -6701,7 +7271,7 @@
         <v>0</v>
       </c>
       <c r="Q96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R96" t="b">
         <v>0</v>
@@ -6745,10 +7315,16 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H97">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I97" t="s">
         <v>15</v>
+      </c>
+      <c r="J97" t="s">
+        <v>26</v>
+      </c>
+      <c r="K97">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L97" t="s">
         <v>32</v>
@@ -6810,11 +7386,17 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H98">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I98" t="s">
         <v>15</v>
       </c>
+      <c r="J98" t="s">
+        <v>30</v>
+      </c>
+      <c r="K98">
+        <v>0</v>
+      </c>
       <c r="L98" t="s">
         <v>32</v>
       </c>
@@ -6831,7 +7413,7 @@
         <v>0</v>
       </c>
       <c r="Q98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R98" t="b">
         <v>1</v>
@@ -6875,10 +7457,16 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H99">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I99" t="s">
         <v>15</v>
+      </c>
+      <c r="J99" t="s">
+        <v>26</v>
+      </c>
+      <c r="K99">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L99" t="s">
         <v>30</v>
@@ -6940,11 +7528,17 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H100">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I100" t="s">
         <v>15</v>
       </c>
+      <c r="J100" t="s">
+        <v>30</v>
+      </c>
+      <c r="K100">
+        <v>0</v>
+      </c>
       <c r="L100" t="s">
         <v>29</v>
       </c>
@@ -6961,7 +7555,7 @@
         <v>0</v>
       </c>
       <c r="Q100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R100" t="b">
         <v>0</v>
@@ -7005,11 +7599,17 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H101">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I101" t="s">
         <v>15</v>
       </c>
+      <c r="J101" t="s">
+        <v>28</v>
+      </c>
+      <c r="K101">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L101" t="s">
         <v>32</v>
       </c>
@@ -7026,7 +7626,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R101" t="b">
         <v>1</v>
@@ -7070,10 +7670,16 @@
         <v>1.920905978863135</v>
       </c>
       <c r="H102">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I102" t="s">
         <v>15</v>
+      </c>
+      <c r="J102" t="s">
+        <v>26</v>
+      </c>
+      <c r="K102">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L102" t="s">
         <v>31</v>
@@ -7135,11 +7741,17 @@
         <v>2.115454798598829</v>
       </c>
       <c r="H103">
-        <v>0.3</v>
+        <v>0.3550036671493964</v>
       </c>
       <c r="I103" t="s">
         <v>15</v>
       </c>
+      <c r="J103" t="s">
+        <v>30</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
       <c r="L103" t="s">
         <v>32</v>
       </c>
@@ -7156,7 +7768,7 @@
         <v>0</v>
       </c>
       <c r="Q103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R103" t="b">
         <v>1</v>
@@ -7200,10 +7812,16 @@
         <v>2.115454798598829</v>
       </c>
       <c r="H104">
-        <v>0.3</v>
+        <v>0.3550036671493964</v>
       </c>
       <c r="I104" t="s">
         <v>15</v>
+      </c>
+      <c r="J104" t="s">
+        <v>28</v>
+      </c>
+      <c r="K104">
+        <v>0.1428571428571428</v>
       </c>
       <c r="L104" t="s">
         <v>26</v>
@@ -7265,10 +7883,16 @@
         <v>2.115454798598829</v>
       </c>
       <c r="H105">
-        <v>0.3</v>
+        <v>0.3550036671493964</v>
       </c>
       <c r="I105" t="s">
         <v>15</v>
+      </c>
+      <c r="J105" t="s">
+        <v>26</v>
+      </c>
+      <c r="K105">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L105" t="s">
         <v>32</v>
@@ -7330,10 +7954,16 @@
         <v>2.115454798598829</v>
       </c>
       <c r="H106">
-        <v>0.3</v>
+        <v>0.3550036671493964</v>
       </c>
       <c r="I106" t="s">
         <v>15</v>
+      </c>
+      <c r="J106" t="s">
+        <v>26</v>
+      </c>
+      <c r="K106">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L106" t="s">
         <v>32</v>
@@ -7395,10 +8025,16 @@
         <v>2.115454798598829</v>
       </c>
       <c r="H107">
-        <v>0.3</v>
+        <v>0.3550036671493964</v>
       </c>
       <c r="I107" t="s">
         <v>15</v>
+      </c>
+      <c r="J107" t="s">
+        <v>28</v>
+      </c>
+      <c r="K107">
+        <v>0.1428571428571428</v>
       </c>
       <c r="L107" t="s">
         <v>32</v>
@@ -7460,10 +8096,16 @@
         <v>2.115454798598829</v>
       </c>
       <c r="H108">
-        <v>0.3</v>
+        <v>0.3550036671493964</v>
       </c>
       <c r="I108" t="s">
         <v>15</v>
+      </c>
+      <c r="J108" t="s">
+        <v>28</v>
+      </c>
+      <c r="K108">
+        <v>0.1428571428571428</v>
       </c>
       <c r="L108" t="s">
         <v>32</v>
@@ -7525,10 +8167,16 @@
         <v>2.115454798598829</v>
       </c>
       <c r="H109">
-        <v>0.3</v>
+        <v>0.3550036671493964</v>
       </c>
       <c r="I109" t="s">
         <v>15</v>
+      </c>
+      <c r="J109" t="s">
+        <v>28</v>
+      </c>
+      <c r="K109">
+        <v>0.1428571428571428</v>
       </c>
       <c r="L109" t="s">
         <v>32</v>
@@ -7590,11 +8238,17 @@
         <v>2.115454798598829</v>
       </c>
       <c r="H110">
-        <v>0.3</v>
+        <v>0.3550036671493964</v>
       </c>
       <c r="I110" t="s">
         <v>15</v>
       </c>
+      <c r="J110" t="s">
+        <v>30</v>
+      </c>
+      <c r="K110">
+        <v>0</v>
+      </c>
       <c r="L110" t="s">
         <v>27</v>
       </c>
@@ -7611,7 +8265,7 @@
         <v>0</v>
       </c>
       <c r="Q110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R110" t="b">
         <v>0</v>
@@ -7655,11 +8309,17 @@
         <v>2.115454798598829</v>
       </c>
       <c r="H111">
-        <v>0.3</v>
+        <v>0.3550036671493964</v>
       </c>
       <c r="I111" t="s">
         <v>15</v>
       </c>
+      <c r="J111" t="s">
+        <v>30</v>
+      </c>
+      <c r="K111">
+        <v>0</v>
+      </c>
       <c r="L111" t="s">
         <v>29</v>
       </c>
@@ -7676,7 +8336,7 @@
         <v>0</v>
       </c>
       <c r="Q111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R111" t="b">
         <v>0</v>
@@ -7720,11 +8380,17 @@
         <v>2.115454798598829</v>
       </c>
       <c r="H112">
-        <v>0.3</v>
+        <v>0.3550036671493964</v>
       </c>
       <c r="I112" t="s">
         <v>15</v>
       </c>
+      <c r="J112" t="s">
+        <v>30</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
       <c r="L112" t="s">
         <v>31</v>
       </c>
@@ -7741,7 +8407,7 @@
         <v>0</v>
       </c>
       <c r="Q112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R112" t="b">
         <v>0</v>

--- a/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_heart.xlsx
+++ b/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_heart.xlsx
@@ -31,13 +31,16 @@
     <t>k</t>
   </si>
   <si>
-    <t>umbral_densidad</t>
+    <t>radio_percentil_distancias</t>
   </si>
   <si>
-    <t>umbral_riesgo</t>
+    <t>radio_percentil_riesgos</t>
   </si>
   <si>
     <t>umbral_entropia</t>
+  </si>
+  <si>
+    <t>entropia</t>
   </si>
   <si>
     <t>criterio_pureza</t>
@@ -59,9 +62,6 @@
   </si>
   <si>
     <t>riesgo_valor</t>
-  </si>
-  <si>
-    <t>entropia</t>
   </si>
   <si>
     <t>pasa_pureza</t>
@@ -572,29 +572,29 @@
       <c r="H2">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I2" t="s">
-        <v>15</v>
+      <c r="I2">
+        <v>0.863120568566631</v>
       </c>
       <c r="J2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" t="s">
         <v>26</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="M2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2" t="s">
         <v>31</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>0.7142857142857143</v>
-      </c>
-      <c r="P2">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q2" t="b">
         <v>0</v>
@@ -643,29 +643,29 @@
       <c r="H3">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I3" t="s">
-        <v>15</v>
+      <c r="I3">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" t="s">
         <v>27</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L3" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="M3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3" t="s">
         <v>26</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>0.2857142857142857</v>
-      </c>
-      <c r="P3">
-        <v>0.9852281360342515</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
@@ -714,29 +714,29 @@
       <c r="H4">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I4" t="s">
-        <v>15</v>
+      <c r="I4">
+        <v>0.863120568566631</v>
       </c>
       <c r="J4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" t="s">
         <v>26</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-      <c r="N4" t="s">
+      <c r="M4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4" t="s">
         <v>26</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>0.2857142857142857</v>
-      </c>
-      <c r="P4">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
@@ -785,29 +785,29 @@
       <c r="H5">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I5" t="s">
-        <v>15</v>
+      <c r="I5">
+        <v>0.863120568566631</v>
       </c>
       <c r="J5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K5" t="s">
         <v>26</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>30</v>
       </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
         <v>30</v>
       </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
       <c r="P5">
-        <v>0.863120568566631</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
@@ -856,29 +856,29 @@
       <c r="H6">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I6" t="s">
-        <v>15</v>
+      <c r="I6">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J6" t="s">
+        <v>8</v>
+      </c>
+      <c r="K6" t="s">
         <v>28</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>26</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>0.2857142857142857</v>
       </c>
-      <c r="N6" t="s">
+      <c r="O6" t="s">
         <v>28</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P6">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q6" t="b">
         <v>1</v>
@@ -927,29 +927,29 @@
       <c r="H7">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I7" t="s">
-        <v>15</v>
+      <c r="I7">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K7" t="s">
         <v>29</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>0.5714285714285714</v>
       </c>
-      <c r="L7" t="s">
-        <v>32</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-      <c r="N7" t="s">
+      <c r="M7" t="s">
+        <v>32</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7" t="s">
         <v>27</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>0.4285714285714285</v>
-      </c>
-      <c r="P7">
-        <v>0.9852281360342515</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
@@ -998,29 +998,29 @@
       <c r="H8">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I8" t="s">
-        <v>15</v>
+      <c r="I8">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" t="s">
         <v>28</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L8" t="s">
-        <v>32</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-      <c r="N8" t="s">
+      <c r="M8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8" t="s">
         <v>30</v>
       </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
       <c r="P8">
-        <v>0.5916727785823273</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="b">
         <v>1</v>
@@ -1069,29 +1069,29 @@
       <c r="H9">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I9" t="s">
-        <v>15</v>
+      <c r="I9">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J9" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" t="s">
         <v>28</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L9" t="s">
-        <v>32</v>
-      </c>
-      <c r="M9">
-        <v>1</v>
-      </c>
-      <c r="N9" t="s">
+      <c r="M9" t="s">
+        <v>32</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9" t="s">
         <v>27</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>0.4285714285714285</v>
-      </c>
-      <c r="P9">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q9" t="b">
         <v>1</v>
@@ -1140,29 +1140,29 @@
       <c r="H10">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I10" t="s">
-        <v>15</v>
+      <c r="I10">
+        <v>0.863120568566631</v>
       </c>
       <c r="J10" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" t="s">
         <v>26</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
         <v>26</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>0.2857142857142857</v>
       </c>
-      <c r="N10" t="s">
+      <c r="O10" t="s">
         <v>28</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P10">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q10" t="b">
         <v>0</v>
@@ -1211,29 +1211,29 @@
       <c r="H11">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I11" t="s">
-        <v>15</v>
+      <c r="I11">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J11" t="s">
+        <v>8</v>
+      </c>
+      <c r="K11" t="s">
         <v>28</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L11" t="s">
-        <v>32</v>
-      </c>
-      <c r="M11">
-        <v>1</v>
-      </c>
-      <c r="N11" t="s">
+      <c r="M11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11" t="s">
         <v>26</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>0.2857142857142857</v>
-      </c>
-      <c r="P11">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q11" t="b">
         <v>1</v>
@@ -1282,29 +1282,29 @@
       <c r="H12">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I12" t="s">
-        <v>15</v>
+      <c r="I12">
+        <v>0</v>
       </c>
       <c r="J12" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" t="s">
         <v>30</v>
       </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12" t="s">
-        <v>32</v>
-      </c>
-      <c r="M12">
-        <v>1</v>
-      </c>
-      <c r="N12" t="s">
-        <v>32</v>
-      </c>
-      <c r="O12">
-        <v>1</v>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" t="s">
+        <v>32</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12" t="s">
+        <v>32</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="b">
         <v>0</v>
@@ -1353,29 +1353,29 @@
       <c r="H13">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I13" t="s">
-        <v>15</v>
+      <c r="I13">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J13" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" t="s">
         <v>28</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L13" t="s">
-        <v>32</v>
-      </c>
-      <c r="M13">
-        <v>1</v>
-      </c>
-      <c r="N13" t="s">
+      <c r="M13" t="s">
+        <v>32</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13" t="s">
         <v>26</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>0.2857142857142857</v>
-      </c>
-      <c r="P13">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q13" t="b">
         <v>1</v>
@@ -1424,29 +1424,29 @@
       <c r="H14">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I14" t="s">
-        <v>15</v>
+      <c r="I14">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J14" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" t="s">
         <v>27</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
         <v>29</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N14" t="s">
+      <c r="O14" t="s">
         <v>30</v>
       </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
       <c r="P14">
-        <v>0.9852281360342515</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="b">
         <v>0</v>
@@ -1495,29 +1495,29 @@
       <c r="H15">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I15" t="s">
-        <v>15</v>
+      <c r="I15">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J15" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" t="s">
         <v>28</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L15" t="s">
+      <c r="M15" t="s">
         <v>30</v>
       </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15" t="s">
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" t="s">
         <v>30</v>
       </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
       <c r="P15">
-        <v>0.5916727785823273</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="b">
         <v>1</v>
@@ -1566,26 +1566,26 @@
       <c r="H16">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I16" t="s">
-        <v>15</v>
+      <c r="I16">
+        <v>0</v>
       </c>
       <c r="J16" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" t="s">
         <v>30</v>
       </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16" t="s">
-        <v>32</v>
-      </c>
-      <c r="M16">
-        <v>1</v>
-      </c>
-      <c r="N16" t="s">
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16" t="s">
+        <v>32</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16" t="s">
         <v>30</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -1637,29 +1637,29 @@
       <c r="H17">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I17" t="s">
-        <v>15</v>
+      <c r="I17">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J17" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" t="s">
         <v>28</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L17" t="s">
-        <v>32</v>
-      </c>
-      <c r="M17">
-        <v>1</v>
-      </c>
-      <c r="N17" t="s">
+      <c r="M17" t="s">
+        <v>32</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17" t="s">
         <v>26</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>0.2857142857142857</v>
-      </c>
-      <c r="P17">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q17" t="b">
         <v>1</v>
@@ -1708,29 +1708,29 @@
       <c r="H18">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I18" t="s">
-        <v>15</v>
+      <c r="I18">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J18" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" t="s">
         <v>28</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L18" t="s">
-        <v>32</v>
-      </c>
-      <c r="M18">
-        <v>1</v>
-      </c>
-      <c r="N18" t="s">
+      <c r="M18" t="s">
+        <v>32</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18" t="s">
         <v>27</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>0.4285714285714285</v>
-      </c>
-      <c r="P18">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q18" t="b">
         <v>1</v>
@@ -1779,29 +1779,29 @@
       <c r="H19">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I19" t="s">
-        <v>15</v>
+      <c r="I19">
+        <v>0.863120568566631</v>
       </c>
       <c r="J19" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" t="s">
         <v>26</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L19" t="s">
+      <c r="M19" t="s">
         <v>30</v>
       </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19" t="s">
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19" t="s">
         <v>30</v>
       </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
       <c r="P19">
-        <v>0.863120568566631</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="b">
         <v>0</v>
@@ -1850,29 +1850,29 @@
       <c r="H20">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I20" t="s">
-        <v>15</v>
+      <c r="I20">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J20" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" t="s">
         <v>28</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L20" t="s">
+      <c r="M20" t="s">
         <v>31</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>0.7142857142857143</v>
       </c>
-      <c r="N20" t="s">
+      <c r="O20" t="s">
         <v>26</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>0.2857142857142857</v>
-      </c>
-      <c r="P20">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q20" t="b">
         <v>1</v>
@@ -1921,29 +1921,29 @@
       <c r="H21">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I21" t="s">
-        <v>15</v>
+      <c r="I21">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J21" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" t="s">
         <v>27</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L21" t="s">
+      <c r="M21" t="s">
         <v>30</v>
       </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21" t="s">
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21" t="s">
         <v>30</v>
       </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
       <c r="P21">
-        <v>0.9852281360342515</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="b">
         <v>0</v>
@@ -1992,29 +1992,29 @@
       <c r="H22">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I22" t="s">
-        <v>15</v>
+      <c r="I22">
+        <v>0</v>
       </c>
       <c r="J22" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" t="s">
         <v>30</v>
       </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22" t="s">
-        <v>32</v>
-      </c>
-      <c r="M22">
-        <v>1</v>
-      </c>
-      <c r="N22" t="s">
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22" t="s">
+        <v>32</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="O22" t="s">
         <v>33</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>0.8571428571428571</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
       </c>
       <c r="Q22" t="b">
         <v>0</v>
@@ -2063,29 +2063,29 @@
       <c r="H23">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I23" t="s">
-        <v>15</v>
+      <c r="I23">
+        <v>0.863120568566631</v>
       </c>
       <c r="J23" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" t="s">
         <v>26</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L23" t="s">
-        <v>32</v>
-      </c>
-      <c r="M23">
-        <v>1</v>
-      </c>
-      <c r="N23" t="s">
+      <c r="M23" t="s">
+        <v>32</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="O23" t="s">
         <v>28</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P23">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q23" t="b">
         <v>0</v>
@@ -2134,29 +2134,29 @@
       <c r="H24">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I24" t="s">
-        <v>15</v>
+      <c r="I24">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J24" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" t="s">
         <v>29</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>0.5714285714285714</v>
       </c>
-      <c r="L24" t="s">
-        <v>32</v>
-      </c>
-      <c r="M24">
-        <v>1</v>
-      </c>
-      <c r="N24" t="s">
+      <c r="M24" t="s">
+        <v>32</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="O24" t="s">
         <v>27</v>
       </c>
-      <c r="O24">
+      <c r="P24">
         <v>0.4285714285714285</v>
-      </c>
-      <c r="P24">
-        <v>0.9852281360342515</v>
       </c>
       <c r="Q24" t="b">
         <v>0</v>
@@ -2205,29 +2205,29 @@
       <c r="H25">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I25" t="s">
-        <v>15</v>
+      <c r="I25">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J25" t="s">
+        <v>8</v>
+      </c>
+      <c r="K25" t="s">
         <v>28</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L25" t="s">
-        <v>32</v>
-      </c>
-      <c r="M25">
-        <v>1</v>
-      </c>
-      <c r="N25" t="s">
+      <c r="M25" t="s">
+        <v>32</v>
+      </c>
+      <c r="N25">
+        <v>1</v>
+      </c>
+      <c r="O25" t="s">
         <v>33</v>
       </c>
-      <c r="O25">
+      <c r="P25">
         <v>0.8571428571428571</v>
-      </c>
-      <c r="P25">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q25" t="b">
         <v>1</v>
@@ -2276,29 +2276,29 @@
       <c r="H26">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I26" t="s">
-        <v>15</v>
+      <c r="I26">
+        <v>0.863120568566631</v>
       </c>
       <c r="J26" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" t="s">
         <v>26</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L26" t="s">
+      <c r="M26" t="s">
         <v>33</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>0.8571428571428571</v>
       </c>
-      <c r="N26" t="s">
+      <c r="O26" t="s">
         <v>28</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P26">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q26" t="b">
         <v>0</v>
@@ -2347,29 +2347,29 @@
       <c r="H27">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I27" t="s">
-        <v>15</v>
+      <c r="I27">
+        <v>0</v>
       </c>
       <c r="J27" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" t="s">
         <v>30</v>
       </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27" t="s">
-        <v>32</v>
-      </c>
-      <c r="M27">
-        <v>1</v>
-      </c>
-      <c r="N27" t="s">
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" t="s">
+        <v>32</v>
+      </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
+      <c r="O27" t="s">
         <v>26</v>
       </c>
-      <c r="O27">
+      <c r="P27">
         <v>0.2857142857142857</v>
-      </c>
-      <c r="P27">
-        <v>0</v>
       </c>
       <c r="Q27" t="b">
         <v>0</v>
@@ -2418,29 +2418,29 @@
       <c r="H28">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I28" t="s">
-        <v>15</v>
+      <c r="I28">
+        <v>0</v>
       </c>
       <c r="J28" t="s">
+        <v>8</v>
+      </c>
+      <c r="K28" t="s">
         <v>30</v>
       </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28" t="s">
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28" t="s">
         <v>31</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>0.7142857142857143</v>
       </c>
-      <c r="N28" t="s">
+      <c r="O28" t="s">
         <v>29</v>
       </c>
-      <c r="O28">
+      <c r="P28">
         <v>0.5714285714285714</v>
-      </c>
-      <c r="P28">
-        <v>0</v>
       </c>
       <c r="Q28" t="b">
         <v>0</v>
@@ -2489,29 +2489,29 @@
       <c r="H29">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I29" t="s">
-        <v>15</v>
+      <c r="I29">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J29" t="s">
+        <v>8</v>
+      </c>
+      <c r="K29" t="s">
         <v>27</v>
       </c>
-      <c r="K29">
+      <c r="L29">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L29" t="s">
+      <c r="M29" t="s">
         <v>33</v>
       </c>
-      <c r="M29">
+      <c r="N29">
         <v>0.8571428571428571</v>
       </c>
-      <c r="N29" t="s">
+      <c r="O29" t="s">
         <v>30</v>
       </c>
-      <c r="O29">
-        <v>0</v>
-      </c>
       <c r="P29">
-        <v>0.9852281360342515</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="b">
         <v>0</v>
@@ -2560,29 +2560,29 @@
       <c r="H30">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I30" t="s">
-        <v>15</v>
+      <c r="I30">
+        <v>0.863120568566631</v>
       </c>
       <c r="J30" t="s">
+        <v>8</v>
+      </c>
+      <c r="K30" t="s">
         <v>26</v>
       </c>
-      <c r="K30">
+      <c r="L30">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L30" t="s">
-        <v>32</v>
-      </c>
-      <c r="M30">
-        <v>1</v>
-      </c>
-      <c r="N30" t="s">
+      <c r="M30" t="s">
+        <v>32</v>
+      </c>
+      <c r="N30">
+        <v>1</v>
+      </c>
+      <c r="O30" t="s">
         <v>31</v>
       </c>
-      <c r="O30">
+      <c r="P30">
         <v>0.7142857142857143</v>
-      </c>
-      <c r="P30">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q30" t="b">
         <v>0</v>
@@ -2631,29 +2631,29 @@
       <c r="H31">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I31" t="s">
-        <v>15</v>
+      <c r="I31">
+        <v>0</v>
       </c>
       <c r="J31" t="s">
+        <v>8</v>
+      </c>
+      <c r="K31" t="s">
         <v>30</v>
       </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31" t="s">
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31" t="s">
         <v>31</v>
       </c>
-      <c r="M31">
+      <c r="N31">
         <v>0.7142857142857143</v>
       </c>
-      <c r="N31" t="s">
+      <c r="O31" t="s">
         <v>28</v>
       </c>
-      <c r="O31">
+      <c r="P31">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P31">
-        <v>0</v>
       </c>
       <c r="Q31" t="b">
         <v>0</v>
@@ -2702,29 +2702,29 @@
       <c r="H32">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I32" t="s">
-        <v>15</v>
+      <c r="I32">
+        <v>0.863120568566631</v>
       </c>
       <c r="J32" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" t="s">
         <v>26</v>
       </c>
-      <c r="K32">
+      <c r="L32">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L32" t="s">
-        <v>32</v>
-      </c>
-      <c r="M32">
-        <v>1</v>
-      </c>
-      <c r="N32" t="s">
+      <c r="M32" t="s">
+        <v>32</v>
+      </c>
+      <c r="N32">
+        <v>1</v>
+      </c>
+      <c r="O32" t="s">
         <v>29</v>
       </c>
-      <c r="O32">
+      <c r="P32">
         <v>0.5714285714285714</v>
-      </c>
-      <c r="P32">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q32" t="b">
         <v>0</v>
@@ -2773,29 +2773,29 @@
       <c r="H33">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I33" t="s">
-        <v>15</v>
+      <c r="I33">
+        <v>0.863120568566631</v>
       </c>
       <c r="J33" t="s">
+        <v>8</v>
+      </c>
+      <c r="K33" t="s">
         <v>26</v>
       </c>
-      <c r="K33">
+      <c r="L33">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L33" t="s">
-        <v>32</v>
-      </c>
-      <c r="M33">
-        <v>1</v>
-      </c>
-      <c r="N33" t="s">
+      <c r="M33" t="s">
+        <v>32</v>
+      </c>
+      <c r="N33">
+        <v>1</v>
+      </c>
+      <c r="O33" t="s">
         <v>30</v>
       </c>
-      <c r="O33">
-        <v>0</v>
-      </c>
       <c r="P33">
-        <v>0.863120568566631</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="b">
         <v>0</v>
@@ -2844,29 +2844,29 @@
       <c r="H34">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I34" t="s">
-        <v>15</v>
+      <c r="I34">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J34" t="s">
+        <v>8</v>
+      </c>
+      <c r="K34" t="s">
         <v>28</v>
       </c>
-      <c r="K34">
+      <c r="L34">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L34" t="s">
-        <v>32</v>
-      </c>
-      <c r="M34">
-        <v>1</v>
-      </c>
-      <c r="N34" t="s">
+      <c r="M34" t="s">
+        <v>32</v>
+      </c>
+      <c r="N34">
+        <v>1</v>
+      </c>
+      <c r="O34" t="s">
         <v>26</v>
       </c>
-      <c r="O34">
+      <c r="P34">
         <v>0.2857142857142857</v>
-      </c>
-      <c r="P34">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q34" t="b">
         <v>1</v>
@@ -2915,29 +2915,29 @@
       <c r="H35">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I35" t="s">
-        <v>15</v>
+      <c r="I35">
+        <v>0</v>
       </c>
       <c r="J35" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" t="s">
         <v>30</v>
       </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35" t="s">
-        <v>32</v>
-      </c>
-      <c r="M35">
-        <v>1</v>
-      </c>
-      <c r="N35" t="s">
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" t="s">
+        <v>32</v>
+      </c>
+      <c r="N35">
+        <v>1</v>
+      </c>
+      <c r="O35" t="s">
         <v>26</v>
       </c>
-      <c r="O35">
+      <c r="P35">
         <v>0.2857142857142857</v>
-      </c>
-      <c r="P35">
-        <v>0</v>
       </c>
       <c r="Q35" t="b">
         <v>0</v>
@@ -2986,29 +2986,29 @@
       <c r="H36">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I36" t="s">
-        <v>15</v>
+      <c r="I36">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J36" t="s">
+        <v>8</v>
+      </c>
+      <c r="K36" t="s">
         <v>27</v>
       </c>
-      <c r="K36">
+      <c r="L36">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L36" t="s">
-        <v>32</v>
-      </c>
-      <c r="M36">
-        <v>1</v>
-      </c>
-      <c r="N36" t="s">
+      <c r="M36" t="s">
+        <v>32</v>
+      </c>
+      <c r="N36">
+        <v>1</v>
+      </c>
+      <c r="O36" t="s">
         <v>30</v>
       </c>
-      <c r="O36">
-        <v>0</v>
-      </c>
       <c r="P36">
-        <v>0.9852281360342515</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="b">
         <v>0</v>
@@ -3057,29 +3057,29 @@
       <c r="H37">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I37" t="s">
-        <v>15</v>
+      <c r="I37">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J37" t="s">
+        <v>8</v>
+      </c>
+      <c r="K37" t="s">
         <v>28</v>
       </c>
-      <c r="K37">
+      <c r="L37">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L37" t="s">
+      <c r="M37" t="s">
         <v>26</v>
       </c>
-      <c r="M37">
+      <c r="N37">
         <v>0.2857142857142857</v>
       </c>
-      <c r="N37" t="s">
+      <c r="O37" t="s">
         <v>30</v>
       </c>
-      <c r="O37">
-        <v>0</v>
-      </c>
       <c r="P37">
-        <v>0.5916727785823273</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="b">
         <v>1</v>
@@ -3128,29 +3128,29 @@
       <c r="H38">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I38" t="s">
-        <v>15</v>
+      <c r="I38">
+        <v>0.863120568566631</v>
       </c>
       <c r="J38" t="s">
+        <v>8</v>
+      </c>
+      <c r="K38" t="s">
         <v>26</v>
       </c>
-      <c r="K38">
+      <c r="L38">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L38" t="s">
+      <c r="M38" t="s">
         <v>33</v>
       </c>
-      <c r="M38">
+      <c r="N38">
         <v>0.8571428571428571</v>
       </c>
-      <c r="N38" t="s">
+      <c r="O38" t="s">
         <v>30</v>
       </c>
-      <c r="O38">
-        <v>0</v>
-      </c>
       <c r="P38">
-        <v>0.863120568566631</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="b">
         <v>0</v>
@@ -3199,29 +3199,29 @@
       <c r="H39">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I39" t="s">
-        <v>15</v>
+      <c r="I39">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J39" t="s">
+        <v>8</v>
+      </c>
+      <c r="K39" t="s">
         <v>29</v>
       </c>
-      <c r="K39">
+      <c r="L39">
         <v>0.5714285714285714</v>
       </c>
-      <c r="L39" t="s">
-        <v>32</v>
-      </c>
-      <c r="M39">
-        <v>1</v>
-      </c>
-      <c r="N39" t="s">
+      <c r="M39" t="s">
+        <v>32</v>
+      </c>
+      <c r="N39">
+        <v>1</v>
+      </c>
+      <c r="O39" t="s">
         <v>26</v>
       </c>
-      <c r="O39">
+      <c r="P39">
         <v>0.2857142857142857</v>
-      </c>
-      <c r="P39">
-        <v>0.9852281360342515</v>
       </c>
       <c r="Q39" t="b">
         <v>0</v>
@@ -3270,29 +3270,29 @@
       <c r="H40">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I40" t="s">
-        <v>15</v>
+      <c r="I40">
+        <v>0.863120568566631</v>
       </c>
       <c r="J40" t="s">
+        <v>8</v>
+      </c>
+      <c r="K40" t="s">
         <v>26</v>
       </c>
-      <c r="K40">
+      <c r="L40">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L40" t="s">
+      <c r="M40" t="s">
         <v>28</v>
       </c>
-      <c r="M40">
+      <c r="N40">
         <v>0.1428571428571428</v>
       </c>
-      <c r="N40" t="s">
+      <c r="O40" t="s">
         <v>30</v>
       </c>
-      <c r="O40">
-        <v>0</v>
-      </c>
       <c r="P40">
-        <v>0.863120568566631</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="b">
         <v>0</v>
@@ -3341,29 +3341,29 @@
       <c r="H41">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I41" t="s">
-        <v>15</v>
+      <c r="I41">
+        <v>0.863120568566631</v>
       </c>
       <c r="J41" t="s">
+        <v>8</v>
+      </c>
+      <c r="K41" t="s">
         <v>26</v>
       </c>
-      <c r="K41">
+      <c r="L41">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L41" t="s">
-        <v>32</v>
-      </c>
-      <c r="M41">
-        <v>1</v>
-      </c>
-      <c r="N41" t="s">
+      <c r="M41" t="s">
+        <v>32</v>
+      </c>
+      <c r="N41">
+        <v>1</v>
+      </c>
+      <c r="O41" t="s">
         <v>27</v>
       </c>
-      <c r="O41">
+      <c r="P41">
         <v>0.4285714285714285</v>
-      </c>
-      <c r="P41">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q41" t="b">
         <v>0</v>
@@ -3412,29 +3412,29 @@
       <c r="H42">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I42" t="s">
-        <v>15</v>
+      <c r="I42">
+        <v>0</v>
       </c>
       <c r="J42" t="s">
+        <v>8</v>
+      </c>
+      <c r="K42" t="s">
         <v>30</v>
       </c>
-      <c r="K42">
-        <v>0</v>
-      </c>
-      <c r="L42" t="s">
-        <v>32</v>
-      </c>
-      <c r="M42">
-        <v>1</v>
-      </c>
-      <c r="N42" t="s">
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42" t="s">
+        <v>32</v>
+      </c>
+      <c r="N42">
+        <v>1</v>
+      </c>
+      <c r="O42" t="s">
         <v>31</v>
       </c>
-      <c r="O42">
+      <c r="P42">
         <v>0.7142857142857143</v>
-      </c>
-      <c r="P42">
-        <v>0</v>
       </c>
       <c r="Q42" t="b">
         <v>0</v>
@@ -3483,29 +3483,29 @@
       <c r="H43">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I43" t="s">
-        <v>15</v>
+      <c r="I43">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J43" t="s">
+        <v>8</v>
+      </c>
+      <c r="K43" t="s">
         <v>27</v>
       </c>
-      <c r="K43">
+      <c r="L43">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L43" t="s">
+      <c r="M43" t="s">
         <v>33</v>
       </c>
-      <c r="M43">
+      <c r="N43">
         <v>0.8571428571428571</v>
       </c>
-      <c r="N43" t="s">
+      <c r="O43" t="s">
         <v>28</v>
       </c>
-      <c r="O43">
+      <c r="P43">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P43">
-        <v>0.9852281360342515</v>
       </c>
       <c r="Q43" t="b">
         <v>0</v>
@@ -3554,29 +3554,29 @@
       <c r="H44">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I44" t="s">
-        <v>15</v>
+      <c r="I44">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J44" t="s">
+        <v>8</v>
+      </c>
+      <c r="K44" t="s">
         <v>28</v>
       </c>
-      <c r="K44">
+      <c r="L44">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L44" t="s">
-        <v>32</v>
-      </c>
-      <c r="M44">
-        <v>1</v>
-      </c>
-      <c r="N44" t="s">
+      <c r="M44" t="s">
+        <v>32</v>
+      </c>
+      <c r="N44">
+        <v>1</v>
+      </c>
+      <c r="O44" t="s">
         <v>31</v>
       </c>
-      <c r="O44">
+      <c r="P44">
         <v>0.7142857142857143</v>
-      </c>
-      <c r="P44">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q44" t="b">
         <v>1</v>
@@ -3625,29 +3625,29 @@
       <c r="H45">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I45" t="s">
-        <v>15</v>
+      <c r="I45">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J45" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" t="s">
         <v>28</v>
       </c>
-      <c r="K45">
+      <c r="L45">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L45" t="s">
-        <v>32</v>
-      </c>
-      <c r="M45">
-        <v>1</v>
-      </c>
-      <c r="N45" t="s">
+      <c r="M45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N45">
+        <v>1</v>
+      </c>
+      <c r="O45" t="s">
         <v>33</v>
       </c>
-      <c r="O45">
+      <c r="P45">
         <v>0.8571428571428571</v>
-      </c>
-      <c r="P45">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q45" t="b">
         <v>1</v>
@@ -3696,29 +3696,29 @@
       <c r="H46">
         <v>0.863120568566631</v>
       </c>
-      <c r="I46" t="s">
-        <v>15</v>
+      <c r="I46">
+        <v>0.863120568566631</v>
       </c>
       <c r="J46" t="s">
+        <v>8</v>
+      </c>
+      <c r="K46" t="s">
         <v>26</v>
       </c>
-      <c r="K46">
+      <c r="L46">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L46" t="s">
+      <c r="M46" t="s">
         <v>27</v>
       </c>
-      <c r="M46">
+      <c r="N46">
         <v>0.4285714285714285</v>
       </c>
-      <c r="N46" t="s">
+      <c r="O46" t="s">
         <v>30</v>
       </c>
-      <c r="O46">
-        <v>0</v>
-      </c>
       <c r="P46">
-        <v>0.863120568566631</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="b">
         <v>1</v>
@@ -3767,29 +3767,29 @@
       <c r="H47">
         <v>0.863120568566631</v>
       </c>
-      <c r="I47" t="s">
-        <v>15</v>
+      <c r="I47">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J47" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" t="s">
         <v>27</v>
       </c>
-      <c r="K47">
+      <c r="L47">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L47" t="s">
-        <v>32</v>
-      </c>
-      <c r="M47">
-        <v>1</v>
-      </c>
-      <c r="N47" t="s">
+      <c r="M47" t="s">
+        <v>32</v>
+      </c>
+      <c r="N47">
+        <v>1</v>
+      </c>
+      <c r="O47" t="s">
         <v>29</v>
       </c>
-      <c r="O47">
+      <c r="P47">
         <v>0.5714285714285714</v>
-      </c>
-      <c r="P47">
-        <v>0.9852281360342515</v>
       </c>
       <c r="Q47" t="b">
         <v>0</v>
@@ -3838,29 +3838,29 @@
       <c r="H48">
         <v>0.863120568566631</v>
       </c>
-      <c r="I48" t="s">
-        <v>15</v>
+      <c r="I48">
+        <v>0.863120568566631</v>
       </c>
       <c r="J48" t="s">
+        <v>8</v>
+      </c>
+      <c r="K48" t="s">
         <v>26</v>
       </c>
-      <c r="K48">
+      <c r="L48">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L48" t="s">
-        <v>32</v>
-      </c>
-      <c r="M48">
-        <v>1</v>
-      </c>
-      <c r="N48" t="s">
+      <c r="M48" t="s">
+        <v>32</v>
+      </c>
+      <c r="N48">
+        <v>1</v>
+      </c>
+      <c r="O48" t="s">
         <v>27</v>
       </c>
-      <c r="O48">
+      <c r="P48">
         <v>0.4285714285714285</v>
-      </c>
-      <c r="P48">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q48" t="b">
         <v>1</v>
@@ -3909,29 +3909,29 @@
       <c r="H49">
         <v>0.863120568566631</v>
       </c>
-      <c r="I49" t="s">
-        <v>15</v>
+      <c r="I49">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J49" t="s">
+        <v>8</v>
+      </c>
+      <c r="K49" t="s">
         <v>28</v>
       </c>
-      <c r="K49">
+      <c r="L49">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L49" t="s">
-        <v>32</v>
-      </c>
-      <c r="M49">
-        <v>1</v>
-      </c>
-      <c r="N49" t="s">
+      <c r="M49" t="s">
+        <v>32</v>
+      </c>
+      <c r="N49">
+        <v>1</v>
+      </c>
+      <c r="O49" t="s">
         <v>33</v>
       </c>
-      <c r="O49">
+      <c r="P49">
         <v>0.8571428571428571</v>
-      </c>
-      <c r="P49">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q49" t="b">
         <v>1</v>
@@ -3980,29 +3980,29 @@
       <c r="H50">
         <v>0.863120568566631</v>
       </c>
-      <c r="I50" t="s">
-        <v>15</v>
+      <c r="I50">
+        <v>0.863120568566631</v>
       </c>
       <c r="J50" t="s">
+        <v>8</v>
+      </c>
+      <c r="K50" t="s">
         <v>26</v>
       </c>
-      <c r="K50">
+      <c r="L50">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L50" t="s">
-        <v>32</v>
-      </c>
-      <c r="M50">
-        <v>1</v>
-      </c>
-      <c r="N50" t="s">
+      <c r="M50" t="s">
+        <v>32</v>
+      </c>
+      <c r="N50">
+        <v>1</v>
+      </c>
+      <c r="O50" t="s">
         <v>31</v>
       </c>
-      <c r="O50">
+      <c r="P50">
         <v>0.7142857142857143</v>
-      </c>
-      <c r="P50">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q50" t="b">
         <v>1</v>
@@ -4051,29 +4051,29 @@
       <c r="H51">
         <v>0.863120568566631</v>
       </c>
-      <c r="I51" t="s">
-        <v>15</v>
+      <c r="I51">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J51" t="s">
+        <v>8</v>
+      </c>
+      <c r="K51" t="s">
         <v>28</v>
       </c>
-      <c r="K51">
+      <c r="L51">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L51" t="s">
-        <v>32</v>
-      </c>
-      <c r="M51">
-        <v>1</v>
-      </c>
-      <c r="N51" t="s">
+      <c r="M51" t="s">
+        <v>32</v>
+      </c>
+      <c r="N51">
+        <v>1</v>
+      </c>
+      <c r="O51" t="s">
         <v>31</v>
       </c>
-      <c r="O51">
+      <c r="P51">
         <v>0.7142857142857143</v>
-      </c>
-      <c r="P51">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q51" t="b">
         <v>1</v>
@@ -4122,29 +4122,29 @@
       <c r="H52">
         <v>0.863120568566631</v>
       </c>
-      <c r="I52" t="s">
-        <v>15</v>
+      <c r="I52">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J52" t="s">
+        <v>8</v>
+      </c>
+      <c r="K52" t="s">
         <v>29</v>
       </c>
-      <c r="K52">
+      <c r="L52">
         <v>0.5714285714285714</v>
       </c>
-      <c r="L52" t="s">
+      <c r="M52" t="s">
         <v>26</v>
       </c>
-      <c r="M52">
+      <c r="N52">
         <v>0.2857142857142857</v>
       </c>
-      <c r="N52" t="s">
+      <c r="O52" t="s">
         <v>30</v>
       </c>
-      <c r="O52">
-        <v>0</v>
-      </c>
       <c r="P52">
-        <v>0.9852281360342515</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="b">
         <v>0</v>
@@ -4193,29 +4193,29 @@
       <c r="H53">
         <v>0.863120568566631</v>
       </c>
-      <c r="I53" t="s">
-        <v>15</v>
+      <c r="I53">
+        <v>0.863120568566631</v>
       </c>
       <c r="J53" t="s">
+        <v>8</v>
+      </c>
+      <c r="K53" t="s">
         <v>26</v>
       </c>
-      <c r="K53">
+      <c r="L53">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L53" t="s">
+      <c r="M53" t="s">
         <v>26</v>
       </c>
-      <c r="M53">
+      <c r="N53">
         <v>0.2857142857142857</v>
       </c>
-      <c r="N53" t="s">
+      <c r="O53" t="s">
         <v>28</v>
       </c>
-      <c r="O53">
+      <c r="P53">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P53">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q53" t="b">
         <v>1</v>
@@ -4264,29 +4264,29 @@
       <c r="H54">
         <v>0.863120568566631</v>
       </c>
-      <c r="I54" t="s">
-        <v>15</v>
+      <c r="I54">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J54" t="s">
+        <v>8</v>
+      </c>
+      <c r="K54" t="s">
         <v>29</v>
       </c>
-      <c r="K54">
+      <c r="L54">
         <v>0.5714285714285714</v>
       </c>
-      <c r="L54" t="s">
+      <c r="M54" t="s">
         <v>29</v>
       </c>
-      <c r="M54">
+      <c r="N54">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N54" t="s">
+      <c r="O54" t="s">
         <v>30</v>
       </c>
-      <c r="O54">
-        <v>0</v>
-      </c>
       <c r="P54">
-        <v>0.9852281360342515</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="b">
         <v>0</v>
@@ -4335,29 +4335,29 @@
       <c r="H55">
         <v>0.863120568566631</v>
       </c>
-      <c r="I55" t="s">
-        <v>15</v>
+      <c r="I55">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J55" t="s">
+        <v>8</v>
+      </c>
+      <c r="K55" t="s">
         <v>28</v>
       </c>
-      <c r="K55">
+      <c r="L55">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L55" t="s">
-        <v>32</v>
-      </c>
-      <c r="M55">
-        <v>1</v>
-      </c>
-      <c r="N55" t="s">
+      <c r="M55" t="s">
+        <v>32</v>
+      </c>
+      <c r="N55">
+        <v>1</v>
+      </c>
+      <c r="O55" t="s">
         <v>26</v>
       </c>
-      <c r="O55">
+      <c r="P55">
         <v>0.2857142857142857</v>
-      </c>
-      <c r="P55">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q55" t="b">
         <v>1</v>
@@ -4406,29 +4406,29 @@
       <c r="H56">
         <v>0.863120568566631</v>
       </c>
-      <c r="I56" t="s">
-        <v>15</v>
+      <c r="I56">
+        <v>0</v>
       </c>
       <c r="J56" t="s">
+        <v>8</v>
+      </c>
+      <c r="K56" t="s">
         <v>30</v>
       </c>
-      <c r="K56">
-        <v>0</v>
-      </c>
-      <c r="L56" t="s">
-        <v>32</v>
-      </c>
-      <c r="M56">
-        <v>1</v>
-      </c>
-      <c r="N56" t="s">
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56" t="s">
+        <v>32</v>
+      </c>
+      <c r="N56">
+        <v>1</v>
+      </c>
+      <c r="O56" t="s">
         <v>26</v>
       </c>
-      <c r="O56">
+      <c r="P56">
         <v>0.2857142857142857</v>
-      </c>
-      <c r="P56">
-        <v>0</v>
       </c>
       <c r="Q56" t="b">
         <v>0</v>
@@ -4477,29 +4477,29 @@
       <c r="H57">
         <v>0.863120568566631</v>
       </c>
-      <c r="I57" t="s">
-        <v>15</v>
+      <c r="I57">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J57" t="s">
+        <v>8</v>
+      </c>
+      <c r="K57" t="s">
         <v>27</v>
       </c>
-      <c r="K57">
+      <c r="L57">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L57" t="s">
-        <v>32</v>
-      </c>
-      <c r="M57">
-        <v>1</v>
-      </c>
-      <c r="N57" t="s">
+      <c r="M57" t="s">
+        <v>32</v>
+      </c>
+      <c r="N57">
+        <v>1</v>
+      </c>
+      <c r="O57" t="s">
         <v>28</v>
       </c>
-      <c r="O57">
+      <c r="P57">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P57">
-        <v>0.9852281360342515</v>
       </c>
       <c r="Q57" t="b">
         <v>0</v>
@@ -4548,29 +4548,29 @@
       <c r="H58">
         <v>0.863120568566631</v>
       </c>
-      <c r="I58" t="s">
-        <v>15</v>
+      <c r="I58">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J58" t="s">
+        <v>8</v>
+      </c>
+      <c r="K58" t="s">
         <v>28</v>
       </c>
-      <c r="K58">
+      <c r="L58">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L58" t="s">
-        <v>32</v>
-      </c>
-      <c r="M58">
-        <v>1</v>
-      </c>
-      <c r="N58" t="s">
+      <c r="M58" t="s">
+        <v>32</v>
+      </c>
+      <c r="N58">
+        <v>1</v>
+      </c>
+      <c r="O58" t="s">
         <v>28</v>
       </c>
-      <c r="O58">
+      <c r="P58">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P58">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q58" t="b">
         <v>1</v>
@@ -4619,29 +4619,29 @@
       <c r="H59">
         <v>0.863120568566631</v>
       </c>
-      <c r="I59" t="s">
-        <v>15</v>
+      <c r="I59">
+        <v>0</v>
       </c>
       <c r="J59" t="s">
+        <v>8</v>
+      </c>
+      <c r="K59" t="s">
         <v>30</v>
       </c>
-      <c r="K59">
-        <v>0</v>
-      </c>
-      <c r="L59" t="s">
-        <v>32</v>
-      </c>
-      <c r="M59">
-        <v>1</v>
-      </c>
-      <c r="N59" t="s">
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59" t="s">
+        <v>32</v>
+      </c>
+      <c r="N59">
+        <v>1</v>
+      </c>
+      <c r="O59" t="s">
         <v>26</v>
       </c>
-      <c r="O59">
+      <c r="P59">
         <v>0.2857142857142857</v>
-      </c>
-      <c r="P59">
-        <v>0</v>
       </c>
       <c r="Q59" t="b">
         <v>0</v>
@@ -4690,29 +4690,29 @@
       <c r="H60">
         <v>0.863120568566631</v>
       </c>
-      <c r="I60" t="s">
-        <v>15</v>
+      <c r="I60">
+        <v>0.863120568566631</v>
       </c>
       <c r="J60" t="s">
+        <v>8</v>
+      </c>
+      <c r="K60" t="s">
         <v>26</v>
       </c>
-      <c r="K60">
+      <c r="L60">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L60" t="s">
+      <c r="M60" t="s">
         <v>28</v>
       </c>
-      <c r="M60">
+      <c r="N60">
         <v>0.1428571428571428</v>
       </c>
-      <c r="N60" t="s">
+      <c r="O60" t="s">
         <v>30</v>
       </c>
-      <c r="O60">
-        <v>0</v>
-      </c>
       <c r="P60">
-        <v>0.863120568566631</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="b">
         <v>1</v>
@@ -4761,29 +4761,29 @@
       <c r="H61">
         <v>0.863120568566631</v>
       </c>
-      <c r="I61" t="s">
-        <v>15</v>
+      <c r="I61">
+        <v>0</v>
       </c>
       <c r="J61" t="s">
+        <v>8</v>
+      </c>
+      <c r="K61" t="s">
         <v>30</v>
       </c>
-      <c r="K61">
-        <v>0</v>
-      </c>
-      <c r="L61" t="s">
-        <v>32</v>
-      </c>
-      <c r="M61">
-        <v>1</v>
-      </c>
-      <c r="N61" t="s">
-        <v>32</v>
-      </c>
-      <c r="O61">
-        <v>1</v>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61" t="s">
+        <v>32</v>
+      </c>
+      <c r="N61">
+        <v>1</v>
+      </c>
+      <c r="O61" t="s">
+        <v>32</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q61" t="b">
         <v>0</v>
@@ -4832,29 +4832,29 @@
       <c r="H62">
         <v>0.863120568566631</v>
       </c>
-      <c r="I62" t="s">
-        <v>15</v>
+      <c r="I62">
+        <v>0.863120568566631</v>
       </c>
       <c r="J62" t="s">
+        <v>8</v>
+      </c>
+      <c r="K62" t="s">
         <v>26</v>
       </c>
-      <c r="K62">
+      <c r="L62">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L62" t="s">
+      <c r="M62" t="s">
         <v>31</v>
       </c>
-      <c r="M62">
+      <c r="N62">
         <v>0.7142857142857143</v>
       </c>
-      <c r="N62" t="s">
+      <c r="O62" t="s">
         <v>26</v>
       </c>
-      <c r="O62">
+      <c r="P62">
         <v>0.2857142857142857</v>
-      </c>
-      <c r="P62">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q62" t="b">
         <v>1</v>
@@ -4903,29 +4903,29 @@
       <c r="H63">
         <v>0.863120568566631</v>
       </c>
-      <c r="I63" t="s">
-        <v>15</v>
+      <c r="I63">
+        <v>0.863120568566631</v>
       </c>
       <c r="J63" t="s">
+        <v>8</v>
+      </c>
+      <c r="K63" t="s">
         <v>26</v>
       </c>
-      <c r="K63">
+      <c r="L63">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L63" t="s">
-        <v>32</v>
-      </c>
-      <c r="M63">
-        <v>1</v>
-      </c>
-      <c r="N63" t="s">
+      <c r="M63" t="s">
+        <v>32</v>
+      </c>
+      <c r="N63">
+        <v>1</v>
+      </c>
+      <c r="O63" t="s">
         <v>26</v>
       </c>
-      <c r="O63">
+      <c r="P63">
         <v>0.2857142857142857</v>
-      </c>
-      <c r="P63">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q63" t="b">
         <v>1</v>
@@ -4974,29 +4974,29 @@
       <c r="H64">
         <v>0.863120568566631</v>
       </c>
-      <c r="I64" t="s">
-        <v>15</v>
+      <c r="I64">
+        <v>0.863120568566631</v>
       </c>
       <c r="J64" t="s">
+        <v>8</v>
+      </c>
+      <c r="K64" t="s">
         <v>26</v>
       </c>
-      <c r="K64">
+      <c r="L64">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L64" t="s">
-        <v>32</v>
-      </c>
-      <c r="M64">
-        <v>1</v>
-      </c>
-      <c r="N64" t="s">
+      <c r="M64" t="s">
+        <v>32</v>
+      </c>
+      <c r="N64">
+        <v>1</v>
+      </c>
+      <c r="O64" t="s">
         <v>31</v>
       </c>
-      <c r="O64">
+      <c r="P64">
         <v>0.7142857142857143</v>
-      </c>
-      <c r="P64">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q64" t="b">
         <v>1</v>
@@ -5045,29 +5045,29 @@
       <c r="H65">
         <v>0.863120568566631</v>
       </c>
-      <c r="I65" t="s">
-        <v>15</v>
+      <c r="I65">
+        <v>0.863120568566631</v>
       </c>
       <c r="J65" t="s">
+        <v>8</v>
+      </c>
+      <c r="K65" t="s">
         <v>26</v>
       </c>
-      <c r="K65">
+      <c r="L65">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L65" t="s">
-        <v>32</v>
-      </c>
-      <c r="M65">
-        <v>1</v>
-      </c>
-      <c r="N65" t="s">
+      <c r="M65" t="s">
+        <v>32</v>
+      </c>
+      <c r="N65">
+        <v>1</v>
+      </c>
+      <c r="O65" t="s">
         <v>29</v>
       </c>
-      <c r="O65">
+      <c r="P65">
         <v>0.5714285714285714</v>
-      </c>
-      <c r="P65">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q65" t="b">
         <v>1</v>
@@ -5116,29 +5116,29 @@
       <c r="H66">
         <v>0.863120568566631</v>
       </c>
-      <c r="I66" t="s">
-        <v>15</v>
+      <c r="I66">
+        <v>0.863120568566631</v>
       </c>
       <c r="J66" t="s">
+        <v>8</v>
+      </c>
+      <c r="K66" t="s">
         <v>26</v>
       </c>
-      <c r="K66">
+      <c r="L66">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L66" t="s">
+      <c r="M66" t="s">
         <v>28</v>
       </c>
-      <c r="M66">
+      <c r="N66">
         <v>0.1428571428571428</v>
       </c>
-      <c r="N66" t="s">
+      <c r="O66" t="s">
         <v>30</v>
       </c>
-      <c r="O66">
-        <v>0</v>
-      </c>
       <c r="P66">
-        <v>0.863120568566631</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="b">
         <v>1</v>
@@ -5187,29 +5187,29 @@
       <c r="H67">
         <v>0.863120568566631</v>
       </c>
-      <c r="I67" t="s">
-        <v>15</v>
+      <c r="I67">
+        <v>0.863120568566631</v>
       </c>
       <c r="J67" t="s">
+        <v>8</v>
+      </c>
+      <c r="K67" t="s">
         <v>26</v>
       </c>
-      <c r="K67">
+      <c r="L67">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L67" t="s">
-        <v>32</v>
-      </c>
-      <c r="M67">
-        <v>1</v>
-      </c>
-      <c r="N67" t="s">
+      <c r="M67" t="s">
+        <v>32</v>
+      </c>
+      <c r="N67">
+        <v>1</v>
+      </c>
+      <c r="O67" t="s">
         <v>28</v>
       </c>
-      <c r="O67">
+      <c r="P67">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P67">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q67" t="b">
         <v>1</v>
@@ -5258,29 +5258,29 @@
       <c r="H68">
         <v>0.863120568566631</v>
       </c>
-      <c r="I68" t="s">
-        <v>15</v>
+      <c r="I68">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J68" t="s">
+        <v>8</v>
+      </c>
+      <c r="K68" t="s">
         <v>28</v>
       </c>
-      <c r="K68">
+      <c r="L68">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L68" t="s">
-        <v>32</v>
-      </c>
-      <c r="M68">
-        <v>1</v>
-      </c>
-      <c r="N68" t="s">
+      <c r="M68" t="s">
+        <v>32</v>
+      </c>
+      <c r="N68">
+        <v>1</v>
+      </c>
+      <c r="O68" t="s">
         <v>28</v>
       </c>
-      <c r="O68">
+      <c r="P68">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P68">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q68" t="b">
         <v>1</v>
@@ -5329,29 +5329,29 @@
       <c r="H69">
         <v>0.863120568566631</v>
       </c>
-      <c r="I69" t="s">
-        <v>15</v>
+      <c r="I69">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J69" t="s">
+        <v>8</v>
+      </c>
+      <c r="K69" t="s">
         <v>28</v>
       </c>
-      <c r="K69">
+      <c r="L69">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L69" t="s">
+      <c r="M69" t="s">
         <v>28</v>
       </c>
-      <c r="M69">
+      <c r="N69">
         <v>0.1428571428571428</v>
       </c>
-      <c r="N69" t="s">
+      <c r="O69" t="s">
         <v>30</v>
       </c>
-      <c r="O69">
-        <v>0</v>
-      </c>
       <c r="P69">
-        <v>0.5916727785823273</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="b">
         <v>1</v>
@@ -5400,29 +5400,29 @@
       <c r="H70">
         <v>0.863120568566631</v>
       </c>
-      <c r="I70" t="s">
-        <v>15</v>
+      <c r="I70">
+        <v>0</v>
       </c>
       <c r="J70" t="s">
+        <v>8</v>
+      </c>
+      <c r="K70" t="s">
         <v>30</v>
       </c>
-      <c r="K70">
-        <v>0</v>
-      </c>
-      <c r="L70" t="s">
-        <v>32</v>
-      </c>
-      <c r="M70">
-        <v>1</v>
-      </c>
-      <c r="N70" t="s">
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70" t="s">
+        <v>32</v>
+      </c>
+      <c r="N70">
+        <v>1</v>
+      </c>
+      <c r="O70" t="s">
         <v>27</v>
       </c>
-      <c r="O70">
+      <c r="P70">
         <v>0.4285714285714285</v>
-      </c>
-      <c r="P70">
-        <v>0</v>
       </c>
       <c r="Q70" t="b">
         <v>0</v>
@@ -5471,29 +5471,29 @@
       <c r="H71">
         <v>0.863120568566631</v>
       </c>
-      <c r="I71" t="s">
-        <v>15</v>
+      <c r="I71">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J71" t="s">
+        <v>8</v>
+      </c>
+      <c r="K71" t="s">
         <v>27</v>
       </c>
-      <c r="K71">
+      <c r="L71">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L71" t="s">
-        <v>32</v>
-      </c>
-      <c r="M71">
-        <v>1</v>
-      </c>
-      <c r="N71" t="s">
+      <c r="M71" t="s">
+        <v>32</v>
+      </c>
+      <c r="N71">
+        <v>1</v>
+      </c>
+      <c r="O71" t="s">
         <v>28</v>
       </c>
-      <c r="O71">
+      <c r="P71">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P71">
-        <v>0.9852281360342515</v>
       </c>
       <c r="Q71" t="b">
         <v>0</v>
@@ -5542,29 +5542,29 @@
       <c r="H72">
         <v>0.863120568566631</v>
       </c>
-      <c r="I72" t="s">
-        <v>15</v>
+      <c r="I72">
+        <v>0.863120568566631</v>
       </c>
       <c r="J72" t="s">
+        <v>8</v>
+      </c>
+      <c r="K72" t="s">
         <v>26</v>
       </c>
-      <c r="K72">
+      <c r="L72">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L72" t="s">
+      <c r="M72" t="s">
         <v>27</v>
       </c>
-      <c r="M72">
+      <c r="N72">
         <v>0.4285714285714285</v>
       </c>
-      <c r="N72" t="s">
+      <c r="O72" t="s">
         <v>30</v>
       </c>
-      <c r="O72">
-        <v>0</v>
-      </c>
       <c r="P72">
-        <v>0.863120568566631</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="b">
         <v>1</v>
@@ -5613,29 +5613,29 @@
       <c r="H73">
         <v>0.863120568566631</v>
       </c>
-      <c r="I73" t="s">
-        <v>15</v>
+      <c r="I73">
+        <v>0.863120568566631</v>
       </c>
       <c r="J73" t="s">
+        <v>8</v>
+      </c>
+      <c r="K73" t="s">
         <v>26</v>
       </c>
-      <c r="K73">
+      <c r="L73">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L73" t="s">
-        <v>32</v>
-      </c>
-      <c r="M73">
-        <v>1</v>
-      </c>
-      <c r="N73" t="s">
+      <c r="M73" t="s">
+        <v>32</v>
+      </c>
+      <c r="N73">
+        <v>1</v>
+      </c>
+      <c r="O73" t="s">
         <v>27</v>
       </c>
-      <c r="O73">
+      <c r="P73">
         <v>0.4285714285714285</v>
-      </c>
-      <c r="P73">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q73" t="b">
         <v>1</v>
@@ -5684,29 +5684,29 @@
       <c r="H74">
         <v>0.863120568566631</v>
       </c>
-      <c r="I74" t="s">
-        <v>15</v>
+      <c r="I74">
+        <v>0.863120568566631</v>
       </c>
       <c r="J74" t="s">
+        <v>8</v>
+      </c>
+      <c r="K74" t="s">
         <v>31</v>
       </c>
-      <c r="K74">
+      <c r="L74">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L74" t="s">
-        <v>32</v>
-      </c>
-      <c r="M74">
-        <v>1</v>
-      </c>
-      <c r="N74" t="s">
+      <c r="M74" t="s">
+        <v>32</v>
+      </c>
+      <c r="N74">
+        <v>1</v>
+      </c>
+      <c r="O74" t="s">
         <v>30</v>
       </c>
-      <c r="O74">
-        <v>0</v>
-      </c>
       <c r="P74">
-        <v>0.863120568566631</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="b">
         <v>1</v>
@@ -5755,29 +5755,29 @@
       <c r="H75">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I75" t="s">
-        <v>15</v>
+      <c r="I75">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J75" t="s">
+        <v>8</v>
+      </c>
+      <c r="K75" t="s">
         <v>28</v>
       </c>
-      <c r="K75">
+      <c r="L75">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L75" t="s">
-        <v>32</v>
-      </c>
-      <c r="M75">
-        <v>1</v>
-      </c>
-      <c r="N75" t="s">
+      <c r="M75" t="s">
+        <v>32</v>
+      </c>
+      <c r="N75">
+        <v>1</v>
+      </c>
+      <c r="O75" t="s">
         <v>29</v>
       </c>
-      <c r="O75">
+      <c r="P75">
         <v>0.5714285714285714</v>
-      </c>
-      <c r="P75">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q75" t="b">
         <v>1</v>
@@ -5826,29 +5826,29 @@
       <c r="H76">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I76" t="s">
-        <v>15</v>
+      <c r="I76">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J76" t="s">
+        <v>8</v>
+      </c>
+      <c r="K76" t="s">
         <v>28</v>
       </c>
-      <c r="K76">
+      <c r="L76">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L76" t="s">
-        <v>32</v>
-      </c>
-      <c r="M76">
-        <v>1</v>
-      </c>
-      <c r="N76" t="s">
+      <c r="M76" t="s">
+        <v>32</v>
+      </c>
+      <c r="N76">
+        <v>1</v>
+      </c>
+      <c r="O76" t="s">
         <v>28</v>
       </c>
-      <c r="O76">
+      <c r="P76">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P76">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q76" t="b">
         <v>1</v>
@@ -5897,29 +5897,29 @@
       <c r="H77">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I77" t="s">
-        <v>15</v>
+      <c r="I77">
+        <v>0.863120568566631</v>
       </c>
       <c r="J77" t="s">
+        <v>8</v>
+      </c>
+      <c r="K77" t="s">
         <v>26</v>
       </c>
-      <c r="K77">
+      <c r="L77">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L77" t="s">
-        <v>32</v>
-      </c>
-      <c r="M77">
-        <v>1</v>
-      </c>
-      <c r="N77" t="s">
+      <c r="M77" t="s">
+        <v>32</v>
+      </c>
+      <c r="N77">
+        <v>1</v>
+      </c>
+      <c r="O77" t="s">
         <v>27</v>
       </c>
-      <c r="O77">
+      <c r="P77">
         <v>0.4285714285714285</v>
-      </c>
-      <c r="P77">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q77" t="b">
         <v>0</v>
@@ -5968,29 +5968,29 @@
       <c r="H78">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I78" t="s">
-        <v>15</v>
+      <c r="I78">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J78" t="s">
+        <v>8</v>
+      </c>
+      <c r="K78" t="s">
         <v>28</v>
       </c>
-      <c r="K78">
+      <c r="L78">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L78" t="s">
-        <v>32</v>
-      </c>
-      <c r="M78">
-        <v>1</v>
-      </c>
-      <c r="N78" t="s">
+      <c r="M78" t="s">
+        <v>32</v>
+      </c>
+      <c r="N78">
+        <v>1</v>
+      </c>
+      <c r="O78" t="s">
         <v>26</v>
       </c>
-      <c r="O78">
+      <c r="P78">
         <v>0.2857142857142857</v>
-      </c>
-      <c r="P78">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q78" t="b">
         <v>1</v>
@@ -6039,29 +6039,29 @@
       <c r="H79">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I79" t="s">
-        <v>15</v>
+      <c r="I79">
+        <v>0.863120568566631</v>
       </c>
       <c r="J79" t="s">
+        <v>8</v>
+      </c>
+      <c r="K79" t="s">
         <v>26</v>
       </c>
-      <c r="K79">
+      <c r="L79">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L79" t="s">
-        <v>32</v>
-      </c>
-      <c r="M79">
-        <v>1</v>
-      </c>
-      <c r="N79" t="s">
+      <c r="M79" t="s">
+        <v>32</v>
+      </c>
+      <c r="N79">
+        <v>1</v>
+      </c>
+      <c r="O79" t="s">
         <v>26</v>
       </c>
-      <c r="O79">
+      <c r="P79">
         <v>0.2857142857142857</v>
-      </c>
-      <c r="P79">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q79" t="b">
         <v>0</v>
@@ -6110,29 +6110,29 @@
       <c r="H80">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I80" t="s">
-        <v>15</v>
+      <c r="I80">
+        <v>0</v>
       </c>
       <c r="J80" t="s">
+        <v>8</v>
+      </c>
+      <c r="K80" t="s">
         <v>30</v>
       </c>
-      <c r="K80">
-        <v>0</v>
-      </c>
-      <c r="L80" t="s">
-        <v>32</v>
-      </c>
-      <c r="M80">
-        <v>1</v>
-      </c>
-      <c r="N80" t="s">
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80" t="s">
+        <v>32</v>
+      </c>
+      <c r="N80">
+        <v>1</v>
+      </c>
+      <c r="O80" t="s">
         <v>26</v>
       </c>
-      <c r="O80">
+      <c r="P80">
         <v>0.2857142857142857</v>
-      </c>
-      <c r="P80">
-        <v>0</v>
       </c>
       <c r="Q80" t="b">
         <v>0</v>
@@ -6181,29 +6181,29 @@
       <c r="H81">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I81" t="s">
-        <v>15</v>
+      <c r="I81">
+        <v>0</v>
       </c>
       <c r="J81" t="s">
+        <v>8</v>
+      </c>
+      <c r="K81" t="s">
         <v>30</v>
       </c>
-      <c r="K81">
-        <v>0</v>
-      </c>
-      <c r="L81" t="s">
-        <v>32</v>
-      </c>
-      <c r="M81">
-        <v>1</v>
-      </c>
-      <c r="N81" t="s">
-        <v>32</v>
-      </c>
-      <c r="O81">
-        <v>1</v>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81" t="s">
+        <v>32</v>
+      </c>
+      <c r="N81">
+        <v>1</v>
+      </c>
+      <c r="O81" t="s">
+        <v>32</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q81" t="b">
         <v>0</v>
@@ -6252,29 +6252,29 @@
       <c r="H82">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I82" t="s">
-        <v>15</v>
+      <c r="I82">
+        <v>0.863120568566631</v>
       </c>
       <c r="J82" t="s">
+        <v>8</v>
+      </c>
+      <c r="K82" t="s">
         <v>26</v>
       </c>
-      <c r="K82">
+      <c r="L82">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L82" t="s">
+      <c r="M82" t="s">
         <v>30</v>
       </c>
-      <c r="M82">
-        <v>0</v>
-      </c>
-      <c r="N82" t="s">
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82" t="s">
         <v>30</v>
       </c>
-      <c r="O82">
-        <v>0</v>
-      </c>
       <c r="P82">
-        <v>0.863120568566631</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="b">
         <v>0</v>
@@ -6323,29 +6323,29 @@
       <c r="H83">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I83" t="s">
-        <v>15</v>
+      <c r="I83">
+        <v>0.863120568566631</v>
       </c>
       <c r="J83" t="s">
+        <v>8</v>
+      </c>
+      <c r="K83" t="s">
         <v>26</v>
       </c>
-      <c r="K83">
+      <c r="L83">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L83" t="s">
+      <c r="M83" t="s">
         <v>33</v>
       </c>
-      <c r="M83">
+      <c r="N83">
         <v>0.8571428571428571</v>
       </c>
-      <c r="N83" t="s">
+      <c r="O83" t="s">
         <v>30</v>
       </c>
-      <c r="O83">
-        <v>0</v>
-      </c>
       <c r="P83">
-        <v>0.863120568566631</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="b">
         <v>0</v>
@@ -6394,29 +6394,29 @@
       <c r="H84">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I84" t="s">
-        <v>15</v>
+      <c r="I84">
+        <v>0.863120568566631</v>
       </c>
       <c r="J84" t="s">
+        <v>8</v>
+      </c>
+      <c r="K84" t="s">
         <v>26</v>
       </c>
-      <c r="K84">
+      <c r="L84">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L84" t="s">
-        <v>32</v>
-      </c>
-      <c r="M84">
-        <v>1</v>
-      </c>
-      <c r="N84" t="s">
+      <c r="M84" t="s">
+        <v>32</v>
+      </c>
+      <c r="N84">
+        <v>1</v>
+      </c>
+      <c r="O84" t="s">
         <v>31</v>
       </c>
-      <c r="O84">
+      <c r="P84">
         <v>0.7142857142857143</v>
-      </c>
-      <c r="P84">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q84" t="b">
         <v>0</v>
@@ -6465,29 +6465,29 @@
       <c r="H85">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I85" t="s">
-        <v>15</v>
+      <c r="I85">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J85" t="s">
+        <v>8</v>
+      </c>
+      <c r="K85" t="s">
         <v>28</v>
       </c>
-      <c r="K85">
+      <c r="L85">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L85" t="s">
+      <c r="M85" t="s">
         <v>28</v>
       </c>
-      <c r="M85">
+      <c r="N85">
         <v>0.1428571428571428</v>
       </c>
-      <c r="N85" t="s">
+      <c r="O85" t="s">
         <v>30</v>
       </c>
-      <c r="O85">
-        <v>0</v>
-      </c>
       <c r="P85">
-        <v>0.5916727785823273</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="b">
         <v>1</v>
@@ -6536,29 +6536,29 @@
       <c r="H86">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I86" t="s">
-        <v>15</v>
+      <c r="I86">
+        <v>0</v>
       </c>
       <c r="J86" t="s">
+        <v>8</v>
+      </c>
+      <c r="K86" t="s">
         <v>30</v>
       </c>
-      <c r="K86">
-        <v>0</v>
-      </c>
-      <c r="L86" t="s">
-        <v>32</v>
-      </c>
-      <c r="M86">
-        <v>1</v>
-      </c>
-      <c r="N86" t="s">
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86" t="s">
+        <v>32</v>
+      </c>
+      <c r="N86">
+        <v>1</v>
+      </c>
+      <c r="O86" t="s">
         <v>33</v>
       </c>
-      <c r="O86">
+      <c r="P86">
         <v>0.8571428571428571</v>
-      </c>
-      <c r="P86">
-        <v>0</v>
       </c>
       <c r="Q86" t="b">
         <v>0</v>
@@ -6607,29 +6607,29 @@
       <c r="H87">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I87" t="s">
-        <v>15</v>
+      <c r="I87">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J87" t="s">
+        <v>8</v>
+      </c>
+      <c r="K87" t="s">
         <v>27</v>
       </c>
-      <c r="K87">
+      <c r="L87">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L87" t="s">
+      <c r="M87" t="s">
         <v>30</v>
       </c>
-      <c r="M87">
-        <v>0</v>
-      </c>
-      <c r="N87" t="s">
+      <c r="N87">
+        <v>0</v>
+      </c>
+      <c r="O87" t="s">
         <v>30</v>
       </c>
-      <c r="O87">
-        <v>0</v>
-      </c>
       <c r="P87">
-        <v>0.9852281360342515</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="b">
         <v>0</v>
@@ -6678,29 +6678,29 @@
       <c r="H88">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I88" t="s">
-        <v>15</v>
+      <c r="I88">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J88" t="s">
+        <v>8</v>
+      </c>
+      <c r="K88" t="s">
         <v>28</v>
       </c>
-      <c r="K88">
+      <c r="L88">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L88" t="s">
-        <v>32</v>
-      </c>
-      <c r="M88">
-        <v>1</v>
-      </c>
-      <c r="N88" t="s">
+      <c r="M88" t="s">
+        <v>32</v>
+      </c>
+      <c r="N88">
+        <v>1</v>
+      </c>
+      <c r="O88" t="s">
         <v>30</v>
       </c>
-      <c r="O88">
-        <v>0</v>
-      </c>
       <c r="P88">
-        <v>0.5916727785823273</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="b">
         <v>1</v>
@@ -6749,29 +6749,29 @@
       <c r="H89">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I89" t="s">
-        <v>15</v>
+      <c r="I89">
+        <v>0</v>
       </c>
       <c r="J89" t="s">
+        <v>8</v>
+      </c>
+      <c r="K89" t="s">
         <v>30</v>
       </c>
-      <c r="K89">
-        <v>0</v>
-      </c>
-      <c r="L89" t="s">
-        <v>32</v>
-      </c>
-      <c r="M89">
-        <v>1</v>
-      </c>
-      <c r="N89" t="s">
-        <v>32</v>
-      </c>
-      <c r="O89">
-        <v>1</v>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89" t="s">
+        <v>32</v>
+      </c>
+      <c r="N89">
+        <v>1</v>
+      </c>
+      <c r="O89" t="s">
+        <v>32</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q89" t="b">
         <v>0</v>
@@ -6820,29 +6820,29 @@
       <c r="H90">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I90" t="s">
-        <v>15</v>
+      <c r="I90">
+        <v>0</v>
       </c>
       <c r="J90" t="s">
+        <v>8</v>
+      </c>
+      <c r="K90" t="s">
         <v>30</v>
       </c>
-      <c r="K90">
-        <v>0</v>
-      </c>
-      <c r="L90" t="s">
-        <v>32</v>
-      </c>
-      <c r="M90">
-        <v>1</v>
-      </c>
-      <c r="N90" t="s">
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90" t="s">
+        <v>32</v>
+      </c>
+      <c r="N90">
+        <v>1</v>
+      </c>
+      <c r="O90" t="s">
         <v>27</v>
       </c>
-      <c r="O90">
+      <c r="P90">
         <v>0.4285714285714285</v>
-      </c>
-      <c r="P90">
-        <v>0</v>
       </c>
       <c r="Q90" t="b">
         <v>0</v>
@@ -6891,29 +6891,29 @@
       <c r="H91">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I91" t="s">
-        <v>15</v>
+      <c r="I91">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J91" t="s">
+        <v>8</v>
+      </c>
+      <c r="K91" t="s">
         <v>28</v>
       </c>
-      <c r="K91">
+      <c r="L91">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L91" t="s">
+      <c r="M91" t="s">
         <v>29</v>
       </c>
-      <c r="M91">
+      <c r="N91">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N91" t="s">
+      <c r="O91" t="s">
         <v>30</v>
       </c>
-      <c r="O91">
-        <v>0</v>
-      </c>
       <c r="P91">
-        <v>0.5916727785823273</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="b">
         <v>1</v>
@@ -6962,29 +6962,29 @@
       <c r="H92">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I92" t="s">
-        <v>15</v>
+      <c r="I92">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J92" t="s">
+        <v>8</v>
+      </c>
+      <c r="K92" t="s">
         <v>28</v>
       </c>
-      <c r="K92">
+      <c r="L92">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L92" t="s">
-        <v>32</v>
-      </c>
-      <c r="M92">
-        <v>1</v>
-      </c>
-      <c r="N92" t="s">
+      <c r="M92" t="s">
+        <v>32</v>
+      </c>
+      <c r="N92">
+        <v>1</v>
+      </c>
+      <c r="O92" t="s">
         <v>33</v>
       </c>
-      <c r="O92">
+      <c r="P92">
         <v>0.8571428571428571</v>
-      </c>
-      <c r="P92">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q92" t="b">
         <v>1</v>
@@ -7033,29 +7033,29 @@
       <c r="H93">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I93" t="s">
-        <v>15</v>
+      <c r="I93">
+        <v>0</v>
       </c>
       <c r="J93" t="s">
+        <v>8</v>
+      </c>
+      <c r="K93" t="s">
         <v>30</v>
       </c>
-      <c r="K93">
-        <v>0</v>
-      </c>
-      <c r="L93" t="s">
-        <v>32</v>
-      </c>
-      <c r="M93">
-        <v>1</v>
-      </c>
-      <c r="N93" t="s">
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93" t="s">
+        <v>32</v>
+      </c>
+      <c r="N93">
+        <v>1</v>
+      </c>
+      <c r="O93" t="s">
         <v>27</v>
       </c>
-      <c r="O93">
+      <c r="P93">
         <v>0.4285714285714285</v>
-      </c>
-      <c r="P93">
-        <v>0</v>
       </c>
       <c r="Q93" t="b">
         <v>0</v>
@@ -7104,29 +7104,29 @@
       <c r="H94">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I94" t="s">
-        <v>15</v>
+      <c r="I94">
+        <v>0.863120568566631</v>
       </c>
       <c r="J94" t="s">
+        <v>8</v>
+      </c>
+      <c r="K94" t="s">
         <v>26</v>
       </c>
-      <c r="K94">
+      <c r="L94">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L94" t="s">
-        <v>32</v>
-      </c>
-      <c r="M94">
-        <v>1</v>
-      </c>
-      <c r="N94" t="s">
+      <c r="M94" t="s">
+        <v>32</v>
+      </c>
+      <c r="N94">
+        <v>1</v>
+      </c>
+      <c r="O94" t="s">
         <v>27</v>
       </c>
-      <c r="O94">
+      <c r="P94">
         <v>0.4285714285714285</v>
-      </c>
-      <c r="P94">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q94" t="b">
         <v>0</v>
@@ -7175,29 +7175,29 @@
       <c r="H95">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I95" t="s">
-        <v>15</v>
+      <c r="I95">
+        <v>0.863120568566631</v>
       </c>
       <c r="J95" t="s">
+        <v>8</v>
+      </c>
+      <c r="K95" t="s">
         <v>26</v>
       </c>
-      <c r="K95">
+      <c r="L95">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L95" t="s">
-        <v>32</v>
-      </c>
-      <c r="M95">
-        <v>1</v>
-      </c>
-      <c r="N95" t="s">
+      <c r="M95" t="s">
+        <v>32</v>
+      </c>
+      <c r="N95">
+        <v>1</v>
+      </c>
+      <c r="O95" t="s">
         <v>31</v>
       </c>
-      <c r="O95">
+      <c r="P95">
         <v>0.7142857142857143</v>
-      </c>
-      <c r="P95">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q95" t="b">
         <v>0</v>
@@ -7246,26 +7246,26 @@
       <c r="H96">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I96" t="s">
-        <v>15</v>
+      <c r="I96">
+        <v>0</v>
       </c>
       <c r="J96" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" t="s">
         <v>30</v>
       </c>
-      <c r="K96">
-        <v>0</v>
-      </c>
-      <c r="L96" t="s">
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96" t="s">
         <v>29</v>
       </c>
-      <c r="M96">
+      <c r="N96">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N96" t="s">
+      <c r="O96" t="s">
         <v>30</v>
-      </c>
-      <c r="O96">
-        <v>0</v>
       </c>
       <c r="P96">
         <v>0</v>
@@ -7317,29 +7317,29 @@
       <c r="H97">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I97" t="s">
-        <v>15</v>
+      <c r="I97">
+        <v>0.863120568566631</v>
       </c>
       <c r="J97" t="s">
+        <v>8</v>
+      </c>
+      <c r="K97" t="s">
         <v>26</v>
       </c>
-      <c r="K97">
+      <c r="L97">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L97" t="s">
-        <v>32</v>
-      </c>
-      <c r="M97">
-        <v>1</v>
-      </c>
-      <c r="N97" t="s">
+      <c r="M97" t="s">
+        <v>32</v>
+      </c>
+      <c r="N97">
+        <v>1</v>
+      </c>
+      <c r="O97" t="s">
         <v>28</v>
       </c>
-      <c r="O97">
+      <c r="P97">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P97">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q97" t="b">
         <v>0</v>
@@ -7388,29 +7388,29 @@
       <c r="H98">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I98" t="s">
-        <v>15</v>
+      <c r="I98">
+        <v>0</v>
       </c>
       <c r="J98" t="s">
+        <v>8</v>
+      </c>
+      <c r="K98" t="s">
         <v>30</v>
       </c>
-      <c r="K98">
-        <v>0</v>
-      </c>
-      <c r="L98" t="s">
-        <v>32</v>
-      </c>
-      <c r="M98">
-        <v>1</v>
-      </c>
-      <c r="N98" t="s">
-        <v>32</v>
-      </c>
-      <c r="O98">
-        <v>1</v>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98" t="s">
+        <v>32</v>
+      </c>
+      <c r="N98">
+        <v>1</v>
+      </c>
+      <c r="O98" t="s">
+        <v>32</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q98" t="b">
         <v>0</v>
@@ -7459,29 +7459,29 @@
       <c r="H99">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I99" t="s">
-        <v>15</v>
+      <c r="I99">
+        <v>0.863120568566631</v>
       </c>
       <c r="J99" t="s">
+        <v>8</v>
+      </c>
+      <c r="K99" t="s">
         <v>26</v>
       </c>
-      <c r="K99">
+      <c r="L99">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L99" t="s">
+      <c r="M99" t="s">
         <v>30</v>
       </c>
-      <c r="M99">
-        <v>0</v>
-      </c>
-      <c r="N99" t="s">
+      <c r="N99">
+        <v>0</v>
+      </c>
+      <c r="O99" t="s">
         <v>30</v>
       </c>
-      <c r="O99">
-        <v>0</v>
-      </c>
       <c r="P99">
-        <v>0.863120568566631</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="b">
         <v>0</v>
@@ -7530,29 +7530,29 @@
       <c r="H100">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I100" t="s">
-        <v>15</v>
+      <c r="I100">
+        <v>0</v>
       </c>
       <c r="J100" t="s">
+        <v>8</v>
+      </c>
+      <c r="K100" t="s">
         <v>30</v>
       </c>
-      <c r="K100">
-        <v>0</v>
-      </c>
-      <c r="L100" t="s">
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100" t="s">
         <v>29</v>
       </c>
-      <c r="M100">
+      <c r="N100">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N100" t="s">
+      <c r="O100" t="s">
         <v>28</v>
       </c>
-      <c r="O100">
+      <c r="P100">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P100">
-        <v>0</v>
       </c>
       <c r="Q100" t="b">
         <v>0</v>
@@ -7601,29 +7601,29 @@
       <c r="H101">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I101" t="s">
-        <v>15</v>
+      <c r="I101">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J101" t="s">
+        <v>8</v>
+      </c>
+      <c r="K101" t="s">
         <v>28</v>
       </c>
-      <c r="K101">
+      <c r="L101">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L101" t="s">
-        <v>32</v>
-      </c>
-      <c r="M101">
-        <v>1</v>
-      </c>
-      <c r="N101" t="s">
+      <c r="M101" t="s">
+        <v>32</v>
+      </c>
+      <c r="N101">
+        <v>1</v>
+      </c>
+      <c r="O101" t="s">
         <v>27</v>
       </c>
-      <c r="O101">
+      <c r="P101">
         <v>0.4285714285714285</v>
-      </c>
-      <c r="P101">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q101" t="b">
         <v>1</v>
@@ -7672,29 +7672,29 @@
       <c r="H102">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I102" t="s">
-        <v>15</v>
+      <c r="I102">
+        <v>0.863120568566631</v>
       </c>
       <c r="J102" t="s">
+        <v>8</v>
+      </c>
+      <c r="K102" t="s">
         <v>26</v>
       </c>
-      <c r="K102">
+      <c r="L102">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L102" t="s">
+      <c r="M102" t="s">
         <v>31</v>
       </c>
-      <c r="M102">
+      <c r="N102">
         <v>0.7142857142857143</v>
       </c>
-      <c r="N102" t="s">
+      <c r="O102" t="s">
         <v>30</v>
       </c>
-      <c r="O102">
-        <v>0</v>
-      </c>
       <c r="P102">
-        <v>0.863120568566631</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="b">
         <v>0</v>
@@ -7743,29 +7743,29 @@
       <c r="H103">
         <v>0.3550036671493964</v>
       </c>
-      <c r="I103" t="s">
-        <v>15</v>
+      <c r="I103">
+        <v>0</v>
       </c>
       <c r="J103" t="s">
+        <v>8</v>
+      </c>
+      <c r="K103" t="s">
         <v>30</v>
       </c>
-      <c r="K103">
-        <v>0</v>
-      </c>
-      <c r="L103" t="s">
-        <v>32</v>
-      </c>
-      <c r="M103">
-        <v>1</v>
-      </c>
-      <c r="N103" t="s">
-        <v>32</v>
-      </c>
-      <c r="O103">
-        <v>1</v>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103" t="s">
+        <v>32</v>
+      </c>
+      <c r="N103">
+        <v>1</v>
+      </c>
+      <c r="O103" t="s">
+        <v>32</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q103" t="b">
         <v>0</v>
@@ -7814,29 +7814,29 @@
       <c r="H104">
         <v>0.3550036671493964</v>
       </c>
-      <c r="I104" t="s">
-        <v>15</v>
+      <c r="I104">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J104" t="s">
+        <v>8</v>
+      </c>
+      <c r="K104" t="s">
         <v>28</v>
       </c>
-      <c r="K104">
+      <c r="L104">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L104" t="s">
+      <c r="M104" t="s">
         <v>26</v>
       </c>
-      <c r="M104">
+      <c r="N104">
         <v>0.2857142857142857</v>
       </c>
-      <c r="N104" t="s">
+      <c r="O104" t="s">
         <v>30</v>
       </c>
-      <c r="O104">
-        <v>0</v>
-      </c>
       <c r="P104">
-        <v>0.5916727785823273</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="b">
         <v>0</v>
@@ -7885,29 +7885,29 @@
       <c r="H105">
         <v>0.3550036671493964</v>
       </c>
-      <c r="I105" t="s">
-        <v>15</v>
+      <c r="I105">
+        <v>0.863120568566631</v>
       </c>
       <c r="J105" t="s">
+        <v>8</v>
+      </c>
+      <c r="K105" t="s">
         <v>26</v>
       </c>
-      <c r="K105">
+      <c r="L105">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L105" t="s">
-        <v>32</v>
-      </c>
-      <c r="M105">
-        <v>1</v>
-      </c>
-      <c r="N105" t="s">
+      <c r="M105" t="s">
+        <v>32</v>
+      </c>
+      <c r="N105">
+        <v>1</v>
+      </c>
+      <c r="O105" t="s">
         <v>28</v>
       </c>
-      <c r="O105">
+      <c r="P105">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P105">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q105" t="b">
         <v>0</v>
@@ -7956,29 +7956,29 @@
       <c r="H106">
         <v>0.3550036671493964</v>
       </c>
-      <c r="I106" t="s">
-        <v>15</v>
+      <c r="I106">
+        <v>0.863120568566631</v>
       </c>
       <c r="J106" t="s">
+        <v>8</v>
+      </c>
+      <c r="K106" t="s">
         <v>26</v>
       </c>
-      <c r="K106">
+      <c r="L106">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L106" t="s">
-        <v>32</v>
-      </c>
-      <c r="M106">
-        <v>1</v>
-      </c>
-      <c r="N106" t="s">
+      <c r="M106" t="s">
+        <v>32</v>
+      </c>
+      <c r="N106">
+        <v>1</v>
+      </c>
+      <c r="O106" t="s">
         <v>27</v>
       </c>
-      <c r="O106">
+      <c r="P106">
         <v>0.4285714285714285</v>
-      </c>
-      <c r="P106">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q106" t="b">
         <v>0</v>
@@ -8027,29 +8027,29 @@
       <c r="H107">
         <v>0.3550036671493964</v>
       </c>
-      <c r="I107" t="s">
-        <v>15</v>
+      <c r="I107">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J107" t="s">
+        <v>8</v>
+      </c>
+      <c r="K107" t="s">
         <v>28</v>
       </c>
-      <c r="K107">
+      <c r="L107">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L107" t="s">
-        <v>32</v>
-      </c>
-      <c r="M107">
-        <v>1</v>
-      </c>
-      <c r="N107" t="s">
+      <c r="M107" t="s">
+        <v>32</v>
+      </c>
+      <c r="N107">
+        <v>1</v>
+      </c>
+      <c r="O107" t="s">
         <v>33</v>
       </c>
-      <c r="O107">
+      <c r="P107">
         <v>0.8571428571428571</v>
-      </c>
-      <c r="P107">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q107" t="b">
         <v>0</v>
@@ -8098,29 +8098,29 @@
       <c r="H108">
         <v>0.3550036671493964</v>
       </c>
-      <c r="I108" t="s">
-        <v>15</v>
+      <c r="I108">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J108" t="s">
+        <v>8</v>
+      </c>
+      <c r="K108" t="s">
         <v>28</v>
       </c>
-      <c r="K108">
+      <c r="L108">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L108" t="s">
-        <v>32</v>
-      </c>
-      <c r="M108">
-        <v>1</v>
-      </c>
-      <c r="N108" t="s">
+      <c r="M108" t="s">
+        <v>32</v>
+      </c>
+      <c r="N108">
+        <v>1</v>
+      </c>
+      <c r="O108" t="s">
         <v>30</v>
       </c>
-      <c r="O108">
-        <v>0</v>
-      </c>
       <c r="P108">
-        <v>0.5916727785823273</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="b">
         <v>0</v>
@@ -8169,29 +8169,29 @@
       <c r="H109">
         <v>0.3550036671493964</v>
       </c>
-      <c r="I109" t="s">
-        <v>15</v>
+      <c r="I109">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J109" t="s">
+        <v>8</v>
+      </c>
+      <c r="K109" t="s">
         <v>28</v>
       </c>
-      <c r="K109">
+      <c r="L109">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L109" t="s">
-        <v>32</v>
-      </c>
-      <c r="M109">
-        <v>1</v>
-      </c>
-      <c r="N109" t="s">
+      <c r="M109" t="s">
+        <v>32</v>
+      </c>
+      <c r="N109">
+        <v>1</v>
+      </c>
+      <c r="O109" t="s">
         <v>33</v>
       </c>
-      <c r="O109">
+      <c r="P109">
         <v>0.8571428571428571</v>
-      </c>
-      <c r="P109">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q109" t="b">
         <v>0</v>
@@ -8240,26 +8240,26 @@
       <c r="H110">
         <v>0.3550036671493964</v>
       </c>
-      <c r="I110" t="s">
-        <v>15</v>
+      <c r="I110">
+        <v>0</v>
       </c>
       <c r="J110" t="s">
+        <v>8</v>
+      </c>
+      <c r="K110" t="s">
         <v>30</v>
       </c>
-      <c r="K110">
-        <v>0</v>
-      </c>
-      <c r="L110" t="s">
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110" t="s">
         <v>27</v>
       </c>
-      <c r="M110">
+      <c r="N110">
         <v>0.4285714285714285</v>
       </c>
-      <c r="N110" t="s">
+      <c r="O110" t="s">
         <v>30</v>
-      </c>
-      <c r="O110">
-        <v>0</v>
       </c>
       <c r="P110">
         <v>0</v>
@@ -8311,26 +8311,26 @@
       <c r="H111">
         <v>0.3550036671493964</v>
       </c>
-      <c r="I111" t="s">
-        <v>15</v>
+      <c r="I111">
+        <v>0</v>
       </c>
       <c r="J111" t="s">
+        <v>8</v>
+      </c>
+      <c r="K111" t="s">
         <v>30</v>
       </c>
-      <c r="K111">
-        <v>0</v>
-      </c>
-      <c r="L111" t="s">
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111" t="s">
         <v>29</v>
       </c>
-      <c r="M111">
+      <c r="N111">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N111" t="s">
+      <c r="O111" t="s">
         <v>30</v>
-      </c>
-      <c r="O111">
-        <v>0</v>
       </c>
       <c r="P111">
         <v>0</v>
@@ -8382,26 +8382,26 @@
       <c r="H112">
         <v>0.3550036671493964</v>
       </c>
-      <c r="I112" t="s">
-        <v>15</v>
+      <c r="I112">
+        <v>0</v>
       </c>
       <c r="J112" t="s">
+        <v>8</v>
+      </c>
+      <c r="K112" t="s">
         <v>30</v>
       </c>
-      <c r="K112">
-        <v>0</v>
-      </c>
-      <c r="L112" t="s">
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112" t="s">
         <v>31</v>
       </c>
-      <c r="M112">
+      <c r="N112">
         <v>0.7142857142857143</v>
       </c>
-      <c r="N112" t="s">
+      <c r="O112" t="s">
         <v>30</v>
-      </c>
-      <c r="O112">
-        <v>0</v>
       </c>
       <c r="P112">
         <v>0</v>
@@ -8450,25 +8450,25 @@
       <c r="G113">
         <v>1.661631768332852</v>
       </c>
-      <c r="I113" t="s">
+      <c r="J113" t="s">
         <v>25</v>
       </c>
-      <c r="J113" t="s">
+      <c r="K113" t="s">
         <v>26</v>
       </c>
-      <c r="K113">
+      <c r="L113">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L113" t="s">
-        <v>32</v>
-      </c>
-      <c r="M113">
-        <v>1</v>
-      </c>
-      <c r="N113" t="s">
+      <c r="M113" t="s">
+        <v>32</v>
+      </c>
+      <c r="N113">
+        <v>1</v>
+      </c>
+      <c r="O113" t="s">
         <v>31</v>
       </c>
-      <c r="O113">
+      <c r="P113">
         <v>0.7142857142857143</v>
       </c>
       <c r="Q113" t="b">
@@ -8515,25 +8515,25 @@
       <c r="G114">
         <v>1.661631768332852</v>
       </c>
-      <c r="I114" t="s">
+      <c r="J114" t="s">
         <v>25</v>
       </c>
-      <c r="J114" t="s">
+      <c r="K114" t="s">
         <v>27</v>
       </c>
-      <c r="K114">
+      <c r="L114">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L114" t="s">
-        <v>32</v>
-      </c>
-      <c r="M114">
-        <v>1</v>
-      </c>
-      <c r="N114" t="s">
+      <c r="M114" t="s">
+        <v>32</v>
+      </c>
+      <c r="N114">
+        <v>1</v>
+      </c>
+      <c r="O114" t="s">
         <v>26</v>
       </c>
-      <c r="O114">
+      <c r="P114">
         <v>0.2857142857142857</v>
       </c>
       <c r="Q114" t="b">
@@ -8580,25 +8580,25 @@
       <c r="G115">
         <v>1.661631768332852</v>
       </c>
-      <c r="I115" t="s">
+      <c r="J115" t="s">
         <v>25</v>
       </c>
-      <c r="J115" t="s">
+      <c r="K115" t="s">
         <v>26</v>
       </c>
-      <c r="K115">
+      <c r="L115">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L115" t="s">
-        <v>32</v>
-      </c>
-      <c r="M115">
-        <v>1</v>
-      </c>
-      <c r="N115" t="s">
+      <c r="M115" t="s">
+        <v>32</v>
+      </c>
+      <c r="N115">
+        <v>1</v>
+      </c>
+      <c r="O115" t="s">
         <v>26</v>
       </c>
-      <c r="O115">
+      <c r="P115">
         <v>0.2857142857142857</v>
       </c>
       <c r="Q115" t="b">
@@ -8645,25 +8645,25 @@
       <c r="G116">
         <v>1.661631768332852</v>
       </c>
-      <c r="I116" t="s">
+      <c r="J116" t="s">
         <v>25</v>
       </c>
-      <c r="J116" t="s">
+      <c r="K116" t="s">
         <v>26</v>
       </c>
-      <c r="K116">
+      <c r="L116">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L116" t="s">
+      <c r="M116" t="s">
         <v>30</v>
       </c>
-      <c r="M116">
-        <v>0</v>
-      </c>
-      <c r="N116" t="s">
+      <c r="N116">
+        <v>0</v>
+      </c>
+      <c r="O116" t="s">
         <v>30</v>
       </c>
-      <c r="O116">
+      <c r="P116">
         <v>0</v>
       </c>
       <c r="Q116" t="b">
@@ -8710,25 +8710,25 @@
       <c r="G117">
         <v>1.661631768332852</v>
       </c>
-      <c r="I117" t="s">
+      <c r="J117" t="s">
         <v>25</v>
       </c>
-      <c r="J117" t="s">
+      <c r="K117" t="s">
         <v>28</v>
       </c>
-      <c r="K117">
+      <c r="L117">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L117" t="s">
+      <c r="M117" t="s">
         <v>26</v>
       </c>
-      <c r="M117">
+      <c r="N117">
         <v>0.2857142857142857</v>
       </c>
-      <c r="N117" t="s">
+      <c r="O117" t="s">
         <v>28</v>
       </c>
-      <c r="O117">
+      <c r="P117">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q117" t="b">
@@ -8775,25 +8775,25 @@
       <c r="G118">
         <v>1.661631768332852</v>
       </c>
-      <c r="I118" t="s">
+      <c r="J118" t="s">
         <v>25</v>
       </c>
-      <c r="J118" t="s">
+      <c r="K118" t="s">
         <v>29</v>
       </c>
-      <c r="K118">
+      <c r="L118">
         <v>0.5714285714285714</v>
       </c>
-      <c r="L118" t="s">
-        <v>32</v>
-      </c>
-      <c r="M118">
-        <v>1</v>
-      </c>
-      <c r="N118" t="s">
+      <c r="M118" t="s">
+        <v>32</v>
+      </c>
+      <c r="N118">
+        <v>1</v>
+      </c>
+      <c r="O118" t="s">
         <v>27</v>
       </c>
-      <c r="O118">
+      <c r="P118">
         <v>0.4285714285714285</v>
       </c>
       <c r="Q118" t="b">
@@ -8840,25 +8840,25 @@
       <c r="G119">
         <v>1.661631768332852</v>
       </c>
-      <c r="I119" t="s">
+      <c r="J119" t="s">
         <v>25</v>
       </c>
-      <c r="J119" t="s">
+      <c r="K119" t="s">
         <v>28</v>
       </c>
-      <c r="K119">
+      <c r="L119">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L119" t="s">
-        <v>32</v>
-      </c>
-      <c r="M119">
-        <v>1</v>
-      </c>
-      <c r="N119" t="s">
+      <c r="M119" t="s">
+        <v>32</v>
+      </c>
+      <c r="N119">
+        <v>1</v>
+      </c>
+      <c r="O119" t="s">
         <v>30</v>
       </c>
-      <c r="O119">
+      <c r="P119">
         <v>0</v>
       </c>
       <c r="Q119" t="b">
@@ -8905,25 +8905,25 @@
       <c r="G120">
         <v>1.661631768332852</v>
       </c>
-      <c r="I120" t="s">
+      <c r="J120" t="s">
         <v>25</v>
       </c>
-      <c r="J120" t="s">
+      <c r="K120" t="s">
         <v>28</v>
       </c>
-      <c r="K120">
+      <c r="L120">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L120" t="s">
-        <v>32</v>
-      </c>
-      <c r="M120">
-        <v>1</v>
-      </c>
-      <c r="N120" t="s">
+      <c r="M120" t="s">
+        <v>32</v>
+      </c>
+      <c r="N120">
+        <v>1</v>
+      </c>
+      <c r="O120" t="s">
         <v>27</v>
       </c>
-      <c r="O120">
+      <c r="P120">
         <v>0.4285714285714285</v>
       </c>
       <c r="Q120" t="b">
@@ -8970,25 +8970,25 @@
       <c r="G121">
         <v>1.661631768332852</v>
       </c>
-      <c r="I121" t="s">
+      <c r="J121" t="s">
         <v>25</v>
       </c>
-      <c r="J121" t="s">
+      <c r="K121" t="s">
         <v>26</v>
       </c>
-      <c r="K121">
+      <c r="L121">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L121" t="s">
+      <c r="M121" t="s">
         <v>26</v>
       </c>
-      <c r="M121">
+      <c r="N121">
         <v>0.2857142857142857</v>
       </c>
-      <c r="N121" t="s">
+      <c r="O121" t="s">
         <v>28</v>
       </c>
-      <c r="O121">
+      <c r="P121">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q121" t="b">
@@ -9035,25 +9035,25 @@
       <c r="G122">
         <v>1.661631768332852</v>
       </c>
-      <c r="I122" t="s">
+      <c r="J122" t="s">
         <v>25</v>
       </c>
-      <c r="J122" t="s">
+      <c r="K122" t="s">
         <v>28</v>
       </c>
-      <c r="K122">
+      <c r="L122">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L122" t="s">
-        <v>32</v>
-      </c>
-      <c r="M122">
-        <v>1</v>
-      </c>
-      <c r="N122" t="s">
+      <c r="M122" t="s">
+        <v>32</v>
+      </c>
+      <c r="N122">
+        <v>1</v>
+      </c>
+      <c r="O122" t="s">
         <v>26</v>
       </c>
-      <c r="O122">
+      <c r="P122">
         <v>0.2857142857142857</v>
       </c>
       <c r="Q122" t="b">
@@ -9100,25 +9100,25 @@
       <c r="G123">
         <v>1.661631768332852</v>
       </c>
-      <c r="I123" t="s">
+      <c r="J123" t="s">
         <v>25</v>
       </c>
-      <c r="J123" t="s">
+      <c r="K123" t="s">
         <v>30</v>
       </c>
-      <c r="K123">
-        <v>0</v>
-      </c>
-      <c r="L123" t="s">
-        <v>32</v>
-      </c>
-      <c r="M123">
-        <v>1</v>
-      </c>
-      <c r="N123" t="s">
-        <v>32</v>
-      </c>
-      <c r="O123">
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123" t="s">
+        <v>32</v>
+      </c>
+      <c r="N123">
+        <v>1</v>
+      </c>
+      <c r="O123" t="s">
+        <v>32</v>
+      </c>
+      <c r="P123">
         <v>1</v>
       </c>
       <c r="Q123" t="b">
@@ -9165,25 +9165,25 @@
       <c r="G124">
         <v>1.661631768332852</v>
       </c>
-      <c r="I124" t="s">
+      <c r="J124" t="s">
         <v>25</v>
       </c>
-      <c r="J124" t="s">
+      <c r="K124" t="s">
         <v>28</v>
       </c>
-      <c r="K124">
+      <c r="L124">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L124" t="s">
-        <v>32</v>
-      </c>
-      <c r="M124">
-        <v>1</v>
-      </c>
-      <c r="N124" t="s">
+      <c r="M124" t="s">
+        <v>32</v>
+      </c>
+      <c r="N124">
+        <v>1</v>
+      </c>
+      <c r="O124" t="s">
         <v>26</v>
       </c>
-      <c r="O124">
+      <c r="P124">
         <v>0.2857142857142857</v>
       </c>
       <c r="Q124" t="b">
@@ -9230,25 +9230,25 @@
       <c r="G125">
         <v>1.661631768332852</v>
       </c>
-      <c r="I125" t="s">
+      <c r="J125" t="s">
         <v>25</v>
       </c>
-      <c r="J125" t="s">
+      <c r="K125" t="s">
         <v>27</v>
       </c>
-      <c r="K125">
+      <c r="L125">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L125" t="s">
+      <c r="M125" t="s">
         <v>29</v>
       </c>
-      <c r="M125">
+      <c r="N125">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N125" t="s">
+      <c r="O125" t="s">
         <v>30</v>
       </c>
-      <c r="O125">
+      <c r="P125">
         <v>0</v>
       </c>
       <c r="Q125" t="b">
@@ -9295,25 +9295,25 @@
       <c r="G126">
         <v>1.661631768332852</v>
       </c>
-      <c r="I126" t="s">
+      <c r="J126" t="s">
         <v>25</v>
       </c>
-      <c r="J126" t="s">
+      <c r="K126" t="s">
         <v>28</v>
       </c>
-      <c r="K126">
+      <c r="L126">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L126" t="s">
+      <c r="M126" t="s">
         <v>30</v>
       </c>
-      <c r="M126">
-        <v>0</v>
-      </c>
-      <c r="N126" t="s">
+      <c r="N126">
+        <v>0</v>
+      </c>
+      <c r="O126" t="s">
         <v>30</v>
       </c>
-      <c r="O126">
+      <c r="P126">
         <v>0</v>
       </c>
       <c r="Q126" t="b">
@@ -9360,25 +9360,25 @@
       <c r="G127">
         <v>1.661631768332852</v>
       </c>
-      <c r="I127" t="s">
+      <c r="J127" t="s">
         <v>25</v>
       </c>
-      <c r="J127" t="s">
+      <c r="K127" t="s">
         <v>30</v>
       </c>
-      <c r="K127">
-        <v>0</v>
-      </c>
-      <c r="L127" t="s">
-        <v>32</v>
-      </c>
-      <c r="M127">
-        <v>1</v>
-      </c>
-      <c r="N127" t="s">
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127" t="s">
+        <v>32</v>
+      </c>
+      <c r="N127">
+        <v>1</v>
+      </c>
+      <c r="O127" t="s">
         <v>30</v>
       </c>
-      <c r="O127">
+      <c r="P127">
         <v>0</v>
       </c>
       <c r="Q127" t="b">
@@ -9425,25 +9425,25 @@
       <c r="G128">
         <v>1.661631768332852</v>
       </c>
-      <c r="I128" t="s">
+      <c r="J128" t="s">
         <v>25</v>
       </c>
-      <c r="J128" t="s">
+      <c r="K128" t="s">
         <v>28</v>
       </c>
-      <c r="K128">
+      <c r="L128">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L128" t="s">
-        <v>32</v>
-      </c>
-      <c r="M128">
-        <v>1</v>
-      </c>
-      <c r="N128" t="s">
+      <c r="M128" t="s">
+        <v>32</v>
+      </c>
+      <c r="N128">
+        <v>1</v>
+      </c>
+      <c r="O128" t="s">
         <v>26</v>
       </c>
-      <c r="O128">
+      <c r="P128">
         <v>0.2857142857142857</v>
       </c>
       <c r="Q128" t="b">
@@ -9490,25 +9490,25 @@
       <c r="G129">
         <v>1.661631768332852</v>
       </c>
-      <c r="I129" t="s">
+      <c r="J129" t="s">
         <v>25</v>
       </c>
-      <c r="J129" t="s">
+      <c r="K129" t="s">
         <v>28</v>
       </c>
-      <c r="K129">
+      <c r="L129">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L129" t="s">
-        <v>32</v>
-      </c>
-      <c r="M129">
-        <v>1</v>
-      </c>
-      <c r="N129" t="s">
+      <c r="M129" t="s">
+        <v>32</v>
+      </c>
+      <c r="N129">
+        <v>1</v>
+      </c>
+      <c r="O129" t="s">
         <v>27</v>
       </c>
-      <c r="O129">
+      <c r="P129">
         <v>0.4285714285714285</v>
       </c>
       <c r="Q129" t="b">
@@ -9555,25 +9555,25 @@
       <c r="G130">
         <v>1.661631768332852</v>
       </c>
-      <c r="I130" t="s">
+      <c r="J130" t="s">
         <v>25</v>
       </c>
-      <c r="J130" t="s">
+      <c r="K130" t="s">
         <v>26</v>
       </c>
-      <c r="K130">
+      <c r="L130">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L130" t="s">
+      <c r="M130" t="s">
         <v>30</v>
       </c>
-      <c r="M130">
-        <v>0</v>
-      </c>
-      <c r="N130" t="s">
+      <c r="N130">
+        <v>0</v>
+      </c>
+      <c r="O130" t="s">
         <v>30</v>
       </c>
-      <c r="O130">
+      <c r="P130">
         <v>0</v>
       </c>
       <c r="Q130" t="b">
@@ -9620,25 +9620,25 @@
       <c r="G131">
         <v>1.661631768332852</v>
       </c>
-      <c r="I131" t="s">
+      <c r="J131" t="s">
         <v>25</v>
       </c>
-      <c r="J131" t="s">
+      <c r="K131" t="s">
         <v>28</v>
       </c>
-      <c r="K131">
+      <c r="L131">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L131" t="s">
+      <c r="M131" t="s">
         <v>31</v>
       </c>
-      <c r="M131">
+      <c r="N131">
         <v>0.7142857142857143</v>
       </c>
-      <c r="N131" t="s">
+      <c r="O131" t="s">
         <v>26</v>
       </c>
-      <c r="O131">
+      <c r="P131">
         <v>0.2857142857142857</v>
       </c>
       <c r="Q131" t="b">
@@ -9685,25 +9685,25 @@
       <c r="G132">
         <v>1.661631768332852</v>
       </c>
-      <c r="I132" t="s">
+      <c r="J132" t="s">
         <v>25</v>
       </c>
-      <c r="J132" t="s">
+      <c r="K132" t="s">
         <v>27</v>
       </c>
-      <c r="K132">
+      <c r="L132">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L132" t="s">
+      <c r="M132" t="s">
         <v>30</v>
       </c>
-      <c r="M132">
-        <v>0</v>
-      </c>
-      <c r="N132" t="s">
+      <c r="N132">
+        <v>0</v>
+      </c>
+      <c r="O132" t="s">
         <v>30</v>
       </c>
-      <c r="O132">
+      <c r="P132">
         <v>0</v>
       </c>
       <c r="Q132" t="b">
@@ -9750,25 +9750,25 @@
       <c r="G133">
         <v>1.661631768332852</v>
       </c>
-      <c r="I133" t="s">
+      <c r="J133" t="s">
         <v>25</v>
       </c>
-      <c r="J133" t="s">
+      <c r="K133" t="s">
         <v>30</v>
       </c>
-      <c r="K133">
-        <v>0</v>
-      </c>
-      <c r="L133" t="s">
-        <v>32</v>
-      </c>
-      <c r="M133">
-        <v>1</v>
-      </c>
-      <c r="N133" t="s">
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133" t="s">
+        <v>32</v>
+      </c>
+      <c r="N133">
+        <v>1</v>
+      </c>
+      <c r="O133" t="s">
         <v>33</v>
       </c>
-      <c r="O133">
+      <c r="P133">
         <v>0.8571428571428571</v>
       </c>
       <c r="Q133" t="b">
@@ -9815,25 +9815,25 @@
       <c r="G134">
         <v>1.661631768332852</v>
       </c>
-      <c r="I134" t="s">
+      <c r="J134" t="s">
         <v>25</v>
       </c>
-      <c r="J134" t="s">
+      <c r="K134" t="s">
         <v>26</v>
       </c>
-      <c r="K134">
+      <c r="L134">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L134" t="s">
-        <v>32</v>
-      </c>
-      <c r="M134">
-        <v>1</v>
-      </c>
-      <c r="N134" t="s">
+      <c r="M134" t="s">
+        <v>32</v>
+      </c>
+      <c r="N134">
+        <v>1</v>
+      </c>
+      <c r="O134" t="s">
         <v>28</v>
       </c>
-      <c r="O134">
+      <c r="P134">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q134" t="b">
@@ -9880,25 +9880,25 @@
       <c r="G135">
         <v>1.661631768332852</v>
       </c>
-      <c r="I135" t="s">
+      <c r="J135" t="s">
         <v>25</v>
       </c>
-      <c r="J135" t="s">
+      <c r="K135" t="s">
         <v>29</v>
       </c>
-      <c r="K135">
+      <c r="L135">
         <v>0.5714285714285714</v>
       </c>
-      <c r="L135" t="s">
-        <v>32</v>
-      </c>
-      <c r="M135">
-        <v>1</v>
-      </c>
-      <c r="N135" t="s">
+      <c r="M135" t="s">
+        <v>32</v>
+      </c>
+      <c r="N135">
+        <v>1</v>
+      </c>
+      <c r="O135" t="s">
         <v>27</v>
       </c>
-      <c r="O135">
+      <c r="P135">
         <v>0.4285714285714285</v>
       </c>
       <c r="Q135" t="b">
@@ -9945,25 +9945,25 @@
       <c r="G136">
         <v>1.661631768332852</v>
       </c>
-      <c r="I136" t="s">
+      <c r="J136" t="s">
         <v>25</v>
       </c>
-      <c r="J136" t="s">
+      <c r="K136" t="s">
         <v>28</v>
       </c>
-      <c r="K136">
+      <c r="L136">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L136" t="s">
-        <v>32</v>
-      </c>
-      <c r="M136">
-        <v>1</v>
-      </c>
-      <c r="N136" t="s">
+      <c r="M136" t="s">
+        <v>32</v>
+      </c>
+      <c r="N136">
+        <v>1</v>
+      </c>
+      <c r="O136" t="s">
         <v>33</v>
       </c>
-      <c r="O136">
+      <c r="P136">
         <v>0.8571428571428571</v>
       </c>
       <c r="Q136" t="b">
@@ -10010,25 +10010,25 @@
       <c r="G137">
         <v>1.661631768332852</v>
       </c>
-      <c r="I137" t="s">
+      <c r="J137" t="s">
         <v>25</v>
       </c>
-      <c r="J137" t="s">
+      <c r="K137" t="s">
         <v>26</v>
       </c>
-      <c r="K137">
+      <c r="L137">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L137" t="s">
+      <c r="M137" t="s">
         <v>33</v>
       </c>
-      <c r="M137">
+      <c r="N137">
         <v>0.8571428571428571</v>
       </c>
-      <c r="N137" t="s">
+      <c r="O137" t="s">
         <v>28</v>
       </c>
-      <c r="O137">
+      <c r="P137">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q137" t="b">
@@ -10075,25 +10075,25 @@
       <c r="G138">
         <v>1.661631768332852</v>
       </c>
-      <c r="I138" t="s">
+      <c r="J138" t="s">
         <v>25</v>
       </c>
-      <c r="J138" t="s">
+      <c r="K138" t="s">
         <v>30</v>
       </c>
-      <c r="K138">
-        <v>0</v>
-      </c>
-      <c r="L138" t="s">
-        <v>32</v>
-      </c>
-      <c r="M138">
-        <v>1</v>
-      </c>
-      <c r="N138" t="s">
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138" t="s">
+        <v>32</v>
+      </c>
+      <c r="N138">
+        <v>1</v>
+      </c>
+      <c r="O138" t="s">
         <v>26</v>
       </c>
-      <c r="O138">
+      <c r="P138">
         <v>0.2857142857142857</v>
       </c>
       <c r="Q138" t="b">
@@ -10140,25 +10140,25 @@
       <c r="G139">
         <v>1.661631768332852</v>
       </c>
-      <c r="I139" t="s">
+      <c r="J139" t="s">
         <v>25</v>
       </c>
-      <c r="J139" t="s">
+      <c r="K139" t="s">
         <v>30</v>
       </c>
-      <c r="K139">
-        <v>0</v>
-      </c>
-      <c r="L139" t="s">
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139" t="s">
         <v>31</v>
       </c>
-      <c r="M139">
+      <c r="N139">
         <v>0.7142857142857143</v>
       </c>
-      <c r="N139" t="s">
+      <c r="O139" t="s">
         <v>29</v>
       </c>
-      <c r="O139">
+      <c r="P139">
         <v>0.5714285714285714</v>
       </c>
       <c r="Q139" t="b">
@@ -10205,25 +10205,25 @@
       <c r="G140">
         <v>1.661631768332852</v>
       </c>
-      <c r="I140" t="s">
+      <c r="J140" t="s">
         <v>25</v>
       </c>
-      <c r="J140" t="s">
+      <c r="K140" t="s">
         <v>27</v>
       </c>
-      <c r="K140">
+      <c r="L140">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L140" t="s">
+      <c r="M140" t="s">
         <v>33</v>
       </c>
-      <c r="M140">
+      <c r="N140">
         <v>0.8571428571428571</v>
       </c>
-      <c r="N140" t="s">
+      <c r="O140" t="s">
         <v>30</v>
       </c>
-      <c r="O140">
+      <c r="P140">
         <v>0</v>
       </c>
       <c r="Q140" t="b">
@@ -10270,25 +10270,25 @@
       <c r="G141">
         <v>1.661631768332852</v>
       </c>
-      <c r="I141" t="s">
+      <c r="J141" t="s">
         <v>25</v>
       </c>
-      <c r="J141" t="s">
+      <c r="K141" t="s">
         <v>26</v>
       </c>
-      <c r="K141">
+      <c r="L141">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L141" t="s">
-        <v>32</v>
-      </c>
-      <c r="M141">
-        <v>1</v>
-      </c>
-      <c r="N141" t="s">
+      <c r="M141" t="s">
+        <v>32</v>
+      </c>
+      <c r="N141">
+        <v>1</v>
+      </c>
+      <c r="O141" t="s">
         <v>31</v>
       </c>
-      <c r="O141">
+      <c r="P141">
         <v>0.7142857142857143</v>
       </c>
       <c r="Q141" t="b">
@@ -10335,25 +10335,25 @@
       <c r="G142">
         <v>1.661631768332852</v>
       </c>
-      <c r="I142" t="s">
+      <c r="J142" t="s">
         <v>25</v>
       </c>
-      <c r="J142" t="s">
+      <c r="K142" t="s">
         <v>30</v>
       </c>
-      <c r="K142">
-        <v>0</v>
-      </c>
-      <c r="L142" t="s">
+      <c r="L142">
+        <v>0</v>
+      </c>
+      <c r="M142" t="s">
         <v>31</v>
       </c>
-      <c r="M142">
+      <c r="N142">
         <v>0.7142857142857143</v>
       </c>
-      <c r="N142" t="s">
+      <c r="O142" t="s">
         <v>28</v>
       </c>
-      <c r="O142">
+      <c r="P142">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q142" t="b">
@@ -10400,25 +10400,25 @@
       <c r="G143">
         <v>1.661631768332852</v>
       </c>
-      <c r="I143" t="s">
+      <c r="J143" t="s">
         <v>25</v>
       </c>
-      <c r="J143" t="s">
+      <c r="K143" t="s">
         <v>26</v>
       </c>
-      <c r="K143">
+      <c r="L143">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L143" t="s">
-        <v>32</v>
-      </c>
-      <c r="M143">
-        <v>1</v>
-      </c>
-      <c r="N143" t="s">
+      <c r="M143" t="s">
+        <v>32</v>
+      </c>
+      <c r="N143">
+        <v>1</v>
+      </c>
+      <c r="O143" t="s">
         <v>29</v>
       </c>
-      <c r="O143">
+      <c r="P143">
         <v>0.5714285714285714</v>
       </c>
       <c r="Q143" t="b">
@@ -10465,25 +10465,25 @@
       <c r="G144">
         <v>1.661631768332852</v>
       </c>
-      <c r="I144" t="s">
+      <c r="J144" t="s">
         <v>25</v>
       </c>
-      <c r="J144" t="s">
+      <c r="K144" t="s">
         <v>26</v>
       </c>
-      <c r="K144">
+      <c r="L144">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L144" t="s">
-        <v>32</v>
-      </c>
-      <c r="M144">
-        <v>1</v>
-      </c>
-      <c r="N144" t="s">
+      <c r="M144" t="s">
+        <v>32</v>
+      </c>
+      <c r="N144">
+        <v>1</v>
+      </c>
+      <c r="O144" t="s">
         <v>30</v>
       </c>
-      <c r="O144">
+      <c r="P144">
         <v>0</v>
       </c>
       <c r="Q144" t="b">
@@ -10530,25 +10530,25 @@
       <c r="G145">
         <v>1.661631768332852</v>
       </c>
-      <c r="I145" t="s">
+      <c r="J145" t="s">
         <v>25</v>
       </c>
-      <c r="J145" t="s">
+      <c r="K145" t="s">
         <v>28</v>
       </c>
-      <c r="K145">
+      <c r="L145">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L145" t="s">
-        <v>32</v>
-      </c>
-      <c r="M145">
-        <v>1</v>
-      </c>
-      <c r="N145" t="s">
+      <c r="M145" t="s">
+        <v>32</v>
+      </c>
+      <c r="N145">
+        <v>1</v>
+      </c>
+      <c r="O145" t="s">
         <v>26</v>
       </c>
-      <c r="O145">
+      <c r="P145">
         <v>0.2857142857142857</v>
       </c>
       <c r="Q145" t="b">
@@ -10595,25 +10595,25 @@
       <c r="G146">
         <v>1.661631768332852</v>
       </c>
-      <c r="I146" t="s">
+      <c r="J146" t="s">
         <v>25</v>
       </c>
-      <c r="J146" t="s">
+      <c r="K146" t="s">
         <v>30</v>
       </c>
-      <c r="K146">
-        <v>0</v>
-      </c>
-      <c r="L146" t="s">
-        <v>32</v>
-      </c>
-      <c r="M146">
-        <v>1</v>
-      </c>
-      <c r="N146" t="s">
+      <c r="L146">
+        <v>0</v>
+      </c>
+      <c r="M146" t="s">
+        <v>32</v>
+      </c>
+      <c r="N146">
+        <v>1</v>
+      </c>
+      <c r="O146" t="s">
         <v>26</v>
       </c>
-      <c r="O146">
+      <c r="P146">
         <v>0.2857142857142857</v>
       </c>
       <c r="Q146" t="b">
@@ -10660,25 +10660,25 @@
       <c r="G147">
         <v>1.661631768332852</v>
       </c>
-      <c r="I147" t="s">
+      <c r="J147" t="s">
         <v>25</v>
       </c>
-      <c r="J147" t="s">
+      <c r="K147" t="s">
         <v>27</v>
       </c>
-      <c r="K147">
+      <c r="L147">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L147" t="s">
-        <v>32</v>
-      </c>
-      <c r="M147">
-        <v>1</v>
-      </c>
-      <c r="N147" t="s">
+      <c r="M147" t="s">
+        <v>32</v>
+      </c>
+      <c r="N147">
+        <v>1</v>
+      </c>
+      <c r="O147" t="s">
         <v>30</v>
       </c>
-      <c r="O147">
+      <c r="P147">
         <v>0</v>
       </c>
       <c r="Q147" t="b">
@@ -10725,25 +10725,25 @@
       <c r="G148">
         <v>1.661631768332852</v>
       </c>
-      <c r="I148" t="s">
+      <c r="J148" t="s">
         <v>25</v>
       </c>
-      <c r="J148" t="s">
+      <c r="K148" t="s">
         <v>28</v>
       </c>
-      <c r="K148">
+      <c r="L148">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L148" t="s">
+      <c r="M148" t="s">
         <v>26</v>
       </c>
-      <c r="M148">
+      <c r="N148">
         <v>0.2857142857142857</v>
       </c>
-      <c r="N148" t="s">
+      <c r="O148" t="s">
         <v>30</v>
       </c>
-      <c r="O148">
+      <c r="P148">
         <v>0</v>
       </c>
       <c r="Q148" t="b">
@@ -10790,25 +10790,25 @@
       <c r="G149">
         <v>1.661631768332852</v>
       </c>
-      <c r="I149" t="s">
+      <c r="J149" t="s">
         <v>25</v>
       </c>
-      <c r="J149" t="s">
+      <c r="K149" t="s">
         <v>26</v>
       </c>
-      <c r="K149">
+      <c r="L149">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L149" t="s">
+      <c r="M149" t="s">
         <v>33</v>
       </c>
-      <c r="M149">
+      <c r="N149">
         <v>0.8571428571428571</v>
       </c>
-      <c r="N149" t="s">
+      <c r="O149" t="s">
         <v>30</v>
       </c>
-      <c r="O149">
+      <c r="P149">
         <v>0</v>
       </c>
       <c r="Q149" t="b">
@@ -10855,25 +10855,25 @@
       <c r="G150">
         <v>1.661631768332852</v>
       </c>
-      <c r="I150" t="s">
+      <c r="J150" t="s">
         <v>25</v>
       </c>
-      <c r="J150" t="s">
+      <c r="K150" t="s">
         <v>29</v>
       </c>
-      <c r="K150">
+      <c r="L150">
         <v>0.5714285714285714</v>
       </c>
-      <c r="L150" t="s">
-        <v>32</v>
-      </c>
-      <c r="M150">
-        <v>1</v>
-      </c>
-      <c r="N150" t="s">
+      <c r="M150" t="s">
+        <v>32</v>
+      </c>
+      <c r="N150">
+        <v>1</v>
+      </c>
+      <c r="O150" t="s">
         <v>26</v>
       </c>
-      <c r="O150">
+      <c r="P150">
         <v>0.2857142857142857</v>
       </c>
       <c r="Q150" t="b">
@@ -10920,25 +10920,25 @@
       <c r="G151">
         <v>1.661631768332852</v>
       </c>
-      <c r="I151" t="s">
+      <c r="J151" t="s">
         <v>25</v>
       </c>
-      <c r="J151" t="s">
+      <c r="K151" t="s">
         <v>26</v>
       </c>
-      <c r="K151">
+      <c r="L151">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L151" t="s">
+      <c r="M151" t="s">
         <v>28</v>
       </c>
-      <c r="M151">
+      <c r="N151">
         <v>0.1428571428571428</v>
       </c>
-      <c r="N151" t="s">
+      <c r="O151" t="s">
         <v>30</v>
       </c>
-      <c r="O151">
+      <c r="P151">
         <v>0</v>
       </c>
       <c r="Q151" t="b">
@@ -10985,25 +10985,25 @@
       <c r="G152">
         <v>1.661631768332852</v>
       </c>
-      <c r="I152" t="s">
+      <c r="J152" t="s">
         <v>25</v>
       </c>
-      <c r="J152" t="s">
+      <c r="K152" t="s">
         <v>26</v>
       </c>
-      <c r="K152">
+      <c r="L152">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L152" t="s">
-        <v>32</v>
-      </c>
-      <c r="M152">
-        <v>1</v>
-      </c>
-      <c r="N152" t="s">
+      <c r="M152" t="s">
+        <v>32</v>
+      </c>
+      <c r="N152">
+        <v>1</v>
+      </c>
+      <c r="O152" t="s">
         <v>27</v>
       </c>
-      <c r="O152">
+      <c r="P152">
         <v>0.4285714285714285</v>
       </c>
       <c r="Q152" t="b">
@@ -11050,25 +11050,25 @@
       <c r="G153">
         <v>1.661631768332852</v>
       </c>
-      <c r="I153" t="s">
+      <c r="J153" t="s">
         <v>25</v>
       </c>
-      <c r="J153" t="s">
+      <c r="K153" t="s">
         <v>30</v>
       </c>
-      <c r="K153">
-        <v>0</v>
-      </c>
-      <c r="L153" t="s">
-        <v>32</v>
-      </c>
-      <c r="M153">
-        <v>1</v>
-      </c>
-      <c r="N153" t="s">
+      <c r="L153">
+        <v>0</v>
+      </c>
+      <c r="M153" t="s">
+        <v>32</v>
+      </c>
+      <c r="N153">
+        <v>1</v>
+      </c>
+      <c r="O153" t="s">
         <v>31</v>
       </c>
-      <c r="O153">
+      <c r="P153">
         <v>0.7142857142857143</v>
       </c>
       <c r="Q153" t="b">
@@ -11115,25 +11115,25 @@
       <c r="G154">
         <v>1.661631768332852</v>
       </c>
-      <c r="I154" t="s">
+      <c r="J154" t="s">
         <v>25</v>
       </c>
-      <c r="J154" t="s">
+      <c r="K154" t="s">
         <v>27</v>
       </c>
-      <c r="K154">
+      <c r="L154">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L154" t="s">
+      <c r="M154" t="s">
         <v>33</v>
       </c>
-      <c r="M154">
+      <c r="N154">
         <v>0.8571428571428571</v>
       </c>
-      <c r="N154" t="s">
+      <c r="O154" t="s">
         <v>28</v>
       </c>
-      <c r="O154">
+      <c r="P154">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q154" t="b">
@@ -11180,25 +11180,25 @@
       <c r="G155">
         <v>1.661631768332852</v>
       </c>
-      <c r="I155" t="s">
+      <c r="J155" t="s">
         <v>25</v>
       </c>
-      <c r="J155" t="s">
+      <c r="K155" t="s">
         <v>28</v>
       </c>
-      <c r="K155">
+      <c r="L155">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L155" t="s">
-        <v>32</v>
-      </c>
-      <c r="M155">
-        <v>1</v>
-      </c>
-      <c r="N155" t="s">
+      <c r="M155" t="s">
+        <v>32</v>
+      </c>
+      <c r="N155">
+        <v>1</v>
+      </c>
+      <c r="O155" t="s">
         <v>31</v>
       </c>
-      <c r="O155">
+      <c r="P155">
         <v>0.7142857142857143</v>
       </c>
       <c r="Q155" t="b">
@@ -11245,25 +11245,25 @@
       <c r="G156">
         <v>1.661631768332852</v>
       </c>
-      <c r="I156" t="s">
+      <c r="J156" t="s">
         <v>25</v>
       </c>
-      <c r="J156" t="s">
+      <c r="K156" t="s">
         <v>28</v>
       </c>
-      <c r="K156">
+      <c r="L156">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L156" t="s">
-        <v>32</v>
-      </c>
-      <c r="M156">
-        <v>1</v>
-      </c>
-      <c r="N156" t="s">
+      <c r="M156" t="s">
+        <v>32</v>
+      </c>
+      <c r="N156">
+        <v>1</v>
+      </c>
+      <c r="O156" t="s">
         <v>33</v>
       </c>
-      <c r="O156">
+      <c r="P156">
         <v>0.8571428571428571</v>
       </c>
       <c r="Q156" t="b">
@@ -11310,25 +11310,25 @@
       <c r="G157">
         <v>1.778362799058254</v>
       </c>
-      <c r="I157" t="s">
+      <c r="J157" t="s">
         <v>25</v>
       </c>
-      <c r="J157" t="s">
+      <c r="K157" t="s">
         <v>26</v>
       </c>
-      <c r="K157">
+      <c r="L157">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L157" t="s">
+      <c r="M157" t="s">
         <v>27</v>
       </c>
-      <c r="M157">
+      <c r="N157">
         <v>0.4285714285714285</v>
       </c>
-      <c r="N157" t="s">
+      <c r="O157" t="s">
         <v>30</v>
       </c>
-      <c r="O157">
+      <c r="P157">
         <v>0</v>
       </c>
       <c r="Q157" t="b">
@@ -11375,25 +11375,25 @@
       <c r="G158">
         <v>1.778362799058254</v>
       </c>
-      <c r="I158" t="s">
+      <c r="J158" t="s">
         <v>25</v>
       </c>
-      <c r="J158" t="s">
+      <c r="K158" t="s">
         <v>27</v>
       </c>
-      <c r="K158">
+      <c r="L158">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L158" t="s">
-        <v>32</v>
-      </c>
-      <c r="M158">
-        <v>1</v>
-      </c>
-      <c r="N158" t="s">
+      <c r="M158" t="s">
+        <v>32</v>
+      </c>
+      <c r="N158">
+        <v>1</v>
+      </c>
+      <c r="O158" t="s">
         <v>29</v>
       </c>
-      <c r="O158">
+      <c r="P158">
         <v>0.5714285714285714</v>
       </c>
       <c r="Q158" t="b">
@@ -11440,25 +11440,25 @@
       <c r="G159">
         <v>1.778362799058254</v>
       </c>
-      <c r="I159" t="s">
+      <c r="J159" t="s">
         <v>25</v>
       </c>
-      <c r="J159" t="s">
+      <c r="K159" t="s">
         <v>26</v>
       </c>
-      <c r="K159">
+      <c r="L159">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L159" t="s">
-        <v>32</v>
-      </c>
-      <c r="M159">
-        <v>1</v>
-      </c>
-      <c r="N159" t="s">
+      <c r="M159" t="s">
+        <v>32</v>
+      </c>
+      <c r="N159">
+        <v>1</v>
+      </c>
+      <c r="O159" t="s">
         <v>27</v>
       </c>
-      <c r="O159">
+      <c r="P159">
         <v>0.4285714285714285</v>
       </c>
       <c r="Q159" t="b">
@@ -11505,25 +11505,25 @@
       <c r="G160">
         <v>1.778362799058254</v>
       </c>
-      <c r="I160" t="s">
+      <c r="J160" t="s">
         <v>25</v>
       </c>
-      <c r="J160" t="s">
+      <c r="K160" t="s">
         <v>28</v>
       </c>
-      <c r="K160">
+      <c r="L160">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L160" t="s">
-        <v>32</v>
-      </c>
-      <c r="M160">
-        <v>1</v>
-      </c>
-      <c r="N160" t="s">
+      <c r="M160" t="s">
+        <v>32</v>
+      </c>
+      <c r="N160">
+        <v>1</v>
+      </c>
+      <c r="O160" t="s">
         <v>33</v>
       </c>
-      <c r="O160">
+      <c r="P160">
         <v>0.8571428571428571</v>
       </c>
       <c r="Q160" t="b">
@@ -11570,25 +11570,25 @@
       <c r="G161">
         <v>1.778362799058254</v>
       </c>
-      <c r="I161" t="s">
+      <c r="J161" t="s">
         <v>25</v>
       </c>
-      <c r="J161" t="s">
+      <c r="K161" t="s">
         <v>26</v>
       </c>
-      <c r="K161">
+      <c r="L161">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L161" t="s">
-        <v>32</v>
-      </c>
-      <c r="M161">
-        <v>1</v>
-      </c>
-      <c r="N161" t="s">
+      <c r="M161" t="s">
+        <v>32</v>
+      </c>
+      <c r="N161">
+        <v>1</v>
+      </c>
+      <c r="O161" t="s">
         <v>31</v>
       </c>
-      <c r="O161">
+      <c r="P161">
         <v>0.7142857142857143</v>
       </c>
       <c r="Q161" t="b">
@@ -11635,25 +11635,25 @@
       <c r="G162">
         <v>1.778362799058254</v>
       </c>
-      <c r="I162" t="s">
+      <c r="J162" t="s">
         <v>25</v>
       </c>
-      <c r="J162" t="s">
+      <c r="K162" t="s">
         <v>28</v>
       </c>
-      <c r="K162">
+      <c r="L162">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L162" t="s">
-        <v>32</v>
-      </c>
-      <c r="M162">
-        <v>1</v>
-      </c>
-      <c r="N162" t="s">
+      <c r="M162" t="s">
+        <v>32</v>
+      </c>
+      <c r="N162">
+        <v>1</v>
+      </c>
+      <c r="O162" t="s">
         <v>31</v>
       </c>
-      <c r="O162">
+      <c r="P162">
         <v>0.7142857142857143</v>
       </c>
       <c r="Q162" t="b">
@@ -11700,25 +11700,25 @@
       <c r="G163">
         <v>1.778362799058254</v>
       </c>
-      <c r="I163" t="s">
+      <c r="J163" t="s">
         <v>25</v>
       </c>
-      <c r="J163" t="s">
+      <c r="K163" t="s">
         <v>29</v>
       </c>
-      <c r="K163">
+      <c r="L163">
         <v>0.5714285714285714</v>
       </c>
-      <c r="L163" t="s">
+      <c r="M163" t="s">
         <v>26</v>
       </c>
-      <c r="M163">
+      <c r="N163">
         <v>0.2857142857142857</v>
       </c>
-      <c r="N163" t="s">
+      <c r="O163" t="s">
         <v>30</v>
       </c>
-      <c r="O163">
+      <c r="P163">
         <v>0</v>
       </c>
       <c r="Q163" t="b">
@@ -11765,25 +11765,25 @@
       <c r="G164">
         <v>1.778362799058254</v>
       </c>
-      <c r="I164" t="s">
+      <c r="J164" t="s">
         <v>25</v>
       </c>
-      <c r="J164" t="s">
+      <c r="K164" t="s">
         <v>26</v>
       </c>
-      <c r="K164">
+      <c r="L164">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L164" t="s">
+      <c r="M164" t="s">
         <v>26</v>
       </c>
-      <c r="M164">
+      <c r="N164">
         <v>0.2857142857142857</v>
       </c>
-      <c r="N164" t="s">
+      <c r="O164" t="s">
         <v>28</v>
       </c>
-      <c r="O164">
+      <c r="P164">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q164" t="b">
@@ -11830,25 +11830,25 @@
       <c r="G165">
         <v>1.778362799058254</v>
       </c>
-      <c r="I165" t="s">
+      <c r="J165" t="s">
         <v>25</v>
       </c>
-      <c r="J165" t="s">
+      <c r="K165" t="s">
         <v>29</v>
       </c>
-      <c r="K165">
+      <c r="L165">
         <v>0.5714285714285714</v>
       </c>
-      <c r="L165" t="s">
+      <c r="M165" t="s">
         <v>29</v>
       </c>
-      <c r="M165">
+      <c r="N165">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N165" t="s">
+      <c r="O165" t="s">
         <v>30</v>
       </c>
-      <c r="O165">
+      <c r="P165">
         <v>0</v>
       </c>
       <c r="Q165" t="b">
@@ -11895,25 +11895,25 @@
       <c r="G166">
         <v>1.778362799058254</v>
       </c>
-      <c r="I166" t="s">
+      <c r="J166" t="s">
         <v>25</v>
       </c>
-      <c r="J166" t="s">
+      <c r="K166" t="s">
         <v>28</v>
       </c>
-      <c r="K166">
+      <c r="L166">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L166" t="s">
-        <v>32</v>
-      </c>
-      <c r="M166">
-        <v>1</v>
-      </c>
-      <c r="N166" t="s">
+      <c r="M166" t="s">
+        <v>32</v>
+      </c>
+      <c r="N166">
+        <v>1</v>
+      </c>
+      <c r="O166" t="s">
         <v>26</v>
       </c>
-      <c r="O166">
+      <c r="P166">
         <v>0.2857142857142857</v>
       </c>
       <c r="Q166" t="b">
@@ -11960,25 +11960,25 @@
       <c r="G167">
         <v>1.778362799058254</v>
       </c>
-      <c r="I167" t="s">
+      <c r="J167" t="s">
         <v>25</v>
       </c>
-      <c r="J167" t="s">
+      <c r="K167" t="s">
         <v>30</v>
       </c>
-      <c r="K167">
-        <v>0</v>
-      </c>
-      <c r="L167" t="s">
-        <v>32</v>
-      </c>
-      <c r="M167">
-        <v>1</v>
-      </c>
-      <c r="N167" t="s">
+      <c r="L167">
+        <v>0</v>
+      </c>
+      <c r="M167" t="s">
+        <v>32</v>
+      </c>
+      <c r="N167">
+        <v>1</v>
+      </c>
+      <c r="O167" t="s">
         <v>26</v>
       </c>
-      <c r="O167">
+      <c r="P167">
         <v>0.2857142857142857</v>
       </c>
       <c r="Q167" t="b">
@@ -12025,25 +12025,25 @@
       <c r="G168">
         <v>1.778362799058254</v>
       </c>
-      <c r="I168" t="s">
+      <c r="J168" t="s">
         <v>25</v>
       </c>
-      <c r="J168" t="s">
+      <c r="K168" t="s">
         <v>27</v>
       </c>
-      <c r="K168">
+      <c r="L168">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L168" t="s">
-        <v>32</v>
-      </c>
-      <c r="M168">
-        <v>1</v>
-      </c>
-      <c r="N168" t="s">
+      <c r="M168" t="s">
+        <v>32</v>
+      </c>
+      <c r="N168">
+        <v>1</v>
+      </c>
+      <c r="O168" t="s">
         <v>28</v>
       </c>
-      <c r="O168">
+      <c r="P168">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q168" t="b">
@@ -12090,25 +12090,25 @@
       <c r="G169">
         <v>1.778362799058254</v>
       </c>
-      <c r="I169" t="s">
+      <c r="J169" t="s">
         <v>25</v>
       </c>
-      <c r="J169" t="s">
+      <c r="K169" t="s">
         <v>28</v>
       </c>
-      <c r="K169">
+      <c r="L169">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L169" t="s">
-        <v>32</v>
-      </c>
-      <c r="M169">
-        <v>1</v>
-      </c>
-      <c r="N169" t="s">
+      <c r="M169" t="s">
+        <v>32</v>
+      </c>
+      <c r="N169">
+        <v>1</v>
+      </c>
+      <c r="O169" t="s">
         <v>28</v>
       </c>
-      <c r="O169">
+      <c r="P169">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q169" t="b">
@@ -12155,25 +12155,25 @@
       <c r="G170">
         <v>1.778362799058254</v>
       </c>
-      <c r="I170" t="s">
+      <c r="J170" t="s">
         <v>25</v>
       </c>
-      <c r="J170" t="s">
+      <c r="K170" t="s">
         <v>30</v>
       </c>
-      <c r="K170">
-        <v>0</v>
-      </c>
-      <c r="L170" t="s">
-        <v>32</v>
-      </c>
-      <c r="M170">
-        <v>1</v>
-      </c>
-      <c r="N170" t="s">
+      <c r="L170">
+        <v>0</v>
+      </c>
+      <c r="M170" t="s">
+        <v>32</v>
+      </c>
+      <c r="N170">
+        <v>1</v>
+      </c>
+      <c r="O170" t="s">
         <v>26</v>
       </c>
-      <c r="O170">
+      <c r="P170">
         <v>0.2857142857142857</v>
       </c>
       <c r="Q170" t="b">
@@ -12220,25 +12220,25 @@
       <c r="G171">
         <v>1.778362799058254</v>
       </c>
-      <c r="I171" t="s">
+      <c r="J171" t="s">
         <v>25</v>
       </c>
-      <c r="J171" t="s">
+      <c r="K171" t="s">
         <v>26</v>
       </c>
-      <c r="K171">
+      <c r="L171">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L171" t="s">
+      <c r="M171" t="s">
         <v>28</v>
       </c>
-      <c r="M171">
+      <c r="N171">
         <v>0.1428571428571428</v>
       </c>
-      <c r="N171" t="s">
+      <c r="O171" t="s">
         <v>30</v>
       </c>
-      <c r="O171">
+      <c r="P171">
         <v>0</v>
       </c>
       <c r="Q171" t="b">
@@ -12285,25 +12285,25 @@
       <c r="G172">
         <v>1.778362799058254</v>
       </c>
-      <c r="I172" t="s">
+      <c r="J172" t="s">
         <v>25</v>
       </c>
-      <c r="J172" t="s">
+      <c r="K172" t="s">
         <v>30</v>
       </c>
-      <c r="K172">
-        <v>0</v>
-      </c>
-      <c r="L172" t="s">
-        <v>32</v>
-      </c>
-      <c r="M172">
-        <v>1</v>
-      </c>
-      <c r="N172" t="s">
-        <v>32</v>
-      </c>
-      <c r="O172">
+      <c r="L172">
+        <v>0</v>
+      </c>
+      <c r="M172" t="s">
+        <v>32</v>
+      </c>
+      <c r="N172">
+        <v>1</v>
+      </c>
+      <c r="O172" t="s">
+        <v>32</v>
+      </c>
+      <c r="P172">
         <v>1</v>
       </c>
       <c r="Q172" t="b">
@@ -12350,25 +12350,25 @@
       <c r="G173">
         <v>1.778362799058254</v>
       </c>
-      <c r="I173" t="s">
+      <c r="J173" t="s">
         <v>25</v>
       </c>
-      <c r="J173" t="s">
+      <c r="K173" t="s">
         <v>26</v>
       </c>
-      <c r="K173">
+      <c r="L173">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L173" t="s">
+      <c r="M173" t="s">
         <v>31</v>
       </c>
-      <c r="M173">
+      <c r="N173">
         <v>0.7142857142857143</v>
       </c>
-      <c r="N173" t="s">
+      <c r="O173" t="s">
         <v>26</v>
       </c>
-      <c r="O173">
+      <c r="P173">
         <v>0.2857142857142857</v>
       </c>
       <c r="Q173" t="b">
@@ -12415,25 +12415,25 @@
       <c r="G174">
         <v>1.778362799058254</v>
       </c>
-      <c r="I174" t="s">
+      <c r="J174" t="s">
         <v>25</v>
       </c>
-      <c r="J174" t="s">
+      <c r="K174" t="s">
         <v>26</v>
       </c>
-      <c r="K174">
+      <c r="L174">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L174" t="s">
-        <v>32</v>
-      </c>
-      <c r="M174">
-        <v>1</v>
-      </c>
-      <c r="N174" t="s">
+      <c r="M174" t="s">
+        <v>32</v>
+      </c>
+      <c r="N174">
+        <v>1</v>
+      </c>
+      <c r="O174" t="s">
         <v>26</v>
       </c>
-      <c r="O174">
+      <c r="P174">
         <v>0.2857142857142857</v>
       </c>
       <c r="Q174" t="b">
@@ -12480,25 +12480,25 @@
       <c r="G175">
         <v>1.778362799058254</v>
       </c>
-      <c r="I175" t="s">
+      <c r="J175" t="s">
         <v>25</v>
       </c>
-      <c r="J175" t="s">
+      <c r="K175" t="s">
         <v>26</v>
       </c>
-      <c r="K175">
+      <c r="L175">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L175" t="s">
-        <v>32</v>
-      </c>
-      <c r="M175">
-        <v>1</v>
-      </c>
-      <c r="N175" t="s">
+      <c r="M175" t="s">
+        <v>32</v>
+      </c>
+      <c r="N175">
+        <v>1</v>
+      </c>
+      <c r="O175" t="s">
         <v>31</v>
       </c>
-      <c r="O175">
+      <c r="P175">
         <v>0.7142857142857143</v>
       </c>
       <c r="Q175" t="b">
@@ -12545,25 +12545,25 @@
       <c r="G176">
         <v>1.778362799058254</v>
       </c>
-      <c r="I176" t="s">
+      <c r="J176" t="s">
         <v>25</v>
       </c>
-      <c r="J176" t="s">
+      <c r="K176" t="s">
         <v>26</v>
       </c>
-      <c r="K176">
+      <c r="L176">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L176" t="s">
-        <v>32</v>
-      </c>
-      <c r="M176">
-        <v>1</v>
-      </c>
-      <c r="N176" t="s">
+      <c r="M176" t="s">
+        <v>32</v>
+      </c>
+      <c r="N176">
+        <v>1</v>
+      </c>
+      <c r="O176" t="s">
         <v>29</v>
       </c>
-      <c r="O176">
+      <c r="P176">
         <v>0.5714285714285714</v>
       </c>
       <c r="Q176" t="b">
@@ -12610,25 +12610,25 @@
       <c r="G177">
         <v>1.778362799058254</v>
       </c>
-      <c r="I177" t="s">
+      <c r="J177" t="s">
         <v>25</v>
       </c>
-      <c r="J177" t="s">
+      <c r="K177" t="s">
         <v>26</v>
       </c>
-      <c r="K177">
+      <c r="L177">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L177" t="s">
+      <c r="M177" t="s">
         <v>28</v>
       </c>
-      <c r="M177">
+      <c r="N177">
         <v>0.1428571428571428</v>
       </c>
-      <c r="N177" t="s">
+      <c r="O177" t="s">
         <v>30</v>
       </c>
-      <c r="O177">
+      <c r="P177">
         <v>0</v>
       </c>
       <c r="Q177" t="b">
@@ -12675,25 +12675,25 @@
       <c r="G178">
         <v>1.778362799058254</v>
       </c>
-      <c r="I178" t="s">
+      <c r="J178" t="s">
         <v>25</v>
       </c>
-      <c r="J178" t="s">
+      <c r="K178" t="s">
         <v>26</v>
       </c>
-      <c r="K178">
+      <c r="L178">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L178" t="s">
-        <v>32</v>
-      </c>
-      <c r="M178">
-        <v>1</v>
-      </c>
-      <c r="N178" t="s">
+      <c r="M178" t="s">
+        <v>32</v>
+      </c>
+      <c r="N178">
+        <v>1</v>
+      </c>
+      <c r="O178" t="s">
         <v>28</v>
       </c>
-      <c r="O178">
+      <c r="P178">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q178" t="b">
@@ -12740,25 +12740,25 @@
       <c r="G179">
         <v>1.778362799058254</v>
       </c>
-      <c r="I179" t="s">
+      <c r="J179" t="s">
         <v>25</v>
       </c>
-      <c r="J179" t="s">
+      <c r="K179" t="s">
         <v>28</v>
       </c>
-      <c r="K179">
+      <c r="L179">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L179" t="s">
-        <v>32</v>
-      </c>
-      <c r="M179">
-        <v>1</v>
-      </c>
-      <c r="N179" t="s">
+      <c r="M179" t="s">
+        <v>32</v>
+      </c>
+      <c r="N179">
+        <v>1</v>
+      </c>
+      <c r="O179" t="s">
         <v>28</v>
       </c>
-      <c r="O179">
+      <c r="P179">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q179" t="b">
@@ -12805,25 +12805,25 @@
       <c r="G180">
         <v>1.778362799058254</v>
       </c>
-      <c r="I180" t="s">
+      <c r="J180" t="s">
         <v>25</v>
       </c>
-      <c r="J180" t="s">
+      <c r="K180" t="s">
         <v>28</v>
       </c>
-      <c r="K180">
+      <c r="L180">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L180" t="s">
+      <c r="M180" t="s">
         <v>28</v>
       </c>
-      <c r="M180">
+      <c r="N180">
         <v>0.1428571428571428</v>
       </c>
-      <c r="N180" t="s">
+      <c r="O180" t="s">
         <v>30</v>
       </c>
-      <c r="O180">
+      <c r="P180">
         <v>0</v>
       </c>
       <c r="Q180" t="b">
@@ -12870,25 +12870,25 @@
       <c r="G181">
         <v>1.778362799058254</v>
       </c>
-      <c r="I181" t="s">
+      <c r="J181" t="s">
         <v>25</v>
       </c>
-      <c r="J181" t="s">
+      <c r="K181" t="s">
         <v>30</v>
       </c>
-      <c r="K181">
-        <v>0</v>
-      </c>
-      <c r="L181" t="s">
-        <v>32</v>
-      </c>
-      <c r="M181">
-        <v>1</v>
-      </c>
-      <c r="N181" t="s">
+      <c r="L181">
+        <v>0</v>
+      </c>
+      <c r="M181" t="s">
+        <v>32</v>
+      </c>
+      <c r="N181">
+        <v>1</v>
+      </c>
+      <c r="O181" t="s">
         <v>27</v>
       </c>
-      <c r="O181">
+      <c r="P181">
         <v>0.4285714285714285</v>
       </c>
       <c r="Q181" t="b">
@@ -12935,25 +12935,25 @@
       <c r="G182">
         <v>1.778362799058254</v>
       </c>
-      <c r="I182" t="s">
+      <c r="J182" t="s">
         <v>25</v>
       </c>
-      <c r="J182" t="s">
+      <c r="K182" t="s">
         <v>27</v>
       </c>
-      <c r="K182">
+      <c r="L182">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L182" t="s">
-        <v>32</v>
-      </c>
-      <c r="M182">
-        <v>1</v>
-      </c>
-      <c r="N182" t="s">
+      <c r="M182" t="s">
+        <v>32</v>
+      </c>
+      <c r="N182">
+        <v>1</v>
+      </c>
+      <c r="O182" t="s">
         <v>28</v>
       </c>
-      <c r="O182">
+      <c r="P182">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q182" t="b">
@@ -13000,25 +13000,25 @@
       <c r="G183">
         <v>1.778362799058254</v>
       </c>
-      <c r="I183" t="s">
+      <c r="J183" t="s">
         <v>25</v>
       </c>
-      <c r="J183" t="s">
+      <c r="K183" t="s">
         <v>26</v>
       </c>
-      <c r="K183">
+      <c r="L183">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L183" t="s">
+      <c r="M183" t="s">
         <v>27</v>
       </c>
-      <c r="M183">
+      <c r="N183">
         <v>0.4285714285714285</v>
       </c>
-      <c r="N183" t="s">
+      <c r="O183" t="s">
         <v>30</v>
       </c>
-      <c r="O183">
+      <c r="P183">
         <v>0</v>
       </c>
       <c r="Q183" t="b">
@@ -13065,25 +13065,25 @@
       <c r="G184">
         <v>1.778362799058254</v>
       </c>
-      <c r="I184" t="s">
+      <c r="J184" t="s">
         <v>25</v>
       </c>
-      <c r="J184" t="s">
+      <c r="K184" t="s">
         <v>26</v>
       </c>
-      <c r="K184">
+      <c r="L184">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L184" t="s">
-        <v>32</v>
-      </c>
-      <c r="M184">
-        <v>1</v>
-      </c>
-      <c r="N184" t="s">
+      <c r="M184" t="s">
+        <v>32</v>
+      </c>
+      <c r="N184">
+        <v>1</v>
+      </c>
+      <c r="O184" t="s">
         <v>27</v>
       </c>
-      <c r="O184">
+      <c r="P184">
         <v>0.4285714285714285</v>
       </c>
       <c r="Q184" t="b">
@@ -13130,25 +13130,25 @@
       <c r="G185">
         <v>1.778362799058254</v>
       </c>
-      <c r="I185" t="s">
+      <c r="J185" t="s">
         <v>25</v>
       </c>
-      <c r="J185" t="s">
+      <c r="K185" t="s">
         <v>31</v>
       </c>
-      <c r="K185">
+      <c r="L185">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L185" t="s">
-        <v>32</v>
-      </c>
-      <c r="M185">
-        <v>1</v>
-      </c>
-      <c r="N185" t="s">
+      <c r="M185" t="s">
+        <v>32</v>
+      </c>
+      <c r="N185">
+        <v>1</v>
+      </c>
+      <c r="O185" t="s">
         <v>30</v>
       </c>
-      <c r="O185">
+      <c r="P185">
         <v>0</v>
       </c>
       <c r="Q185" t="b">
@@ -13195,25 +13195,25 @@
       <c r="G186">
         <v>1.920905978863135</v>
       </c>
-      <c r="I186" t="s">
+      <c r="J186" t="s">
         <v>25</v>
       </c>
-      <c r="J186" t="s">
+      <c r="K186" t="s">
         <v>28</v>
       </c>
-      <c r="K186">
+      <c r="L186">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L186" t="s">
-        <v>32</v>
-      </c>
-      <c r="M186">
-        <v>1</v>
-      </c>
-      <c r="N186" t="s">
+      <c r="M186" t="s">
+        <v>32</v>
+      </c>
+      <c r="N186">
+        <v>1</v>
+      </c>
+      <c r="O186" t="s">
         <v>29</v>
       </c>
-      <c r="O186">
+      <c r="P186">
         <v>0.5714285714285714</v>
       </c>
       <c r="Q186" t="b">
@@ -13260,25 +13260,25 @@
       <c r="G187">
         <v>1.920905978863135</v>
       </c>
-      <c r="I187" t="s">
+      <c r="J187" t="s">
         <v>25</v>
       </c>
-      <c r="J187" t="s">
+      <c r="K187" t="s">
         <v>28</v>
       </c>
-      <c r="K187">
+      <c r="L187">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L187" t="s">
-        <v>32</v>
-      </c>
-      <c r="M187">
-        <v>1</v>
-      </c>
-      <c r="N187" t="s">
+      <c r="M187" t="s">
+        <v>32</v>
+      </c>
+      <c r="N187">
+        <v>1</v>
+      </c>
+      <c r="O187" t="s">
         <v>28</v>
       </c>
-      <c r="O187">
+      <c r="P187">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q187" t="b">
@@ -13325,25 +13325,25 @@
       <c r="G188">
         <v>1.920905978863135</v>
       </c>
-      <c r="I188" t="s">
+      <c r="J188" t="s">
         <v>25</v>
       </c>
-      <c r="J188" t="s">
+      <c r="K188" t="s">
         <v>26</v>
       </c>
-      <c r="K188">
+      <c r="L188">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L188" t="s">
-        <v>32</v>
-      </c>
-      <c r="M188">
-        <v>1</v>
-      </c>
-      <c r="N188" t="s">
+      <c r="M188" t="s">
+        <v>32</v>
+      </c>
+      <c r="N188">
+        <v>1</v>
+      </c>
+      <c r="O188" t="s">
         <v>27</v>
       </c>
-      <c r="O188">
+      <c r="P188">
         <v>0.4285714285714285</v>
       </c>
       <c r="Q188" t="b">
@@ -13390,25 +13390,25 @@
       <c r="G189">
         <v>1.920905978863135</v>
       </c>
-      <c r="I189" t="s">
+      <c r="J189" t="s">
         <v>25</v>
       </c>
-      <c r="J189" t="s">
+      <c r="K189" t="s">
         <v>28</v>
       </c>
-      <c r="K189">
+      <c r="L189">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L189" t="s">
-        <v>32</v>
-      </c>
-      <c r="M189">
-        <v>1</v>
-      </c>
-      <c r="N189" t="s">
+      <c r="M189" t="s">
+        <v>32</v>
+      </c>
+      <c r="N189">
+        <v>1</v>
+      </c>
+      <c r="O189" t="s">
         <v>26</v>
       </c>
-      <c r="O189">
+      <c r="P189">
         <v>0.2857142857142857</v>
       </c>
       <c r="Q189" t="b">
@@ -13455,25 +13455,25 @@
       <c r="G190">
         <v>1.920905978863135</v>
       </c>
-      <c r="I190" t="s">
+      <c r="J190" t="s">
         <v>25</v>
       </c>
-      <c r="J190" t="s">
+      <c r="K190" t="s">
         <v>26</v>
       </c>
-      <c r="K190">
+      <c r="L190">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L190" t="s">
-        <v>32</v>
-      </c>
-      <c r="M190">
-        <v>1</v>
-      </c>
-      <c r="N190" t="s">
+      <c r="M190" t="s">
+        <v>32</v>
+      </c>
+      <c r="N190">
+        <v>1</v>
+      </c>
+      <c r="O190" t="s">
         <v>26</v>
       </c>
-      <c r="O190">
+      <c r="P190">
         <v>0.2857142857142857</v>
       </c>
       <c r="Q190" t="b">
@@ -13520,25 +13520,25 @@
       <c r="G191">
         <v>1.920905978863135</v>
       </c>
-      <c r="I191" t="s">
+      <c r="J191" t="s">
         <v>25</v>
       </c>
-      <c r="J191" t="s">
+      <c r="K191" t="s">
         <v>30</v>
       </c>
-      <c r="K191">
-        <v>0</v>
-      </c>
-      <c r="L191" t="s">
-        <v>32</v>
-      </c>
-      <c r="M191">
-        <v>1</v>
-      </c>
-      <c r="N191" t="s">
+      <c r="L191">
+        <v>0</v>
+      </c>
+      <c r="M191" t="s">
+        <v>32</v>
+      </c>
+      <c r="N191">
+        <v>1</v>
+      </c>
+      <c r="O191" t="s">
         <v>26</v>
       </c>
-      <c r="O191">
+      <c r="P191">
         <v>0.2857142857142857</v>
       </c>
       <c r="Q191" t="b">
@@ -13585,25 +13585,25 @@
       <c r="G192">
         <v>1.920905978863135</v>
       </c>
-      <c r="I192" t="s">
+      <c r="J192" t="s">
         <v>25</v>
       </c>
-      <c r="J192" t="s">
+      <c r="K192" t="s">
         <v>30</v>
       </c>
-      <c r="K192">
-        <v>0</v>
-      </c>
-      <c r="L192" t="s">
-        <v>32</v>
-      </c>
-      <c r="M192">
-        <v>1</v>
-      </c>
-      <c r="N192" t="s">
-        <v>32</v>
-      </c>
-      <c r="O192">
+      <c r="L192">
+        <v>0</v>
+      </c>
+      <c r="M192" t="s">
+        <v>32</v>
+      </c>
+      <c r="N192">
+        <v>1</v>
+      </c>
+      <c r="O192" t="s">
+        <v>32</v>
+      </c>
+      <c r="P192">
         <v>1</v>
       </c>
       <c r="Q192" t="b">
@@ -13650,25 +13650,25 @@
       <c r="G193">
         <v>1.920905978863135</v>
       </c>
-      <c r="I193" t="s">
+      <c r="J193" t="s">
         <v>25</v>
       </c>
-      <c r="J193" t="s">
+      <c r="K193" t="s">
         <v>26</v>
       </c>
-      <c r="K193">
+      <c r="L193">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L193" t="s">
+      <c r="M193" t="s">
         <v>30</v>
       </c>
-      <c r="M193">
-        <v>0</v>
-      </c>
-      <c r="N193" t="s">
+      <c r="N193">
+        <v>0</v>
+      </c>
+      <c r="O193" t="s">
         <v>30</v>
       </c>
-      <c r="O193">
+      <c r="P193">
         <v>0</v>
       </c>
       <c r="Q193" t="b">
@@ -13715,25 +13715,25 @@
       <c r="G194">
         <v>1.920905978863135</v>
       </c>
-      <c r="I194" t="s">
+      <c r="J194" t="s">
         <v>25</v>
       </c>
-      <c r="J194" t="s">
+      <c r="K194" t="s">
         <v>26</v>
       </c>
-      <c r="K194">
+      <c r="L194">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L194" t="s">
+      <c r="M194" t="s">
         <v>33</v>
       </c>
-      <c r="M194">
+      <c r="N194">
         <v>0.8571428571428571</v>
       </c>
-      <c r="N194" t="s">
+      <c r="O194" t="s">
         <v>30</v>
       </c>
-      <c r="O194">
+      <c r="P194">
         <v>0</v>
       </c>
       <c r="Q194" t="b">
@@ -13780,25 +13780,25 @@
       <c r="G195">
         <v>1.920905978863135</v>
       </c>
-      <c r="I195" t="s">
+      <c r="J195" t="s">
         <v>25</v>
       </c>
-      <c r="J195" t="s">
+      <c r="K195" t="s">
         <v>26</v>
       </c>
-      <c r="K195">
+      <c r="L195">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L195" t="s">
-        <v>32</v>
-      </c>
-      <c r="M195">
-        <v>1</v>
-      </c>
-      <c r="N195" t="s">
+      <c r="M195" t="s">
+        <v>32</v>
+      </c>
+      <c r="N195">
+        <v>1</v>
+      </c>
+      <c r="O195" t="s">
         <v>31</v>
       </c>
-      <c r="O195">
+      <c r="P195">
         <v>0.7142857142857143</v>
       </c>
       <c r="Q195" t="b">
@@ -13845,25 +13845,25 @@
       <c r="G196">
         <v>1.920905978863135</v>
       </c>
-      <c r="I196" t="s">
+      <c r="J196" t="s">
         <v>25</v>
       </c>
-      <c r="J196" t="s">
+      <c r="K196" t="s">
         <v>28</v>
       </c>
-      <c r="K196">
+      <c r="L196">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L196" t="s">
+      <c r="M196" t="s">
         <v>28</v>
       </c>
-      <c r="M196">
+      <c r="N196">
         <v>0.1428571428571428</v>
       </c>
-      <c r="N196" t="s">
+      <c r="O196" t="s">
         <v>30</v>
       </c>
-      <c r="O196">
+      <c r="P196">
         <v>0</v>
       </c>
       <c r="Q196" t="b">
@@ -13910,25 +13910,25 @@
       <c r="G197">
         <v>1.920905978863135</v>
       </c>
-      <c r="I197" t="s">
+      <c r="J197" t="s">
         <v>25</v>
       </c>
-      <c r="J197" t="s">
+      <c r="K197" t="s">
         <v>30</v>
       </c>
-      <c r="K197">
-        <v>0</v>
-      </c>
-      <c r="L197" t="s">
-        <v>32</v>
-      </c>
-      <c r="M197">
-        <v>1</v>
-      </c>
-      <c r="N197" t="s">
+      <c r="L197">
+        <v>0</v>
+      </c>
+      <c r="M197" t="s">
+        <v>32</v>
+      </c>
+      <c r="N197">
+        <v>1</v>
+      </c>
+      <c r="O197" t="s">
         <v>33</v>
       </c>
-      <c r="O197">
+      <c r="P197">
         <v>0.8571428571428571</v>
       </c>
       <c r="Q197" t="b">
@@ -13975,25 +13975,25 @@
       <c r="G198">
         <v>1.920905978863135</v>
       </c>
-      <c r="I198" t="s">
+      <c r="J198" t="s">
         <v>25</v>
       </c>
-      <c r="J198" t="s">
+      <c r="K198" t="s">
         <v>27</v>
       </c>
-      <c r="K198">
+      <c r="L198">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L198" t="s">
+      <c r="M198" t="s">
         <v>30</v>
       </c>
-      <c r="M198">
-        <v>0</v>
-      </c>
-      <c r="N198" t="s">
+      <c r="N198">
+        <v>0</v>
+      </c>
+      <c r="O198" t="s">
         <v>30</v>
       </c>
-      <c r="O198">
+      <c r="P198">
         <v>0</v>
       </c>
       <c r="Q198" t="b">
@@ -14040,25 +14040,25 @@
       <c r="G199">
         <v>1.920905978863135</v>
       </c>
-      <c r="I199" t="s">
+      <c r="J199" t="s">
         <v>25</v>
       </c>
-      <c r="J199" t="s">
+      <c r="K199" t="s">
         <v>28</v>
       </c>
-      <c r="K199">
+      <c r="L199">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L199" t="s">
-        <v>32</v>
-      </c>
-      <c r="M199">
-        <v>1</v>
-      </c>
-      <c r="N199" t="s">
+      <c r="M199" t="s">
+        <v>32</v>
+      </c>
+      <c r="N199">
+        <v>1</v>
+      </c>
+      <c r="O199" t="s">
         <v>30</v>
       </c>
-      <c r="O199">
+      <c r="P199">
         <v>0</v>
       </c>
       <c r="Q199" t="b">
@@ -14105,25 +14105,25 @@
       <c r="G200">
         <v>1.920905978863135</v>
       </c>
-      <c r="I200" t="s">
+      <c r="J200" t="s">
         <v>25</v>
       </c>
-      <c r="J200" t="s">
+      <c r="K200" t="s">
         <v>30</v>
       </c>
-      <c r="K200">
-        <v>0</v>
-      </c>
-      <c r="L200" t="s">
-        <v>32</v>
-      </c>
-      <c r="M200">
-        <v>1</v>
-      </c>
-      <c r="N200" t="s">
-        <v>32</v>
-      </c>
-      <c r="O200">
+      <c r="L200">
+        <v>0</v>
+      </c>
+      <c r="M200" t="s">
+        <v>32</v>
+      </c>
+      <c r="N200">
+        <v>1</v>
+      </c>
+      <c r="O200" t="s">
+        <v>32</v>
+      </c>
+      <c r="P200">
         <v>1</v>
       </c>
       <c r="Q200" t="b">
@@ -14170,25 +14170,25 @@
       <c r="G201">
         <v>1.920905978863135</v>
       </c>
-      <c r="I201" t="s">
+      <c r="J201" t="s">
         <v>25</v>
       </c>
-      <c r="J201" t="s">
+      <c r="K201" t="s">
         <v>30</v>
       </c>
-      <c r="K201">
-        <v>0</v>
-      </c>
-      <c r="L201" t="s">
-        <v>32</v>
-      </c>
-      <c r="M201">
-        <v>1</v>
-      </c>
-      <c r="N201" t="s">
+      <c r="L201">
+        <v>0</v>
+      </c>
+      <c r="M201" t="s">
+        <v>32</v>
+      </c>
+      <c r="N201">
+        <v>1</v>
+      </c>
+      <c r="O201" t="s">
         <v>27</v>
       </c>
-      <c r="O201">
+      <c r="P201">
         <v>0.4285714285714285</v>
       </c>
       <c r="Q201" t="b">
@@ -14235,25 +14235,25 @@
       <c r="G202">
         <v>1.920905978863135</v>
       </c>
-      <c r="I202" t="s">
+      <c r="J202" t="s">
         <v>25</v>
       </c>
-      <c r="J202" t="s">
+      <c r="K202" t="s">
         <v>28</v>
       </c>
-      <c r="K202">
+      <c r="L202">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L202" t="s">
+      <c r="M202" t="s">
         <v>29</v>
       </c>
-      <c r="M202">
+      <c r="N202">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N202" t="s">
+      <c r="O202" t="s">
         <v>30</v>
       </c>
-      <c r="O202">
+      <c r="P202">
         <v>0</v>
       </c>
       <c r="Q202" t="b">
@@ -14300,25 +14300,25 @@
       <c r="G203">
         <v>1.920905978863135</v>
       </c>
-      <c r="I203" t="s">
+      <c r="J203" t="s">
         <v>25</v>
       </c>
-      <c r="J203" t="s">
+      <c r="K203" t="s">
         <v>28</v>
       </c>
-      <c r="K203">
+      <c r="L203">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L203" t="s">
-        <v>32</v>
-      </c>
-      <c r="M203">
-        <v>1</v>
-      </c>
-      <c r="N203" t="s">
+      <c r="M203" t="s">
+        <v>32</v>
+      </c>
+      <c r="N203">
+        <v>1</v>
+      </c>
+      <c r="O203" t="s">
         <v>33</v>
       </c>
-      <c r="O203">
+      <c r="P203">
         <v>0.8571428571428571</v>
       </c>
       <c r="Q203" t="b">
@@ -14365,25 +14365,25 @@
       <c r="G204">
         <v>1.920905978863135</v>
       </c>
-      <c r="I204" t="s">
+      <c r="J204" t="s">
         <v>25</v>
       </c>
-      <c r="J204" t="s">
+      <c r="K204" t="s">
         <v>30</v>
       </c>
-      <c r="K204">
-        <v>0</v>
-      </c>
-      <c r="L204" t="s">
-        <v>32</v>
-      </c>
-      <c r="M204">
-        <v>1</v>
-      </c>
-      <c r="N204" t="s">
+      <c r="L204">
+        <v>0</v>
+      </c>
+      <c r="M204" t="s">
+        <v>32</v>
+      </c>
+      <c r="N204">
+        <v>1</v>
+      </c>
+      <c r="O204" t="s">
         <v>27</v>
       </c>
-      <c r="O204">
+      <c r="P204">
         <v>0.4285714285714285</v>
       </c>
       <c r="Q204" t="b">
@@ -14430,25 +14430,25 @@
       <c r="G205">
         <v>1.920905978863135</v>
       </c>
-      <c r="I205" t="s">
+      <c r="J205" t="s">
         <v>25</v>
       </c>
-      <c r="J205" t="s">
+      <c r="K205" t="s">
         <v>26</v>
       </c>
-      <c r="K205">
+      <c r="L205">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L205" t="s">
-        <v>32</v>
-      </c>
-      <c r="M205">
-        <v>1</v>
-      </c>
-      <c r="N205" t="s">
+      <c r="M205" t="s">
+        <v>32</v>
+      </c>
+      <c r="N205">
+        <v>1</v>
+      </c>
+      <c r="O205" t="s">
         <v>27</v>
       </c>
-      <c r="O205">
+      <c r="P205">
         <v>0.4285714285714285</v>
       </c>
       <c r="Q205" t="b">
@@ -14495,25 +14495,25 @@
       <c r="G206">
         <v>1.920905978863135</v>
       </c>
-      <c r="I206" t="s">
+      <c r="J206" t="s">
         <v>25</v>
       </c>
-      <c r="J206" t="s">
+      <c r="K206" t="s">
         <v>26</v>
       </c>
-      <c r="K206">
+      <c r="L206">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L206" t="s">
-        <v>32</v>
-      </c>
-      <c r="M206">
-        <v>1</v>
-      </c>
-      <c r="N206" t="s">
+      <c r="M206" t="s">
+        <v>32</v>
+      </c>
+      <c r="N206">
+        <v>1</v>
+      </c>
+      <c r="O206" t="s">
         <v>31</v>
       </c>
-      <c r="O206">
+      <c r="P206">
         <v>0.7142857142857143</v>
       </c>
       <c r="Q206" t="b">
@@ -14560,25 +14560,25 @@
       <c r="G207">
         <v>1.920905978863135</v>
       </c>
-      <c r="I207" t="s">
+      <c r="J207" t="s">
         <v>25</v>
       </c>
-      <c r="J207" t="s">
+      <c r="K207" t="s">
         <v>30</v>
       </c>
-      <c r="K207">
-        <v>0</v>
-      </c>
-      <c r="L207" t="s">
+      <c r="L207">
+        <v>0</v>
+      </c>
+      <c r="M207" t="s">
         <v>29</v>
       </c>
-      <c r="M207">
+      <c r="N207">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N207" t="s">
+      <c r="O207" t="s">
         <v>30</v>
       </c>
-      <c r="O207">
+      <c r="P207">
         <v>0</v>
       </c>
       <c r="Q207" t="b">
@@ -14625,25 +14625,25 @@
       <c r="G208">
         <v>1.920905978863135</v>
       </c>
-      <c r="I208" t="s">
+      <c r="J208" t="s">
         <v>25</v>
       </c>
-      <c r="J208" t="s">
+      <c r="K208" t="s">
         <v>26</v>
       </c>
-      <c r="K208">
+      <c r="L208">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L208" t="s">
-        <v>32</v>
-      </c>
-      <c r="M208">
-        <v>1</v>
-      </c>
-      <c r="N208" t="s">
+      <c r="M208" t="s">
+        <v>32</v>
+      </c>
+      <c r="N208">
+        <v>1</v>
+      </c>
+      <c r="O208" t="s">
         <v>28</v>
       </c>
-      <c r="O208">
+      <c r="P208">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q208" t="b">
@@ -14690,25 +14690,25 @@
       <c r="G209">
         <v>1.920905978863135</v>
       </c>
-      <c r="I209" t="s">
+      <c r="J209" t="s">
         <v>25</v>
       </c>
-      <c r="J209" t="s">
+      <c r="K209" t="s">
         <v>30</v>
       </c>
-      <c r="K209">
-        <v>0</v>
-      </c>
-      <c r="L209" t="s">
-        <v>32</v>
-      </c>
-      <c r="M209">
-        <v>1</v>
-      </c>
-      <c r="N209" t="s">
-        <v>32</v>
-      </c>
-      <c r="O209">
+      <c r="L209">
+        <v>0</v>
+      </c>
+      <c r="M209" t="s">
+        <v>32</v>
+      </c>
+      <c r="N209">
+        <v>1</v>
+      </c>
+      <c r="O209" t="s">
+        <v>32</v>
+      </c>
+      <c r="P209">
         <v>1</v>
       </c>
       <c r="Q209" t="b">
@@ -14755,25 +14755,25 @@
       <c r="G210">
         <v>1.920905978863135</v>
       </c>
-      <c r="I210" t="s">
+      <c r="J210" t="s">
         <v>25</v>
       </c>
-      <c r="J210" t="s">
+      <c r="K210" t="s">
         <v>26</v>
       </c>
-      <c r="K210">
+      <c r="L210">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L210" t="s">
+      <c r="M210" t="s">
         <v>30</v>
       </c>
-      <c r="M210">
-        <v>0</v>
-      </c>
-      <c r="N210" t="s">
+      <c r="N210">
+        <v>0</v>
+      </c>
+      <c r="O210" t="s">
         <v>30</v>
       </c>
-      <c r="O210">
+      <c r="P210">
         <v>0</v>
       </c>
       <c r="Q210" t="b">
@@ -14820,25 +14820,25 @@
       <c r="G211">
         <v>1.920905978863135</v>
       </c>
-      <c r="I211" t="s">
+      <c r="J211" t="s">
         <v>25</v>
       </c>
-      <c r="J211" t="s">
+      <c r="K211" t="s">
         <v>30</v>
       </c>
-      <c r="K211">
-        <v>0</v>
-      </c>
-      <c r="L211" t="s">
+      <c r="L211">
+        <v>0</v>
+      </c>
+      <c r="M211" t="s">
         <v>29</v>
       </c>
-      <c r="M211">
+      <c r="N211">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N211" t="s">
+      <c r="O211" t="s">
         <v>28</v>
       </c>
-      <c r="O211">
+      <c r="P211">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q211" t="b">
@@ -14885,25 +14885,25 @@
       <c r="G212">
         <v>1.920905978863135</v>
       </c>
-      <c r="I212" t="s">
+      <c r="J212" t="s">
         <v>25</v>
       </c>
-      <c r="J212" t="s">
+      <c r="K212" t="s">
         <v>28</v>
       </c>
-      <c r="K212">
+      <c r="L212">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L212" t="s">
-        <v>32</v>
-      </c>
-      <c r="M212">
-        <v>1</v>
-      </c>
-      <c r="N212" t="s">
+      <c r="M212" t="s">
+        <v>32</v>
+      </c>
+      <c r="N212">
+        <v>1</v>
+      </c>
+      <c r="O212" t="s">
         <v>27</v>
       </c>
-      <c r="O212">
+      <c r="P212">
         <v>0.4285714285714285</v>
       </c>
       <c r="Q212" t="b">
@@ -14950,25 +14950,25 @@
       <c r="G213">
         <v>1.920905978863135</v>
       </c>
-      <c r="I213" t="s">
+      <c r="J213" t="s">
         <v>25</v>
       </c>
-      <c r="J213" t="s">
+      <c r="K213" t="s">
         <v>26</v>
       </c>
-      <c r="K213">
+      <c r="L213">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L213" t="s">
+      <c r="M213" t="s">
         <v>31</v>
       </c>
-      <c r="M213">
+      <c r="N213">
         <v>0.7142857142857143</v>
       </c>
-      <c r="N213" t="s">
+      <c r="O213" t="s">
         <v>30</v>
       </c>
-      <c r="O213">
+      <c r="P213">
         <v>0</v>
       </c>
       <c r="Q213" t="b">
@@ -15015,25 +15015,25 @@
       <c r="G214">
         <v>2.115454798598829</v>
       </c>
-      <c r="I214" t="s">
+      <c r="J214" t="s">
         <v>25</v>
       </c>
-      <c r="J214" t="s">
+      <c r="K214" t="s">
         <v>30</v>
       </c>
-      <c r="K214">
-        <v>0</v>
-      </c>
-      <c r="L214" t="s">
-        <v>32</v>
-      </c>
-      <c r="M214">
-        <v>1</v>
-      </c>
-      <c r="N214" t="s">
-        <v>32</v>
-      </c>
-      <c r="O214">
+      <c r="L214">
+        <v>0</v>
+      </c>
+      <c r="M214" t="s">
+        <v>32</v>
+      </c>
+      <c r="N214">
+        <v>1</v>
+      </c>
+      <c r="O214" t="s">
+        <v>32</v>
+      </c>
+      <c r="P214">
         <v>1</v>
       </c>
       <c r="Q214" t="b">
@@ -15080,25 +15080,25 @@
       <c r="G215">
         <v>2.115454798598829</v>
       </c>
-      <c r="I215" t="s">
+      <c r="J215" t="s">
         <v>25</v>
       </c>
-      <c r="J215" t="s">
+      <c r="K215" t="s">
         <v>28</v>
       </c>
-      <c r="K215">
+      <c r="L215">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L215" t="s">
+      <c r="M215" t="s">
         <v>26</v>
       </c>
-      <c r="M215">
+      <c r="N215">
         <v>0.2857142857142857</v>
       </c>
-      <c r="N215" t="s">
+      <c r="O215" t="s">
         <v>30</v>
       </c>
-      <c r="O215">
+      <c r="P215">
         <v>0</v>
       </c>
       <c r="Q215" t="b">
@@ -15145,25 +15145,25 @@
       <c r="G216">
         <v>2.115454798598829</v>
       </c>
-      <c r="I216" t="s">
+      <c r="J216" t="s">
         <v>25</v>
       </c>
-      <c r="J216" t="s">
+      <c r="K216" t="s">
         <v>26</v>
       </c>
-      <c r="K216">
+      <c r="L216">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L216" t="s">
-        <v>32</v>
-      </c>
-      <c r="M216">
-        <v>1</v>
-      </c>
-      <c r="N216" t="s">
+      <c r="M216" t="s">
+        <v>32</v>
+      </c>
+      <c r="N216">
+        <v>1</v>
+      </c>
+      <c r="O216" t="s">
         <v>28</v>
       </c>
-      <c r="O216">
+      <c r="P216">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q216" t="b">
@@ -15210,25 +15210,25 @@
       <c r="G217">
         <v>2.115454798598829</v>
       </c>
-      <c r="I217" t="s">
+      <c r="J217" t="s">
         <v>25</v>
       </c>
-      <c r="J217" t="s">
+      <c r="K217" t="s">
         <v>26</v>
       </c>
-      <c r="K217">
+      <c r="L217">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L217" t="s">
-        <v>32</v>
-      </c>
-      <c r="M217">
-        <v>1</v>
-      </c>
-      <c r="N217" t="s">
+      <c r="M217" t="s">
+        <v>32</v>
+      </c>
+      <c r="N217">
+        <v>1</v>
+      </c>
+      <c r="O217" t="s">
         <v>27</v>
       </c>
-      <c r="O217">
+      <c r="P217">
         <v>0.4285714285714285</v>
       </c>
       <c r="Q217" t="b">
@@ -15275,25 +15275,25 @@
       <c r="G218">
         <v>2.115454798598829</v>
       </c>
-      <c r="I218" t="s">
+      <c r="J218" t="s">
         <v>25</v>
       </c>
-      <c r="J218" t="s">
+      <c r="K218" t="s">
         <v>28</v>
       </c>
-      <c r="K218">
+      <c r="L218">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L218" t="s">
-        <v>32</v>
-      </c>
-      <c r="M218">
-        <v>1</v>
-      </c>
-      <c r="N218" t="s">
+      <c r="M218" t="s">
+        <v>32</v>
+      </c>
+      <c r="N218">
+        <v>1</v>
+      </c>
+      <c r="O218" t="s">
         <v>33</v>
       </c>
-      <c r="O218">
+      <c r="P218">
         <v>0.8571428571428571</v>
       </c>
       <c r="Q218" t="b">
@@ -15340,25 +15340,25 @@
       <c r="G219">
         <v>2.115454798598829</v>
       </c>
-      <c r="I219" t="s">
+      <c r="J219" t="s">
         <v>25</v>
       </c>
-      <c r="J219" t="s">
+      <c r="K219" t="s">
         <v>28</v>
       </c>
-      <c r="K219">
+      <c r="L219">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L219" t="s">
-        <v>32</v>
-      </c>
-      <c r="M219">
-        <v>1</v>
-      </c>
-      <c r="N219" t="s">
+      <c r="M219" t="s">
+        <v>32</v>
+      </c>
+      <c r="N219">
+        <v>1</v>
+      </c>
+      <c r="O219" t="s">
         <v>30</v>
       </c>
-      <c r="O219">
+      <c r="P219">
         <v>0</v>
       </c>
       <c r="Q219" t="b">
@@ -15405,25 +15405,25 @@
       <c r="G220">
         <v>2.115454798598829</v>
       </c>
-      <c r="I220" t="s">
+      <c r="J220" t="s">
         <v>25</v>
       </c>
-      <c r="J220" t="s">
+      <c r="K220" t="s">
         <v>28</v>
       </c>
-      <c r="K220">
+      <c r="L220">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L220" t="s">
-        <v>32</v>
-      </c>
-      <c r="M220">
-        <v>1</v>
-      </c>
-      <c r="N220" t="s">
+      <c r="M220" t="s">
+        <v>32</v>
+      </c>
+      <c r="N220">
+        <v>1</v>
+      </c>
+      <c r="O220" t="s">
         <v>33</v>
       </c>
-      <c r="O220">
+      <c r="P220">
         <v>0.8571428571428571</v>
       </c>
       <c r="Q220" t="b">
@@ -15470,25 +15470,25 @@
       <c r="G221">
         <v>2.115454798598829</v>
       </c>
-      <c r="I221" t="s">
+      <c r="J221" t="s">
         <v>25</v>
       </c>
-      <c r="J221" t="s">
+      <c r="K221" t="s">
         <v>30</v>
       </c>
-      <c r="K221">
-        <v>0</v>
-      </c>
-      <c r="L221" t="s">
+      <c r="L221">
+        <v>0</v>
+      </c>
+      <c r="M221" t="s">
         <v>27</v>
       </c>
-      <c r="M221">
+      <c r="N221">
         <v>0.4285714285714285</v>
       </c>
-      <c r="N221" t="s">
+      <c r="O221" t="s">
         <v>30</v>
       </c>
-      <c r="O221">
+      <c r="P221">
         <v>0</v>
       </c>
       <c r="Q221" t="b">
@@ -15535,25 +15535,25 @@
       <c r="G222">
         <v>2.115454798598829</v>
       </c>
-      <c r="I222" t="s">
+      <c r="J222" t="s">
         <v>25</v>
       </c>
-      <c r="J222" t="s">
+      <c r="K222" t="s">
         <v>30</v>
       </c>
-      <c r="K222">
-        <v>0</v>
-      </c>
-      <c r="L222" t="s">
+      <c r="L222">
+        <v>0</v>
+      </c>
+      <c r="M222" t="s">
         <v>29</v>
       </c>
-      <c r="M222">
+      <c r="N222">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N222" t="s">
+      <c r="O222" t="s">
         <v>30</v>
       </c>
-      <c r="O222">
+      <c r="P222">
         <v>0</v>
       </c>
       <c r="Q222" t="b">
@@ -15600,25 +15600,25 @@
       <c r="G223">
         <v>2.115454798598829</v>
       </c>
-      <c r="I223" t="s">
+      <c r="J223" t="s">
         <v>25</v>
       </c>
-      <c r="J223" t="s">
+      <c r="K223" t="s">
         <v>30</v>
       </c>
-      <c r="K223">
-        <v>0</v>
-      </c>
-      <c r="L223" t="s">
+      <c r="L223">
+        <v>0</v>
+      </c>
+      <c r="M223" t="s">
         <v>31</v>
       </c>
-      <c r="M223">
+      <c r="N223">
         <v>0.7142857142857143</v>
       </c>
-      <c r="N223" t="s">
+      <c r="O223" t="s">
         <v>30</v>
       </c>
-      <c r="O223">
+      <c r="P223">
         <v>0</v>
       </c>
       <c r="Q223" t="b">

--- a/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_heart.xlsx
+++ b/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_heart.xlsx
@@ -600,10 +600,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2">
         <v>7</v>
@@ -671,10 +671,10 @@
         <v>0</v>
       </c>
       <c r="R3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3">
         <v>7</v>
@@ -742,10 +742,10 @@
         <v>0</v>
       </c>
       <c r="R4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4">
         <v>7</v>
@@ -881,7 +881,7 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="Q6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
@@ -955,10 +955,10 @@
         <v>0</v>
       </c>
       <c r="R7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7">
         <v>7</v>
@@ -984,7 +984,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1023,10 +1023,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="b">
         <v>1</v>
@@ -1035,7 +1035,7 @@
         <v>7</v>
       </c>
       <c r="U8">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="V8">
         <v>7</v>
@@ -1094,13 +1094,13 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="Q9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9">
         <v>7</v>
@@ -1236,13 +1236,13 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="Q11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11">
         <v>7</v>
@@ -1310,10 +1310,10 @@
         <v>0</v>
       </c>
       <c r="R12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12">
         <v>7</v>
@@ -1378,13 +1378,13 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="Q13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13">
         <v>7</v>
@@ -1520,7 +1520,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="R16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="b">
         <v>1</v>
@@ -1662,13 +1662,13 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="Q17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17">
         <v>7</v>
@@ -1733,13 +1733,13 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="Q18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18">
         <v>7</v>
@@ -1875,13 +1875,13 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="Q20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
       </c>
       <c r="S20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20">
         <v>5</v>
@@ -2020,10 +2020,10 @@
         <v>0</v>
       </c>
       <c r="R22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22">
         <v>7</v>
@@ -2091,7 +2091,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="b">
         <v>1</v>
@@ -2162,10 +2162,10 @@
         <v>0</v>
       </c>
       <c r="R24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24">
         <v>7</v>
@@ -2230,13 +2230,13 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="Q25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25">
         <v>7</v>
@@ -2304,7 +2304,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="b">
         <v>1</v>
@@ -2375,10 +2375,10 @@
         <v>0</v>
       </c>
       <c r="R27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27">
         <v>7</v>
@@ -2449,7 +2449,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28">
         <v>5</v>
@@ -2517,7 +2517,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="b">
         <v>1</v>
@@ -2588,10 +2588,10 @@
         <v>0</v>
       </c>
       <c r="R30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30">
         <v>7</v>
@@ -2730,10 +2730,10 @@
         <v>0</v>
       </c>
       <c r="R32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32">
         <v>7</v>
@@ -2801,7 +2801,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="b">
         <v>1</v>
@@ -2869,13 +2869,13 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="Q34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T34">
         <v>7</v>
@@ -2943,10 +2943,10 @@
         <v>0</v>
       </c>
       <c r="R35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35">
         <v>7</v>
@@ -3014,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="R36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="b">
         <v>1</v>
@@ -3082,7 +3082,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
@@ -3156,7 +3156,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" t="b">
         <v>1</v>
@@ -3227,10 +3227,10 @@
         <v>0</v>
       </c>
       <c r="R39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T39">
         <v>7</v>
@@ -3369,10 +3369,10 @@
         <v>0</v>
       </c>
       <c r="R41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T41">
         <v>7</v>
@@ -3440,10 +3440,10 @@
         <v>0</v>
       </c>
       <c r="R42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T42">
         <v>7</v>
@@ -3511,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="R43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="b">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0.7142857142857143</v>
       </c>
       <c r="Q44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T44">
         <v>7</v>
@@ -3650,13 +3650,13 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="Q45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T45">
         <v>7</v>
@@ -3721,7 +3721,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="b">
         <v>0</v>
@@ -3795,10 +3795,10 @@
         <v>0</v>
       </c>
       <c r="R47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T47">
         <v>7</v>
@@ -3863,13 +3863,13 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="Q48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48">
         <v>7</v>
@@ -3934,13 +3934,13 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="Q49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T49">
         <v>7</v>
@@ -4005,13 +4005,13 @@
         <v>0.7142857142857143</v>
       </c>
       <c r="Q50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T50">
         <v>7</v>
@@ -4076,13 +4076,13 @@
         <v>0.7142857142857143</v>
       </c>
       <c r="Q51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T51">
         <v>7</v>
@@ -4218,7 +4218,7 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="Q53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R53" t="b">
         <v>0</v>
@@ -4360,13 +4360,13 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="Q55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T55">
         <v>7</v>
@@ -4434,10 +4434,10 @@
         <v>0</v>
       </c>
       <c r="R56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56">
         <v>7</v>
@@ -4505,7 +4505,7 @@
         <v>0</v>
       </c>
       <c r="R57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S57" t="b">
         <v>1</v>
@@ -4534,7 +4534,7 @@
         <v>2</v>
       </c>
       <c r="D58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58">
         <v>7</v>
@@ -4573,10 +4573,10 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="Q58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S58" t="b">
         <v>1</v>
@@ -4585,7 +4585,7 @@
         <v>7</v>
       </c>
       <c r="U58">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="V58">
         <v>7</v>
@@ -4647,10 +4647,10 @@
         <v>0</v>
       </c>
       <c r="R59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T59">
         <v>7</v>
@@ -4715,7 +4715,7 @@
         <v>0</v>
       </c>
       <c r="Q60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R60" t="b">
         <v>0</v>
@@ -4789,10 +4789,10 @@
         <v>0</v>
       </c>
       <c r="R61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61">
         <v>7</v>
@@ -4857,13 +4857,13 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="Q62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
       <c r="S62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62">
         <v>5</v>
@@ -4928,13 +4928,13 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="Q63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T63">
         <v>7</v>
@@ -4999,13 +4999,13 @@
         <v>0.7142857142857143</v>
       </c>
       <c r="Q64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T64">
         <v>7</v>
@@ -5070,13 +5070,13 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="Q65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T65">
         <v>7</v>
@@ -5141,7 +5141,7 @@
         <v>0</v>
       </c>
       <c r="Q66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
@@ -5173,7 +5173,7 @@
         <v>2</v>
       </c>
       <c r="D67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67">
         <v>7</v>
@@ -5212,10 +5212,10 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="Q67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S67" t="b">
         <v>1</v>
@@ -5224,7 +5224,7 @@
         <v>7</v>
       </c>
       <c r="U67">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V67">
         <v>7</v>
@@ -5244,7 +5244,7 @@
         <v>2</v>
       </c>
       <c r="D68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68">
         <v>7</v>
@@ -5283,10 +5283,10 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="Q68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S68" t="b">
         <v>1</v>
@@ -5295,7 +5295,7 @@
         <v>7</v>
       </c>
       <c r="U68">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="V68">
         <v>7</v>
@@ -5354,7 +5354,7 @@
         <v>0</v>
       </c>
       <c r="Q69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R69" t="b">
         <v>0</v>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="R70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T70">
         <v>7</v>
@@ -5499,7 +5499,7 @@
         <v>0</v>
       </c>
       <c r="R71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S71" t="b">
         <v>1</v>
@@ -5567,7 +5567,7 @@
         <v>0</v>
       </c>
       <c r="Q72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R72" t="b">
         <v>0</v>
@@ -5638,13 +5638,13 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="Q73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T73">
         <v>7</v>
@@ -5670,7 +5670,7 @@
         <v>2</v>
       </c>
       <c r="D74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74">
         <v>7</v>
@@ -5712,7 +5712,7 @@
         <v>1</v>
       </c>
       <c r="R74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S74" t="b">
         <v>1</v>
@@ -5721,7 +5721,7 @@
         <v>7</v>
       </c>
       <c r="U74">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="V74">
         <v>7</v>
@@ -5780,13 +5780,13 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="Q75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T75">
         <v>7</v>
@@ -5812,7 +5812,7 @@
         <v>3</v>
       </c>
       <c r="D76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76">
         <v>7</v>
@@ -5851,10 +5851,10 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="Q76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S76" t="b">
         <v>1</v>
@@ -5863,7 +5863,7 @@
         <v>7</v>
       </c>
       <c r="U76">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="V76">
         <v>7</v>
@@ -5925,10 +5925,10 @@
         <v>0</v>
       </c>
       <c r="R77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T77">
         <v>7</v>
@@ -5993,13 +5993,13 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="Q78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T78">
         <v>7</v>
@@ -6067,10 +6067,10 @@
         <v>0</v>
       </c>
       <c r="R79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T79">
         <v>7</v>
@@ -6138,10 +6138,10 @@
         <v>0</v>
       </c>
       <c r="R80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T80">
         <v>7</v>
@@ -6209,10 +6209,10 @@
         <v>0</v>
       </c>
       <c r="R81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T81">
         <v>7</v>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="R83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S83" t="b">
         <v>1</v>
@@ -6422,10 +6422,10 @@
         <v>0</v>
       </c>
       <c r="R84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T84">
         <v>7</v>
@@ -6490,7 +6490,7 @@
         <v>0</v>
       </c>
       <c r="Q85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R85" t="b">
         <v>0</v>
@@ -6564,10 +6564,10 @@
         <v>0</v>
       </c>
       <c r="R86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T86">
         <v>7</v>
@@ -6664,7 +6664,7 @@
         <v>3</v>
       </c>
       <c r="D88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88">
         <v>7</v>
@@ -6703,10 +6703,10 @@
         <v>0</v>
       </c>
       <c r="Q88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S88" t="b">
         <v>1</v>
@@ -6715,7 +6715,7 @@
         <v>7</v>
       </c>
       <c r="U88">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="V88">
         <v>7</v>
@@ -6777,10 +6777,10 @@
         <v>0</v>
       </c>
       <c r="R89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T89">
         <v>7</v>
@@ -6848,10 +6848,10 @@
         <v>0</v>
       </c>
       <c r="R90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T90">
         <v>7</v>
@@ -6916,7 +6916,7 @@
         <v>0</v>
       </c>
       <c r="Q91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R91" t="b">
         <v>0</v>
@@ -6987,13 +6987,13 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="Q92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T92">
         <v>7</v>
@@ -7061,10 +7061,10 @@
         <v>0</v>
       </c>
       <c r="R93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T93">
         <v>7</v>
@@ -7132,10 +7132,10 @@
         <v>0</v>
       </c>
       <c r="R94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T94">
         <v>7</v>
@@ -7203,10 +7203,10 @@
         <v>0</v>
       </c>
       <c r="R95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T95">
         <v>7</v>
@@ -7345,7 +7345,7 @@
         <v>0</v>
       </c>
       <c r="R97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S97" t="b">
         <v>1</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="R98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T98">
         <v>7</v>
@@ -7626,13 +7626,13 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="Q101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T101">
         <v>7</v>
@@ -7771,10 +7771,10 @@
         <v>0</v>
       </c>
       <c r="R103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T103">
         <v>7</v>
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="R105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S105" t="b">
         <v>1</v>
@@ -7984,10 +7984,10 @@
         <v>0</v>
       </c>
       <c r="R106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T106">
         <v>7</v>
@@ -8055,10 +8055,10 @@
         <v>0</v>
       </c>
       <c r="R107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T107">
         <v>7</v>
@@ -8126,7 +8126,7 @@
         <v>0</v>
       </c>
       <c r="R108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S108" t="b">
         <v>1</v>
@@ -8197,10 +8197,10 @@
         <v>0</v>
       </c>
       <c r="R109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T109">
         <v>7</v>
@@ -8475,10 +8475,10 @@
         <v>0</v>
       </c>
       <c r="R113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T113">
         <v>7</v>
@@ -8540,10 +8540,10 @@
         <v>0</v>
       </c>
       <c r="R114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T114">
         <v>7</v>
@@ -8605,10 +8605,10 @@
         <v>0</v>
       </c>
       <c r="R115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T115">
         <v>7</v>
@@ -8800,10 +8800,10 @@
         <v>0</v>
       </c>
       <c r="R118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T118">
         <v>7</v>
@@ -8865,7 +8865,7 @@
         <v>0</v>
       </c>
       <c r="R119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S119" t="b">
         <v>1</v>
@@ -8930,10 +8930,10 @@
         <v>0</v>
       </c>
       <c r="R120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T120">
         <v>7</v>
@@ -9060,10 +9060,10 @@
         <v>0</v>
       </c>
       <c r="R122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T122">
         <v>7</v>
@@ -9125,10 +9125,10 @@
         <v>0</v>
       </c>
       <c r="R123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T123">
         <v>7</v>
@@ -9190,10 +9190,10 @@
         <v>0</v>
       </c>
       <c r="R124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T124">
         <v>7</v>
@@ -9385,7 +9385,7 @@
         <v>0</v>
       </c>
       <c r="R127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S127" t="b">
         <v>1</v>
@@ -9450,10 +9450,10 @@
         <v>0</v>
       </c>
       <c r="R128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T128">
         <v>7</v>
@@ -9515,10 +9515,10 @@
         <v>0</v>
       </c>
       <c r="R129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T129">
         <v>7</v>
@@ -9648,7 +9648,7 @@
         <v>0</v>
       </c>
       <c r="S131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T131">
         <v>5</v>
@@ -9775,10 +9775,10 @@
         <v>0</v>
       </c>
       <c r="R133" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T133">
         <v>7</v>
@@ -9840,7 +9840,7 @@
         <v>0</v>
       </c>
       <c r="R134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S134" t="b">
         <v>1</v>
@@ -9905,10 +9905,10 @@
         <v>0</v>
       </c>
       <c r="R135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T135">
         <v>7</v>
@@ -9970,10 +9970,10 @@
         <v>0</v>
       </c>
       <c r="R136" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T136">
         <v>7</v>
@@ -10035,7 +10035,7 @@
         <v>0</v>
       </c>
       <c r="R137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S137" t="b">
         <v>1</v>
@@ -10100,10 +10100,10 @@
         <v>0</v>
       </c>
       <c r="R138" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T138">
         <v>7</v>
@@ -10168,7 +10168,7 @@
         <v>0</v>
       </c>
       <c r="S139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T139">
         <v>5</v>
@@ -10230,7 +10230,7 @@
         <v>0</v>
       </c>
       <c r="R140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S140" t="b">
         <v>1</v>
@@ -10295,10 +10295,10 @@
         <v>0</v>
       </c>
       <c r="R141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T141">
         <v>7</v>
@@ -10425,10 +10425,10 @@
         <v>0</v>
       </c>
       <c r="R143" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T143">
         <v>7</v>
@@ -10490,7 +10490,7 @@
         <v>0</v>
       </c>
       <c r="R144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S144" t="b">
         <v>1</v>
@@ -10555,10 +10555,10 @@
         <v>0</v>
       </c>
       <c r="R145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T145">
         <v>7</v>
@@ -10620,10 +10620,10 @@
         <v>0</v>
       </c>
       <c r="R146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S146" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T146">
         <v>7</v>
@@ -10685,7 +10685,7 @@
         <v>0</v>
       </c>
       <c r="R147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S147" t="b">
         <v>1</v>
@@ -10815,7 +10815,7 @@
         <v>0</v>
       </c>
       <c r="R149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S149" t="b">
         <v>1</v>
@@ -10880,10 +10880,10 @@
         <v>0</v>
       </c>
       <c r="R150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T150">
         <v>7</v>
@@ -11010,10 +11010,10 @@
         <v>0</v>
       </c>
       <c r="R152" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S152" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T152">
         <v>7</v>
@@ -11075,10 +11075,10 @@
         <v>0</v>
       </c>
       <c r="R153" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S153" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T153">
         <v>7</v>
@@ -11140,7 +11140,7 @@
         <v>0</v>
       </c>
       <c r="R154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S154" t="b">
         <v>1</v>
@@ -11205,10 +11205,10 @@
         <v>0</v>
       </c>
       <c r="R155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S155" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T155">
         <v>7</v>
@@ -11270,10 +11270,10 @@
         <v>0</v>
       </c>
       <c r="R156" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S156" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T156">
         <v>7</v>
@@ -11400,10 +11400,10 @@
         <v>0</v>
       </c>
       <c r="R158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T158">
         <v>7</v>
@@ -11465,10 +11465,10 @@
         <v>0</v>
       </c>
       <c r="R159" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T159">
         <v>7</v>
@@ -11530,10 +11530,10 @@
         <v>0</v>
       </c>
       <c r="R160" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T160">
         <v>7</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="R161" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S161" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T161">
         <v>7</v>
@@ -11660,10 +11660,10 @@
         <v>0</v>
       </c>
       <c r="R162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S162" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T162">
         <v>7</v>
@@ -11920,10 +11920,10 @@
         <v>0</v>
       </c>
       <c r="R166" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S166" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T166">
         <v>7</v>
@@ -11985,10 +11985,10 @@
         <v>0</v>
       </c>
       <c r="R167" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S167" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T167">
         <v>7</v>
@@ -12050,7 +12050,7 @@
         <v>0</v>
       </c>
       <c r="R168" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S168" t="b">
         <v>1</v>
@@ -12115,7 +12115,7 @@
         <v>0</v>
       </c>
       <c r="R169" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S169" t="b">
         <v>1</v>
@@ -12180,10 +12180,10 @@
         <v>0</v>
       </c>
       <c r="R170" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S170" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T170">
         <v>7</v>
@@ -12310,10 +12310,10 @@
         <v>0</v>
       </c>
       <c r="R172" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S172" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T172">
         <v>7</v>
@@ -12378,7 +12378,7 @@
         <v>0</v>
       </c>
       <c r="S173" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T173">
         <v>5</v>
@@ -12440,10 +12440,10 @@
         <v>0</v>
       </c>
       <c r="R174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S174" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T174">
         <v>7</v>
@@ -12505,10 +12505,10 @@
         <v>0</v>
       </c>
       <c r="R175" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S175" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T175">
         <v>7</v>
@@ -12570,10 +12570,10 @@
         <v>0</v>
       </c>
       <c r="R176" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S176" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T176">
         <v>7</v>
@@ -12700,7 +12700,7 @@
         <v>0</v>
       </c>
       <c r="R178" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S178" t="b">
         <v>1</v>
@@ -12765,7 +12765,7 @@
         <v>0</v>
       </c>
       <c r="R179" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S179" t="b">
         <v>1</v>
@@ -12895,10 +12895,10 @@
         <v>0</v>
       </c>
       <c r="R181" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S181" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T181">
         <v>7</v>
@@ -12960,7 +12960,7 @@
         <v>0</v>
       </c>
       <c r="R182" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S182" t="b">
         <v>1</v>
@@ -13090,10 +13090,10 @@
         <v>0</v>
       </c>
       <c r="R184" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S184" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T184">
         <v>7</v>
@@ -13119,7 +13119,7 @@
         <v>2</v>
       </c>
       <c r="D185" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E185">
         <v>7</v>
@@ -13155,7 +13155,7 @@
         <v>1</v>
       </c>
       <c r="R185" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S185" t="b">
         <v>1</v>
@@ -13164,7 +13164,7 @@
         <v>7</v>
       </c>
       <c r="U185">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="V185">
         <v>7</v>
@@ -13220,10 +13220,10 @@
         <v>0</v>
       </c>
       <c r="R186" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S186" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T186">
         <v>7</v>
@@ -13285,7 +13285,7 @@
         <v>0</v>
       </c>
       <c r="R187" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S187" t="b">
         <v>1</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="R188" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S188" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T188">
         <v>7</v>
@@ -13415,10 +13415,10 @@
         <v>0</v>
       </c>
       <c r="R189" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S189" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T189">
         <v>7</v>
@@ -13480,10 +13480,10 @@
         <v>0</v>
       </c>
       <c r="R190" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S190" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T190">
         <v>7</v>
@@ -13545,10 +13545,10 @@
         <v>0</v>
       </c>
       <c r="R191" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S191" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T191">
         <v>7</v>
@@ -13610,10 +13610,10 @@
         <v>0</v>
       </c>
       <c r="R192" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S192" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T192">
         <v>7</v>
@@ -13740,7 +13740,7 @@
         <v>0</v>
       </c>
       <c r="R194" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S194" t="b">
         <v>1</v>
@@ -13805,10 +13805,10 @@
         <v>0</v>
       </c>
       <c r="R195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S195" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T195">
         <v>7</v>
@@ -13935,10 +13935,10 @@
         <v>0</v>
       </c>
       <c r="R197" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S197" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T197">
         <v>7</v>
@@ -14065,7 +14065,7 @@
         <v>0</v>
       </c>
       <c r="R199" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S199" t="b">
         <v>1</v>
@@ -14130,10 +14130,10 @@
         <v>0</v>
       </c>
       <c r="R200" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S200" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T200">
         <v>7</v>
@@ -14195,10 +14195,10 @@
         <v>0</v>
       </c>
       <c r="R201" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S201" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T201">
         <v>7</v>
@@ -14325,10 +14325,10 @@
         <v>0</v>
       </c>
       <c r="R203" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S203" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T203">
         <v>7</v>
@@ -14390,10 +14390,10 @@
         <v>0</v>
       </c>
       <c r="R204" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S204" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T204">
         <v>7</v>
@@ -14455,10 +14455,10 @@
         <v>0</v>
       </c>
       <c r="R205" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S205" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T205">
         <v>7</v>
@@ -14520,10 +14520,10 @@
         <v>0</v>
       </c>
       <c r="R206" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S206" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T206">
         <v>7</v>
@@ -14650,7 +14650,7 @@
         <v>0</v>
       </c>
       <c r="R208" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S208" t="b">
         <v>1</v>
@@ -14715,10 +14715,10 @@
         <v>0</v>
       </c>
       <c r="R209" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S209" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T209">
         <v>7</v>
@@ -14910,10 +14910,10 @@
         <v>0</v>
       </c>
       <c r="R212" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S212" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T212">
         <v>7</v>
@@ -15040,10 +15040,10 @@
         <v>0</v>
       </c>
       <c r="R214" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S214" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T214">
         <v>7</v>
@@ -15170,7 +15170,7 @@
         <v>0</v>
       </c>
       <c r="R216" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S216" t="b">
         <v>1</v>
@@ -15235,10 +15235,10 @@
         <v>0</v>
       </c>
       <c r="R217" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S217" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T217">
         <v>7</v>
@@ -15300,10 +15300,10 @@
         <v>0</v>
       </c>
       <c r="R218" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S218" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T218">
         <v>7</v>
@@ -15365,7 +15365,7 @@
         <v>0</v>
       </c>
       <c r="R219" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S219" t="b">
         <v>1</v>
@@ -15430,10 +15430,10 @@
         <v>0</v>
       </c>
       <c r="R220" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S220" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T220">
         <v>7</v>

--- a/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_heart.xlsx
+++ b/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_heart.xlsx
@@ -88,10 +88,10 @@
     <t>cant_min_en_p_elegido</t>
   </si>
   <si>
-    <t>D35_R35_Pentropia</t>
+    <t>PRD35_PR35_CPent_UD080_PE45</t>
   </si>
   <si>
-    <t>D35_R35_Pproporcion</t>
+    <t>PRD35_PR35_CPprop_UD080_Ppp041</t>
   </si>
   <si>
     <t>proporcion</t>
